--- a/Side Bar Files/GWD Data/GWD MR Abstract.xlsx
+++ b/Side Bar Files/GWD Data/GWD MR Abstract.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="391">
   <si>
     <t>GWD Revised Market Rates 2025</t>
   </si>
@@ -32,7 +32,7 @@
     <t>Index</t>
   </si>
   <si>
-    <t>TVM</t>
+    <t>ADMIN</t>
   </si>
   <si>
     <t>Sl No</t>
@@ -536,7 +536,7 @@
     <t>12 mm thick nylon rope</t>
   </si>
   <si>
-    <t>meter</t>
+    <t>metre</t>
   </si>
   <si>
     <t>Pump Accessories</t>
@@ -1185,6 +1185,15 @@
   </si>
   <si>
     <t>32 A DP switch with indicator modular (MR1017)</t>
+  </si>
+  <si>
+    <t>GWDMR194</t>
+  </si>
+  <si>
+    <t>S&amp;F Digital Timer Switch</t>
+  </si>
+  <si>
+    <t>Motor Starter</t>
   </si>
 </sst>
 </file>
@@ -1229,7 +1238,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1245,24 +1254,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAD1DC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4DD0E1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F7FA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1395,54 +1386,54 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="4" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="1" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="1" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1454,6 +1445,39 @@
     <cellStyle name="Comma" xfId="18" builtinId="3"/>
     <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF4DD0E1"/>
+          <bgColor rgb="FF4DD0E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFE0F7FA"/>
+          <bgColor rgb="FFE0F7FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="GWD MR Abstract-style" pivot="0" table="0" count="3">
+      <tableStyleElement type="headerRow" dxfId="0"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="secondRowStripe" dxfId="2"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -1542,6 +1566,7 @@
       <sheetName val="3 Core Cable PRICE"/>
       <sheetName val="ARS Filter Media"/>
       <sheetName val="BW Casing Pipes"/>
+      <sheetName val="Electrical Essentials"/>
       <sheetName val="GI on Wall PRICE"/>
       <sheetName val="GI wo Trench"/>
       <sheetName val="GI With Trench PRICE"/>
@@ -1549,16 +1574,19 @@
       <sheetName val="Gravel for TWC"/>
       <sheetName val="Gutter&amp;Clamp"/>
       <sheetName val="HDPE Pipe PRICE"/>
+      <sheetName val="HP Erection and Pullout"/>
       <sheetName val="HP Repair Labour"/>
       <sheetName val="HP Repair Spares"/>
       <sheetName val="Hydrants"/>
       <sheetName val="Iron Structure"/>
+      <sheetName val="Lock"/>
       <sheetName val="Metallic PH"/>
       <sheetName val="Motor Starter GWD"/>
       <sheetName val="Motor Starter Monoblock"/>
       <sheetName val="Motor Starter PRICE"/>
       <sheetName val="Other Fittings PRICE"/>
       <sheetName val="Panel Board"/>
+      <sheetName val="Pump Cover"/>
       <sheetName val="Pump Erection "/>
       <sheetName val="Pump Pullout"/>
       <sheetName val="PVC Fittings"/>
@@ -1619,9 +1647,33 @@
       <sheetData sheetId="37"/>
       <sheetData sheetId="38"/>
       <sheetData sheetId="39"/>
+      <sheetData sheetId="40"/>
+      <sheetData sheetId="41"/>
+      <sheetData sheetId="42"/>
+      <sheetData sheetId="43"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_2" displayName="Table_2" ref="A3:L198">
+  <tableColumns count="12">
+    <tableColumn id="1" name="Sl No"/>
+    <tableColumn id="2" name="Code"/>
+    <tableColumn id="3" name="Item Name"/>
+    <tableColumn id="4" name="Item Name With Code"/>
+    <tableColumn id="5" name="Unit"/>
+    <tableColumn id="6" name="Main Category"/>
+    <tableColumn id="7" name="Sub Category 1"/>
+    <tableColumn id="8" name="Sub Category 2"/>
+    <tableColumn id="9" name="C1"/>
+    <tableColumn id="10" name="C2"/>
+    <tableColumn id="11" name="Indexed"/>
+    <tableColumn id="12" name="Total"/>
+  </tableColumns>
+  <tableStyleInfo name="GWD MR Abstract-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1920,8 +1972,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6D23B45-9E43-4E94-9450-9EBDF4BFB9A6}">
-  <dimension ref="A1:L197"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8272A8AB-D3E8-4EC4-9C8C-E2B6EAA3B9A7}">
+  <dimension ref="A1:L198"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:12" ht="12.75">
@@ -1960,7 +2012,7 @@
       <c r="K2" s="5"/>
       <c r="L2" s="11">
         <f t="array" ref="L2">((IFERROR(INDEX(CostIndex,MATCH(J2,District,0),),)))</f>
-        <v>1.4765999999999999</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="12.75">
@@ -2035,52 +2087,52 @@
       </c>
       <c r="K4" s="16">
         <f>J4*($L$2-1)</f>
-        <v>14.7746</v>
+        <v>0</v>
       </c>
       <c r="L4" s="16">
         <f>SUM(I4:K4)</f>
-        <v>125.77460000000001</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="12.75">
-      <c r="A5" s="17">
+      <c r="A5" s="14">
         <v>2</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="18" t="str">
+      <c r="D5" s="15" t="str">
         <f>CONCATENATE(C5," (Code: ",B5,")")</f>
         <v>S&amp;F PVC Bend 140 mm (DG) (Code: GWDMR002)</v>
       </c>
-      <c r="E5" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="19" t="s">
+      <c r="E5" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="19" t="s">
+      <c r="H5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="17">
+      <c r="I5" s="14">
         <v>150</v>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="14">
         <v>35</v>
       </c>
-      <c r="K5" s="19">
+      <c r="K5" s="16">
         <f>J5*($L$2-1)</f>
-        <v>16.681000000000001</v>
-      </c>
-      <c r="L5" s="19">
+        <v>0</v>
+      </c>
+      <c r="L5" s="16">
         <f>SUM(I5:K5)</f>
-        <v>201.68100000000001</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="12.75">
@@ -2117,52 +2169,52 @@
       </c>
       <c r="K6" s="16">
         <f>J6*($L$2-1)</f>
-        <v>17.6342</v>
+        <v>0</v>
       </c>
       <c r="L6" s="16">
         <f>SUM(I6:K6)</f>
-        <v>93.134200000000007</v>
+        <v>75.50</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="12.75">
-      <c r="A7" s="17">
+      <c r="A7" s="14">
         <v>4</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="18" t="str">
+      <c r="D7" s="15" t="str">
         <f>CONCATENATE(C7," (Code: ",B7,")")</f>
         <v>PVC End cap 150 mm (DG) (Code: GWDMR004)</v>
       </c>
-      <c r="E7" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="19" t="s">
+      <c r="E7" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I7" s="17">
+      <c r="I7" s="14">
         <v>41.20</v>
       </c>
-      <c r="J7" s="17">
+      <c r="J7" s="14">
         <v>39.50</v>
       </c>
-      <c r="K7" s="19">
+      <c r="K7" s="16">
         <f>J7*($L$2-1)</f>
-        <v>18.825700000000001</v>
-      </c>
-      <c r="L7" s="19">
+        <v>0</v>
+      </c>
+      <c r="L7" s="16">
         <f>SUM(I7:K7)</f>
-        <v>99.525700000000001</v>
+        <v>80.70</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="12.75">
@@ -2199,52 +2251,52 @@
       </c>
       <c r="K8" s="16">
         <f>J8*($L$2-1)</f>
-        <v>20.970400000000001</v>
+        <v>0</v>
       </c>
       <c r="L8" s="16">
         <f>SUM(I8:K8)</f>
-        <v>112.7704</v>
+        <v>91.80</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="12.75">
-      <c r="A9" s="17">
+      <c r="A9" s="14">
         <v>6</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="18" t="str">
+      <c r="D9" s="15" t="str">
         <f>CONCATENATE(C9," (Code: ",B9,")")</f>
         <v>PVC End Cap 200 mm (DG) (Code: GWDMR006)</v>
       </c>
-      <c r="E9" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G9" s="19" t="s">
+      <c r="E9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G9" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="H9" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="17">
+      <c r="I9" s="14">
         <v>52.50</v>
       </c>
-      <c r="J9" s="17">
+      <c r="J9" s="14">
         <v>48.50</v>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="16">
         <f>J9*($L$2-1)</f>
-        <v>23.115100000000002</v>
-      </c>
-      <c r="L9" s="19">
+        <v>0</v>
+      </c>
+      <c r="L9" s="16">
         <f>SUM(I9:K9)</f>
-        <v>124.1151</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="12.75">
@@ -2273,7 +2325,7 @@
       <c r="H10" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="14">
         <v>200</v>
       </c>
       <c r="J10" s="14">
@@ -2289,42 +2341,42 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="12.75">
-      <c r="A11" s="17">
+      <c r="A11" s="14">
         <v>8</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="18" t="str">
+      <c r="D11" s="15" t="str">
         <f>CONCATENATE(C11," (Code: ",B11,")")</f>
         <v>PVC Square End Cap 160 mm (Code: GWDMR008)</v>
       </c>
-      <c r="E11" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G11" s="19" t="s">
+      <c r="E11" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G11" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H11" s="19" t="s">
+      <c r="H11" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="17">
+      <c r="I11" s="14">
         <v>250</v>
       </c>
-      <c r="J11" s="17">
-        <v>0</v>
-      </c>
-      <c r="K11" s="19">
+      <c r="J11" s="14">
+        <v>0</v>
+      </c>
+      <c r="K11" s="16">
         <f>J11*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L11" s="19">
+      <c r="L11" s="16">
         <f>SUM(I11:K11)</f>
         <v>250</v>
       </c>
@@ -2355,7 +2407,7 @@
       <c r="H12" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="14">
         <v>150</v>
       </c>
       <c r="J12" s="14">
@@ -2371,42 +2423,42 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="12.75">
-      <c r="A13" s="17">
+      <c r="A13" s="14">
         <v>10</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="D13" s="18" t="str">
+      <c r="D13" s="15" t="str">
         <f>CONCATENATE(C13," (Code: ",B13,")")</f>
         <v>PVC Half  End Cap 160 mm (Code: GWDMR010)</v>
       </c>
-      <c r="E13" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="19" t="s">
+      <c r="E13" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G13" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H13" s="19" t="s">
+      <c r="H13" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="14">
         <v>160</v>
       </c>
-      <c r="J13" s="17">
-        <v>0</v>
-      </c>
-      <c r="K13" s="19">
+      <c r="J13" s="14">
+        <v>0</v>
+      </c>
+      <c r="K13" s="16">
         <f>J13*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="16">
         <f>SUM(I13:K13)</f>
         <v>160</v>
       </c>
@@ -2437,7 +2489,7 @@
       <c r="H14" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="14">
         <v>150</v>
       </c>
       <c r="J14" s="14">
@@ -2453,42 +2505,42 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="12.75">
-      <c r="A15" s="17">
+      <c r="A15" s="14">
         <v>12</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="D15" s="18" t="str">
+      <c r="D15" s="15" t="str">
         <f>CONCATENATE(C15," (Code: ",B15,")")</f>
         <v>PVC Half Square End Cap 160 mm (Code: GWDMR012)</v>
       </c>
-      <c r="E15" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="19" t="s">
+      <c r="E15" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G15" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="14">
         <v>175</v>
       </c>
-      <c r="J15" s="17">
-        <v>0</v>
-      </c>
-      <c r="K15" s="19">
+      <c r="J15" s="14">
+        <v>0</v>
+      </c>
+      <c r="K15" s="16">
         <f>J15*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L15" s="19">
+      <c r="L15" s="16">
         <f>SUM(I15:K15)</f>
         <v>175</v>
       </c>
@@ -2527,52 +2579,52 @@
       </c>
       <c r="K16" s="16">
         <f>J16*($L$2-1)</f>
-        <v>15.4895</v>
+        <v>0</v>
       </c>
       <c r="L16" s="16">
         <f>SUM(I16:K16)</f>
-        <v>132.98949999999999</v>
+        <v>117.50</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="12.75">
-      <c r="A17" s="17">
+      <c r="A17" s="14">
         <v>14</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="D17" s="18" t="str">
+      <c r="D17" s="15" t="str">
         <f>CONCATENATE(C17," (Code: ",B17,")")</f>
         <v>S&amp;F PVC Tee 140 mm (DG) (Code: GWDMR014)</v>
       </c>
-      <c r="E17" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F17" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G17" s="19" t="s">
+      <c r="E17" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="19" t="s">
+      <c r="H17" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="14">
         <v>160</v>
       </c>
-      <c r="J17" s="17">
+      <c r="J17" s="14">
         <v>36</v>
       </c>
-      <c r="K17" s="19">
+      <c r="K17" s="16">
         <f>J17*($L$2-1)</f>
-        <v>17.157599999999999</v>
-      </c>
-      <c r="L17" s="19">
+        <v>0</v>
+      </c>
+      <c r="L17" s="16">
         <f>SUM(I17:K17)</f>
-        <v>213.1576</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="12.75">
@@ -2609,50 +2661,50 @@
       </c>
       <c r="K18" s="16">
         <f>J18*($L$2-1)</f>
-        <v>17.8725</v>
+        <v>0</v>
       </c>
       <c r="L18" s="16">
         <f>SUM(I18:K18)</f>
-        <v>245.3725</v>
+        <v>227.50</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="12.75">
-      <c r="A19" s="17">
+      <c r="A19" s="14">
         <v>16</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="D19" s="18" t="str">
+      <c r="D19" s="15" t="str">
         <f>CONCATENATE(C19," (Code: ",B19,")")</f>
         <v>PVC Reducer 90X75 mm (Code: GWDMR016)</v>
       </c>
-      <c r="E19" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F19" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G19" s="19" t="s">
+      <c r="E19" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G19" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="19" t="s">
+      <c r="H19" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="14">
         <v>73</v>
       </c>
-      <c r="J19" s="17">
-        <v>0</v>
-      </c>
-      <c r="K19" s="19">
+      <c r="J19" s="14">
+        <v>0</v>
+      </c>
+      <c r="K19" s="16">
         <f>J19*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="19">
+      <c r="L19" s="16">
         <f>SUM(I19:K19)</f>
         <v>73</v>
       </c>
@@ -2699,42 +2751,42 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="12.75">
-      <c r="A21" s="17">
-        <v>18</v>
-      </c>
-      <c r="B21" s="18" t="s">
+      <c r="A21" s="14">
+        <v>18</v>
+      </c>
+      <c r="B21" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="18" t="str">
+      <c r="D21" s="15" t="str">
         <f>CONCATENATE(C21," (Code: ",B21,")")</f>
         <v>PVC Reducer 140X90 mm (Code: GWDMR018)</v>
       </c>
-      <c r="E21" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F21" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G21" s="19" t="s">
+      <c r="E21" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="19" t="s">
+      <c r="H21" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="14">
         <v>156</v>
       </c>
-      <c r="J21" s="17">
-        <v>0</v>
-      </c>
-      <c r="K21" s="19">
+      <c r="J21" s="14">
+        <v>0</v>
+      </c>
+      <c r="K21" s="16">
         <f>J21*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L21" s="19">
+      <c r="L21" s="16">
         <f>SUM(I21:K21)</f>
         <v>156</v>
       </c>
@@ -2781,42 +2833,42 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="12.75">
-      <c r="A23" s="17">
+      <c r="A23" s="14">
         <v>20</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="D23" s="18" t="str">
+      <c r="D23" s="15" t="str">
         <f>CONCATENATE(C23," (Code: ",B23,")")</f>
         <v>PVC Reducer 160X110 mm (Code: GWDMR020)</v>
       </c>
-      <c r="E23" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="19" t="s">
+      <c r="E23" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G23" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="19" t="s">
+      <c r="H23" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="14">
         <v>290</v>
       </c>
-      <c r="J23" s="17">
-        <v>0</v>
-      </c>
-      <c r="K23" s="19">
+      <c r="J23" s="14">
+        <v>0</v>
+      </c>
+      <c r="K23" s="16">
         <f>J23*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L23" s="19">
+      <c r="L23" s="16">
         <f>SUM(I23:K23)</f>
         <v>290</v>
       </c>
@@ -2863,42 +2915,42 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="12.75">
-      <c r="A25" s="17">
+      <c r="A25" s="14">
         <v>21</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="D25" s="18" t="str">
+      <c r="D25" s="15" t="str">
         <f>CONCATENATE(C25," (Code: ",B25,")")</f>
         <v>PVC Runner Drop 140 mm (Code: GWDMR021)</v>
       </c>
-      <c r="E25" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="19" t="s">
+      <c r="E25" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G25" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="19" t="s">
+      <c r="H25" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="14">
         <v>210</v>
       </c>
-      <c r="J25" s="17">
-        <v>0</v>
-      </c>
-      <c r="K25" s="19">
+      <c r="J25" s="14">
+        <v>0</v>
+      </c>
+      <c r="K25" s="16">
         <f>J25*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L25" s="19">
+      <c r="L25" s="16">
         <f>SUM(I25:K25)</f>
         <v>210</v>
       </c>
@@ -2945,42 +2997,42 @@
       </c>
     </row>
     <row r="27" spans="1:12" ht="12.75">
-      <c r="A27" s="17">
+      <c r="A27" s="14">
         <v>23</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="D27" s="18" t="str">
+      <c r="D27" s="15" t="str">
         <f>CONCATENATE(C27," (Code: ",B27,")")</f>
         <v>PVC  End Drop 140 mm (Code: GWDMR023)</v>
       </c>
-      <c r="E27" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G27" s="19" t="s">
+      <c r="E27" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G27" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H27" s="19" t="s">
+      <c r="H27" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I27" s="17">
+      <c r="I27" s="14">
         <v>192</v>
       </c>
-      <c r="J27" s="17">
-        <v>0</v>
-      </c>
-      <c r="K27" s="19">
+      <c r="J27" s="14">
+        <v>0</v>
+      </c>
+      <c r="K27" s="16">
         <f>J27*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="19">
+      <c r="L27" s="16">
         <f>SUM(I27:K27)</f>
         <v>192</v>
       </c>
@@ -3027,42 +3079,42 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="12.75">
-      <c r="A29" s="17">
+      <c r="A29" s="14">
         <v>25</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D29" s="18" t="str">
+      <c r="D29" s="15" t="str">
         <f>CONCATENATE(C29," (Code: ",B29,")")</f>
         <v>PVC Half End Drop 140 mm (Code: GWDMR025)</v>
       </c>
-      <c r="E29" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F29" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="19" t="s">
+      <c r="E29" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G29" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H29" s="19" t="s">
+      <c r="H29" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I29" s="17">
+      <c r="I29" s="14">
         <v>174</v>
       </c>
-      <c r="J29" s="17">
-        <v>0</v>
-      </c>
-      <c r="K29" s="19">
+      <c r="J29" s="14">
+        <v>0</v>
+      </c>
+      <c r="K29" s="16">
         <f>J29*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L29" s="19">
+      <c r="L29" s="16">
         <f>SUM(I29:K29)</f>
         <v>174</v>
       </c>
@@ -3109,42 +3161,42 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="12.75">
-      <c r="A31" s="17">
+      <c r="A31" s="14">
         <v>27</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D31" s="18" t="str">
+      <c r="D31" s="15" t="str">
         <f>CONCATENATE(C31," (Code: ",B31,")")</f>
         <v>PVC Square End Drop 140 mm (Code: GWDMR027)</v>
       </c>
-      <c r="E31" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F31" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G31" s="19" t="s">
+      <c r="E31" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G31" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H31" s="19" t="s">
+      <c r="H31" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="14">
         <v>198</v>
       </c>
-      <c r="J31" s="17">
-        <v>0</v>
-      </c>
-      <c r="K31" s="19">
+      <c r="J31" s="14">
+        <v>0</v>
+      </c>
+      <c r="K31" s="16">
         <f>J31*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L31" s="19">
+      <c r="L31" s="16">
         <f>SUM(I31:K31)</f>
         <v>198</v>
       </c>
@@ -3191,42 +3243,42 @@
       </c>
     </row>
     <row r="33" spans="1:12" ht="12.75">
-      <c r="A33" s="17">
+      <c r="A33" s="14">
         <v>29</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D33" s="18" t="str">
+      <c r="D33" s="15" t="str">
         <f>CONCATENATE(C33," (Code: ",B33,")")</f>
         <v>PVC Square Half End Drop 140 mm (Code: GWDMR029)</v>
       </c>
-      <c r="E33" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G33" s="19" t="s">
+      <c r="E33" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G33" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H33" s="19" t="s">
+      <c r="H33" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I33" s="17">
+      <c r="I33" s="14">
         <v>180</v>
       </c>
-      <c r="J33" s="17">
-        <v>0</v>
-      </c>
-      <c r="K33" s="19">
+      <c r="J33" s="14">
+        <v>0</v>
+      </c>
+      <c r="K33" s="16">
         <f>J33*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L33" s="19">
+      <c r="L33" s="16">
         <f>SUM(I33:K33)</f>
         <v>180</v>
       </c>
@@ -3273,44 +3325,44 @@
       </c>
     </row>
     <row r="35" spans="1:12" ht="12.75">
-      <c r="A35" s="17">
+      <c r="A35" s="14">
         <v>31</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="15" t="s">
         <v>89</v>
       </c>
-      <c r="D35" s="18" t="str">
+      <c r="D35" s="15" t="str">
         <f>CONCATENATE(C35," (Code: ",B35,")")</f>
         <v>S&amp;F PVC 45o Elbow 90 mm (DG) (Code: GWDMR031)</v>
       </c>
-      <c r="E35" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" s="19" t="s">
+      <c r="E35" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G35" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H35" s="19" t="s">
+      <c r="H35" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="I35" s="17">
+      <c r="I35" s="14">
         <v>45</v>
       </c>
-      <c r="J35" s="17">
+      <c r="J35" s="14">
         <v>31.50</v>
       </c>
-      <c r="K35" s="19">
+      <c r="K35" s="16">
         <f>J35*($L$2-1)</f>
-        <v>15.0129</v>
-      </c>
-      <c r="L35" s="19">
+        <v>0</v>
+      </c>
+      <c r="L35" s="16">
         <f>SUM(I35:K35)</f>
-        <v>91.512900000000002</v>
+        <v>76.50</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="12.75">
@@ -3347,52 +3399,52 @@
       </c>
       <c r="K36" s="16">
         <f>J36*($L$2-1)</f>
-        <v>18.110800000000001</v>
+        <v>0</v>
       </c>
       <c r="L36" s="16">
         <f>SUM(I36:K36)</f>
-        <v>136.11080000000001</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="12.75">
-      <c r="A37" s="17">
+      <c r="A37" s="14">
         <v>33</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="15" t="s">
         <v>93</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="D37" s="18" t="str">
+      <c r="D37" s="15" t="str">
         <f>CONCATENATE(C37," (Code: ",B37,")")</f>
         <v>S&amp;F PVC 45o Elbow 160 mm (DG) (Code: GWDMR033)</v>
       </c>
-      <c r="E37" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G37" s="19" t="s">
+      <c r="E37" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G37" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H37" s="19" t="s">
+      <c r="H37" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="I37" s="17">
+      <c r="I37" s="14">
         <v>95</v>
       </c>
-      <c r="J37" s="17">
+      <c r="J37" s="14">
         <v>42</v>
       </c>
-      <c r="K37" s="19">
+      <c r="K37" s="16">
         <f>J37*($L$2-1)</f>
-        <v>20.017199999999999</v>
-      </c>
-      <c r="L37" s="19">
+        <v>0</v>
+      </c>
+      <c r="L37" s="16">
         <f>SUM(I37:K37)</f>
-        <v>157.0172</v>
+        <v>137</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="12.75">
@@ -3437,42 +3489,42 @@
       </c>
     </row>
     <row r="39" spans="1:12" ht="12.75">
-      <c r="A39" s="17">
+      <c r="A39" s="14">
         <v>35</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="D39" s="18" t="str">
+      <c r="D39" s="15" t="str">
         <f>CONCATENATE(C39," (Code: ",B39,")")</f>
         <v>PVC Tank connector 40 mm (Code: GWDMR035)</v>
       </c>
-      <c r="E39" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F39" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G39" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H39" s="19" t="s">
+      <c r="E39" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H39" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I39" s="17">
+      <c r="I39" s="14">
         <v>240</v>
       </c>
-      <c r="J39" s="17">
-        <v>0</v>
-      </c>
-      <c r="K39" s="19">
+      <c r="J39" s="14">
+        <v>0</v>
+      </c>
+      <c r="K39" s="16">
         <f>J39*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L39" s="19">
+      <c r="L39" s="16">
         <f>SUM(I39:K39)</f>
         <v>240</v>
       </c>
@@ -3519,42 +3571,42 @@
       </c>
     </row>
     <row r="41" spans="1:12" ht="12.75">
-      <c r="A41" s="17">
+      <c r="A41" s="14">
         <v>37</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="D41" s="18" t="str">
+      <c r="D41" s="15" t="str">
         <f>CONCATENATE(C41," (Code: ",B41,")")</f>
         <v>PVC Tank connector 63 mm (Code: GWDMR037)</v>
       </c>
-      <c r="E41" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G41" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H41" s="19" t="s">
+      <c r="E41" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H41" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I41" s="17">
+      <c r="I41" s="14">
         <v>420</v>
       </c>
-      <c r="J41" s="17">
-        <v>0</v>
-      </c>
-      <c r="K41" s="19">
+      <c r="J41" s="14">
+        <v>0</v>
+      </c>
+      <c r="K41" s="16">
         <f>J41*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L41" s="19">
+      <c r="L41" s="16">
         <f>SUM(I41:K41)</f>
         <v>420</v>
       </c>
@@ -3601,42 +3653,42 @@
       </c>
     </row>
     <row r="43" spans="1:12" ht="12.75">
-      <c r="A43" s="17">
+      <c r="A43" s="14">
         <v>39</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="D43" s="18" t="str">
+      <c r="D43" s="15" t="str">
         <f>CONCATENATE(C43," (Code: ",B43,")")</f>
         <v>PVC Tank connector 90 mm (Code: GWDMR039)</v>
       </c>
-      <c r="E43" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G43" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H43" s="19" t="s">
+      <c r="E43" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H43" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="I43" s="17">
+      <c r="I43" s="14">
         <v>540</v>
       </c>
-      <c r="J43" s="17">
-        <v>0</v>
-      </c>
-      <c r="K43" s="19">
+      <c r="J43" s="14">
+        <v>0</v>
+      </c>
+      <c r="K43" s="16">
         <f>J43*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L43" s="19">
+      <c r="L43" s="16">
         <f>SUM(I43:K43)</f>
         <v>540</v>
       </c>
@@ -3683,42 +3735,42 @@
       </c>
     </row>
     <row r="45" spans="1:12" ht="12.75">
-      <c r="A45" s="17">
+      <c r="A45" s="14">
         <v>41</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="D45" s="18" t="str">
+      <c r="D45" s="15" t="str">
         <f>CONCATENATE(C45," (Code: ",B45,")")</f>
         <v>PVC Ball valve 32 mm (Code: GWDMR041)</v>
       </c>
-      <c r="E45" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G45" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H45" s="19" t="s">
+      <c r="E45" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H45" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I45" s="17">
+      <c r="I45" s="14">
         <v>216</v>
       </c>
-      <c r="J45" s="17">
-        <v>0</v>
-      </c>
-      <c r="K45" s="19">
+      <c r="J45" s="14">
+        <v>0</v>
+      </c>
+      <c r="K45" s="16">
         <f>J45*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L45" s="19">
+      <c r="L45" s="16">
         <f>SUM(I45:K45)</f>
         <v>216</v>
       </c>
@@ -3765,42 +3817,42 @@
       </c>
     </row>
     <row r="47" spans="1:12" ht="12.75">
-      <c r="A47" s="17">
+      <c r="A47" s="14">
         <v>43</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="D47" s="18" t="str">
+      <c r="D47" s="15" t="str">
         <f>CONCATENATE(C47," (Code: ",B47,")")</f>
         <v>PVC Ball valve 50 mm (Code: GWDMR043)</v>
       </c>
-      <c r="E47" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G47" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H47" s="19" t="s">
+      <c r="E47" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H47" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I47" s="17">
+      <c r="I47" s="14">
         <v>456</v>
       </c>
-      <c r="J47" s="17">
-        <v>0</v>
-      </c>
-      <c r="K47" s="19">
+      <c r="J47" s="14">
+        <v>0</v>
+      </c>
+      <c r="K47" s="16">
         <f>J47*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L47" s="19">
+      <c r="L47" s="16">
         <f>SUM(I47:K47)</f>
         <v>456</v>
       </c>
@@ -3847,42 +3899,42 @@
       </c>
     </row>
     <row r="49" spans="1:12" ht="12.75">
-      <c r="A49" s="17">
+      <c r="A49" s="14">
         <v>45</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="15" t="s">
         <v>120</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="D49" s="18" t="str">
+      <c r="D49" s="15" t="str">
         <f>CONCATENATE(C49," (Code: ",B49,")")</f>
         <v>PVC Ball valve 75 mm (Code: GWDMR045)</v>
       </c>
-      <c r="E49" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F49" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G49" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H49" s="19" t="s">
+      <c r="E49" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H49" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I49" s="17">
+      <c r="I49" s="14">
         <v>720</v>
       </c>
-      <c r="J49" s="17">
-        <v>0</v>
-      </c>
-      <c r="K49" s="19">
+      <c r="J49" s="14">
+        <v>0</v>
+      </c>
+      <c r="K49" s="16">
         <f>J49*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L49" s="19">
+      <c r="L49" s="16">
         <f>SUM(I49:K49)</f>
         <v>720</v>
       </c>
@@ -3929,42 +3981,42 @@
       </c>
     </row>
     <row r="51" spans="1:12" ht="12.75">
-      <c r="A51" s="17">
+      <c r="A51" s="14">
         <v>47</v>
       </c>
-      <c r="B51" s="18" t="s">
+      <c r="B51" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="C51" s="18" t="s">
+      <c r="C51" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="D51" s="18" t="str">
+      <c r="D51" s="15" t="str">
         <f>CONCATENATE(C51," (Code: ",B51,")")</f>
         <v>PVC Ball valve 110 mm (Code: GWDMR047)</v>
       </c>
-      <c r="E51" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F51" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G51" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H51" s="19" t="s">
+      <c r="E51" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G51" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H51" s="16" t="s">
         <v>111</v>
       </c>
-      <c r="I51" s="17">
+      <c r="I51" s="14">
         <v>1020</v>
       </c>
-      <c r="J51" s="17">
-        <v>0</v>
-      </c>
-      <c r="K51" s="19">
+      <c r="J51" s="14">
+        <v>0</v>
+      </c>
+      <c r="K51" s="16">
         <f>J51*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L51" s="19">
+      <c r="L51" s="16">
         <f>SUM(I51:K51)</f>
         <v>1020</v>
       </c>
@@ -4003,52 +4055,52 @@
       </c>
       <c r="K52" s="16">
         <f>J52*($L$2-1)</f>
-        <v>13.564036</v>
+        <v>0</v>
       </c>
       <c r="L52" s="16">
         <f>SUM(I52:K52)</f>
-        <v>60.524036000000002</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="12.75">
-      <c r="A53" s="17">
+      <c r="A53" s="14">
         <v>49</v>
       </c>
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D53" s="18" t="str">
+      <c r="D53" s="15" t="str">
         <f>CONCATENATE(C53," (Code: ",B53,")")</f>
         <v>S&amp;F PVC Coupling 40 mm (DG) (Code: GWDMR049)</v>
       </c>
-      <c r="E53" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F53" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G53" s="19" t="s">
+      <c r="E53" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G53" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H53" s="19" t="s">
+      <c r="H53" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="I53" s="17">
+      <c r="I53" s="14">
         <v>22.50</v>
       </c>
-      <c r="J53" s="17">
+      <c r="J53" s="14">
         <v>28.46</v>
       </c>
-      <c r="K53" s="19">
+      <c r="K53" s="16">
         <f>J53*($L$2-1)</f>
-        <v>13.564036</v>
-      </c>
-      <c r="L53" s="19">
+        <v>0</v>
+      </c>
+      <c r="L53" s="16">
         <f>SUM(I53:K53)</f>
-        <v>64.524035999999995</v>
+        <v>50.96</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="12.75">
@@ -4085,52 +4137,52 @@
       </c>
       <c r="K54" s="16">
         <f>J54*($L$2-1)</f>
-        <v>13.564036</v>
+        <v>0</v>
       </c>
       <c r="L54" s="16">
         <f>SUM(I54:K54)</f>
-        <v>67.524035999999995</v>
+        <v>53.96</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="12.75">
-      <c r="A55" s="17">
+      <c r="A55" s="14">
         <v>51</v>
       </c>
-      <c r="B55" s="18" t="s">
+      <c r="B55" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C55" s="18" t="s">
+      <c r="C55" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="D55" s="18" t="str">
+      <c r="D55" s="15" t="str">
         <f>CONCATENATE(C55," (Code: ",B55,")")</f>
         <v>S&amp;F PVC Coupling 63 mm (DG) (Code: GWDMR051)</v>
       </c>
-      <c r="E55" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" s="19" t="s">
+      <c r="E55" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="H55" s="19" t="s">
+      <c r="H55" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="I55" s="17">
+      <c r="I55" s="14">
         <v>28.46</v>
       </c>
-      <c r="J55" s="17">
+      <c r="J55" s="14">
         <v>29.77</v>
       </c>
-      <c r="K55" s="19">
+      <c r="K55" s="16">
         <f>J55*($L$2-1)</f>
-        <v>14.188382000000001</v>
-      </c>
-      <c r="L55" s="19">
+        <v>0</v>
+      </c>
+      <c r="L55" s="16">
         <f>SUM(I55:K55)</f>
-        <v>72.418381999999994</v>
+        <v>58.23</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="12.75">
@@ -4175,42 +4227,42 @@
       </c>
     </row>
     <row r="57" spans="1:12" ht="12.75">
-      <c r="A57" s="17">
+      <c r="A57" s="14">
         <v>53</v>
       </c>
-      <c r="B57" s="18" t="s">
+      <c r="B57" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="C57" s="18" t="s">
+      <c r="C57" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="D57" s="18" t="str">
+      <c r="D57" s="15" t="str">
         <f>CONCATENATE(C57," (Code: ",B57,")")</f>
         <v>GI Bend 40 mm (Code: GWDMR053)</v>
       </c>
-      <c r="E57" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F57" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G57" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H57" s="19" t="s">
+      <c r="E57" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H57" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="I57" s="17">
+      <c r="I57" s="14">
         <v>162</v>
       </c>
-      <c r="J57" s="17">
-        <v>0</v>
-      </c>
-      <c r="K57" s="19">
+      <c r="J57" s="14">
+        <v>0</v>
+      </c>
+      <c r="K57" s="16">
         <f>J57*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L57" s="19">
+      <c r="L57" s="16">
         <f>SUM(I57:K57)</f>
         <v>162</v>
       </c>
@@ -4257,42 +4309,42 @@
       </c>
     </row>
     <row r="59" spans="1:12" ht="12.75">
-      <c r="A59" s="17">
+      <c r="A59" s="14">
         <v>55</v>
       </c>
-      <c r="B59" s="18" t="s">
+      <c r="B59" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="D59" s="18" t="str">
+      <c r="D59" s="15" t="str">
         <f>CONCATENATE(C59," (Code: ",B59,")")</f>
         <v>GI Bend 65 mm (Code: GWDMR055)</v>
       </c>
-      <c r="E59" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F59" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G59" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H59" s="19" t="s">
+      <c r="E59" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G59" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H59" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="I59" s="17">
+      <c r="I59" s="14">
         <v>414</v>
       </c>
-      <c r="J59" s="17">
-        <v>0</v>
-      </c>
-      <c r="K59" s="19">
+      <c r="J59" s="14">
+        <v>0</v>
+      </c>
+      <c r="K59" s="16">
         <f>J59*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L59" s="19">
+      <c r="L59" s="16">
         <f>SUM(I59:K59)</f>
         <v>414</v>
       </c>
@@ -4339,42 +4391,42 @@
       </c>
     </row>
     <row r="61" spans="1:12" ht="12.75">
-      <c r="A61" s="17">
+      <c r="A61" s="14">
         <v>57</v>
       </c>
-      <c r="B61" s="18" t="s">
+      <c r="B61" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="C61" s="18" t="s">
+      <c r="C61" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="D61" s="18" t="str">
+      <c r="D61" s="15" t="str">
         <f>CONCATENATE(C61," (Code: ",B61,")")</f>
         <v>GI Socket 40 mm (Code: GWDMR057)</v>
       </c>
-      <c r="E61" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F61" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G61" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H61" s="19" t="s">
+      <c r="E61" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G61" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H61" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="I61" s="17">
+      <c r="I61" s="14">
         <v>69.69</v>
       </c>
-      <c r="J61" s="17">
-        <v>0</v>
-      </c>
-      <c r="K61" s="19">
+      <c r="J61" s="14">
+        <v>0</v>
+      </c>
+      <c r="K61" s="16">
         <f>J61*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L61" s="19">
+      <c r="L61" s="16">
         <f>SUM(I61:K61)</f>
         <v>69.69</v>
       </c>
@@ -4421,42 +4473,42 @@
       </c>
     </row>
     <row r="63" spans="1:12" ht="12.75">
-      <c r="A63" s="17">
+      <c r="A63" s="14">
         <v>59</v>
       </c>
-      <c r="B63" s="18" t="s">
+      <c r="B63" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="C63" s="18" t="s">
+      <c r="C63" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="D63" s="18" t="str">
+      <c r="D63" s="15" t="str">
         <f>CONCATENATE(C63," (Code: ",B63,")")</f>
         <v>GI Socket 65 mm (Code: GWDMR059)</v>
       </c>
-      <c r="E63" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F63" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G63" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H63" s="19" t="s">
+      <c r="E63" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G63" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H63" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="I63" s="17">
+      <c r="I63" s="14">
         <v>127.77</v>
       </c>
-      <c r="J63" s="17">
-        <v>0</v>
-      </c>
-      <c r="K63" s="19">
+      <c r="J63" s="14">
+        <v>0</v>
+      </c>
+      <c r="K63" s="16">
         <f>J63*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L63" s="19">
+      <c r="L63" s="16">
         <f>SUM(I63:K63)</f>
         <v>127.77</v>
       </c>
@@ -4503,42 +4555,42 @@
       </c>
     </row>
     <row r="65" spans="1:12" ht="12.75">
-      <c r="A65" s="17">
+      <c r="A65" s="14">
         <v>61</v>
       </c>
-      <c r="B65" s="18" t="s">
+      <c r="B65" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="C65" s="18" t="s">
+      <c r="C65" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="D65" s="18" t="str">
+      <c r="D65" s="15" t="str">
         <f>CONCATENATE(C65," (Code: ",B65,")")</f>
         <v>GI Tee 40 mm (Code: GWDMR061)</v>
       </c>
-      <c r="E65" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F65" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G65" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H65" s="19" t="s">
+      <c r="E65" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H65" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="I65" s="17">
+      <c r="I65" s="14">
         <v>270</v>
       </c>
-      <c r="J65" s="17">
-        <v>0</v>
-      </c>
-      <c r="K65" s="19">
+      <c r="J65" s="14">
+        <v>0</v>
+      </c>
+      <c r="K65" s="16">
         <f>J65*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L65" s="19">
+      <c r="L65" s="16">
         <f>SUM(I65:K65)</f>
         <v>270</v>
       </c>
@@ -4585,42 +4637,42 @@
       </c>
     </row>
     <row r="67" spans="1:12" ht="12.75">
-      <c r="A67" s="17">
+      <c r="A67" s="14">
         <v>63</v>
       </c>
-      <c r="B67" s="18" t="s">
+      <c r="B67" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="C67" s="18" t="s">
+      <c r="C67" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="D67" s="18" t="str">
+      <c r="D67" s="15" t="str">
         <f>CONCATENATE(C67," (Code: ",B67,")")</f>
         <v>GI Tee 65 mm (Code: GWDMR063)</v>
       </c>
-      <c r="E67" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F67" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G67" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H67" s="19" t="s">
+      <c r="E67" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H67" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="I67" s="17">
+      <c r="I67" s="14">
         <v>636</v>
       </c>
-      <c r="J67" s="17">
-        <v>0</v>
-      </c>
-      <c r="K67" s="19">
+      <c r="J67" s="14">
+        <v>0</v>
+      </c>
+      <c r="K67" s="16">
         <f>J67*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L67" s="19">
+      <c r="L67" s="16">
         <f>SUM(I67:K67)</f>
         <v>636</v>
       </c>
@@ -4667,42 +4719,42 @@
       </c>
     </row>
     <row r="69" spans="1:12" ht="12.75">
-      <c r="A69" s="17">
+      <c r="A69" s="14">
         <v>65</v>
       </c>
-      <c r="B69" s="18" t="s">
+      <c r="B69" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="C69" s="18" t="s">
+      <c r="C69" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="D69" s="18" t="str">
+      <c r="D69" s="15" t="str">
         <f>CONCATENATE(C69," (Code: ",B69,")")</f>
         <v>Compressor pump 2 HP single phase (Code: GWDMR065)</v>
       </c>
-      <c r="E69" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F69" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G69" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H69" s="19" t="s">
+      <c r="E69" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F69" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G69" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H69" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="I69" s="17">
+      <c r="I69" s="14">
         <v>27540</v>
       </c>
-      <c r="J69" s="17">
-        <v>0</v>
-      </c>
-      <c r="K69" s="19">
+      <c r="J69" s="14">
+        <v>0</v>
+      </c>
+      <c r="K69" s="16">
         <f>J69*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L69" s="19">
+      <c r="L69" s="16">
         <f>SUM(I69:K69)</f>
         <v>27540</v>
       </c>
@@ -4749,42 +4801,42 @@
       </c>
     </row>
     <row r="71" spans="1:12" ht="12.75">
-      <c r="A71" s="17">
+      <c r="A71" s="14">
         <v>67</v>
       </c>
-      <c r="B71" s="18" t="s">
+      <c r="B71" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="C71" s="18" t="s">
+      <c r="C71" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="D71" s="18" t="str">
+      <c r="D71" s="15" t="str">
         <f>CONCATENATE(C71," (Code: ",B71,")")</f>
         <v>Compressor pump 7.5 HP three phase (Code: GWDMR067)</v>
       </c>
-      <c r="E71" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G71" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H71" s="19" t="s">
+      <c r="E71" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G71" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H71" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="I71" s="17">
+      <c r="I71" s="14">
         <v>51000</v>
       </c>
-      <c r="J71" s="17">
-        <v>0</v>
-      </c>
-      <c r="K71" s="19">
+      <c r="J71" s="14">
+        <v>0</v>
+      </c>
+      <c r="K71" s="16">
         <f>J71*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L71" s="19">
+      <c r="L71" s="16">
         <f>SUM(I71:K71)</f>
         <v>51000</v>
       </c>
@@ -4831,42 +4883,42 @@
       </c>
     </row>
     <row r="73" spans="1:12" ht="12.75">
-      <c r="A73" s="17">
+      <c r="A73" s="14">
         <v>69</v>
       </c>
-      <c r="B73" s="18" t="s">
+      <c r="B73" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="C73" s="18" t="s">
+      <c r="C73" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="D73" s="18" t="str">
+      <c r="D73" s="15" t="str">
         <f>CONCATENATE(C73," (Code: ",B73,")")</f>
         <v>14 mm thick nylon rope (Code: GWDMR069)</v>
       </c>
-      <c r="E73" s="17" t="s">
+      <c r="E73" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="F73" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G73" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H73" s="19" t="s">
+      <c r="F73" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G73" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H73" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="I73" s="17">
+      <c r="I73" s="14">
         <v>49.20</v>
       </c>
-      <c r="J73" s="17">
-        <v>0</v>
-      </c>
-      <c r="K73" s="19">
+      <c r="J73" s="14">
+        <v>0</v>
+      </c>
+      <c r="K73" s="16">
         <f>J73*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L73" s="19">
+      <c r="L73" s="16">
         <f>SUM(I73:K73)</f>
         <v>49.20</v>
       </c>
@@ -4913,42 +4965,42 @@
       </c>
     </row>
     <row r="75" spans="1:12" ht="12.75">
-      <c r="A75" s="17">
+      <c r="A75" s="14">
         <v>71</v>
       </c>
-      <c r="B75" s="18" t="s">
+      <c r="B75" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="C75" s="18" t="s">
+      <c r="C75" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="D75" s="18" t="str">
+      <c r="D75" s="15" t="str">
         <f>CONCATENATE(C75," (Code: ",B75,")")</f>
         <v>Steel rope (Code: GWDMR071)</v>
       </c>
-      <c r="E75" s="17" t="s">
+      <c r="E75" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="F75" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G75" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H75" s="19" t="s">
+      <c r="F75" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G75" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H75" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="I75" s="17">
+      <c r="I75" s="14">
         <v>114</v>
       </c>
-      <c r="J75" s="17">
-        <v>0</v>
-      </c>
-      <c r="K75" s="19">
+      <c r="J75" s="14">
+        <v>0</v>
+      </c>
+      <c r="K75" s="16">
         <f>J75*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L75" s="19">
+      <c r="L75" s="16">
         <f>SUM(I75:K75)</f>
         <v>114</v>
       </c>
@@ -4995,42 +5047,42 @@
       </c>
     </row>
     <row r="77" spans="1:12" ht="12.75">
-      <c r="A77" s="17">
+      <c r="A77" s="14">
         <v>73</v>
       </c>
-      <c r="B77" s="18" t="s">
+      <c r="B77" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="C77" s="18" t="s">
+      <c r="C77" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="D77" s="18" t="str">
+      <c r="D77" s="15" t="str">
         <f>CONCATENATE(C77," (Code: ",B77,")")</f>
         <v>40 mm dia UPVC pipe (Code: GWDMR073)</v>
       </c>
-      <c r="E77" s="17" t="s">
+      <c r="E77" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="F77" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G77" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H77" s="19" t="s">
+      <c r="F77" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G77" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H77" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="I77" s="17">
+      <c r="I77" s="14">
         <v>354</v>
       </c>
-      <c r="J77" s="17">
-        <v>0</v>
-      </c>
-      <c r="K77" s="19">
+      <c r="J77" s="14">
+        <v>0</v>
+      </c>
+      <c r="K77" s="16">
         <f>J77*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L77" s="19">
+      <c r="L77" s="16">
         <f>SUM(I77:K77)</f>
         <v>354</v>
       </c>
@@ -5077,42 +5129,42 @@
       </c>
     </row>
     <row r="79" spans="1:12" ht="12.75">
-      <c r="A79" s="17">
+      <c r="A79" s="14">
         <v>75</v>
       </c>
-      <c r="B79" s="18" t="s">
+      <c r="B79" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="C79" s="18" t="s">
+      <c r="C79" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="D79" s="18" t="str">
+      <c r="D79" s="15" t="str">
         <f>CONCATENATE(C79," (Code: ",B79,")")</f>
         <v>63 mm dia UPVC pipe (Code: GWDMR075)</v>
       </c>
-      <c r="E79" s="17" t="s">
+      <c r="E79" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="F79" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G79" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H79" s="19" t="s">
+      <c r="F79" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G79" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H79" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="I79" s="17">
+      <c r="I79" s="14">
         <v>552</v>
       </c>
-      <c r="J79" s="17">
-        <v>0</v>
-      </c>
-      <c r="K79" s="19">
+      <c r="J79" s="14">
+        <v>0</v>
+      </c>
+      <c r="K79" s="16">
         <f>J79*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L79" s="19">
+      <c r="L79" s="16">
         <f>SUM(I79:K79)</f>
         <v>552</v>
       </c>
@@ -5159,42 +5211,42 @@
       </c>
     </row>
     <row r="81" spans="1:12" ht="12.75">
-      <c r="A81" s="17">
+      <c r="A81" s="14">
         <v>77</v>
       </c>
-      <c r="B81" s="18" t="s">
+      <c r="B81" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C81" s="18" t="s">
+      <c r="C81" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="D81" s="18" t="str">
+      <c r="D81" s="15" t="str">
         <f>CONCATENATE(C81," (Code: ",B81,")")</f>
         <v>32 mm dia HDPE pipe (DG) (8kg) (Code: GWDMR077)</v>
       </c>
-      <c r="E81" s="17" t="s">
+      <c r="E81" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="F81" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G81" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H81" s="19" t="s">
+      <c r="F81" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H81" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="I81" s="17">
+      <c r="I81" s="14">
         <v>35</v>
       </c>
-      <c r="J81" s="17">
-        <v>0</v>
-      </c>
-      <c r="K81" s="19">
+      <c r="J81" s="14">
+        <v>0</v>
+      </c>
+      <c r="K81" s="16">
         <f>J81*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L81" s="19">
+      <c r="L81" s="16">
         <f>SUM(I81:K81)</f>
         <v>35</v>
       </c>
@@ -5241,42 +5293,42 @@
       </c>
     </row>
     <row r="83" spans="1:12" ht="12.75">
-      <c r="A83" s="17">
+      <c r="A83" s="14">
         <v>79</v>
       </c>
-      <c r="B83" s="18" t="s">
+      <c r="B83" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C83" s="18" t="s">
+      <c r="C83" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="D83" s="18" t="str">
+      <c r="D83" s="15" t="str">
         <f>CONCATENATE(C83," (Code: ",B83,")")</f>
         <v>32 mm SS Adapter (Code: GWDMR079)</v>
       </c>
-      <c r="E83" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F83" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G83" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H83" s="19" t="s">
+      <c r="E83" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F83" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G83" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H83" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="I83" s="17">
+      <c r="I83" s="14">
         <v>804</v>
       </c>
-      <c r="J83" s="17">
-        <v>0</v>
-      </c>
-      <c r="K83" s="19">
+      <c r="J83" s="14">
+        <v>0</v>
+      </c>
+      <c r="K83" s="16">
         <f>J83*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L83" s="19">
+      <c r="L83" s="16">
         <f>SUM(I83:K83)</f>
         <v>804</v>
       </c>
@@ -5323,42 +5375,42 @@
       </c>
     </row>
     <row r="85" spans="1:12" ht="12.75">
-      <c r="A85" s="17">
+      <c r="A85" s="14">
         <v>81</v>
       </c>
-      <c r="B85" s="18" t="s">
+      <c r="B85" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="C85" s="18" t="s">
+      <c r="C85" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="D85" s="18" t="str">
+      <c r="D85" s="15" t="str">
         <f>CONCATENATE(C85," (Code: ",B85,")")</f>
         <v>50 mm SS Adapter (Code: GWDMR081)</v>
       </c>
-      <c r="E85" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F85" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G85" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H85" s="19" t="s">
+      <c r="E85" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F85" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G85" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H85" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="I85" s="17">
+      <c r="I85" s="14">
         <v>1200</v>
       </c>
-      <c r="J85" s="17">
-        <v>0</v>
-      </c>
-      <c r="K85" s="19">
+      <c r="J85" s="14">
+        <v>0</v>
+      </c>
+      <c r="K85" s="16">
         <f>J85*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L85" s="19">
+      <c r="L85" s="16">
         <f>SUM(I85:K85)</f>
         <v>1200</v>
       </c>
@@ -5405,42 +5457,42 @@
       </c>
     </row>
     <row r="87" spans="1:12" ht="12.75">
-      <c r="A87" s="17">
+      <c r="A87" s="14">
         <v>83</v>
       </c>
-      <c r="B87" s="18" t="s">
+      <c r="B87" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="C87" s="18" t="s">
+      <c r="C87" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="D87" s="18" t="str">
+      <c r="D87" s="15" t="str">
         <f>CONCATENATE(C87," (Code: ",B87,")")</f>
         <v>63 mm UPVC Union (Code: GWDMR083)</v>
       </c>
-      <c r="E87" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F87" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G87" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H87" s="19" t="s">
+      <c r="E87" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F87" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G87" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H87" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="I87" s="17">
+      <c r="I87" s="14">
         <v>540</v>
       </c>
-      <c r="J87" s="17">
-        <v>0</v>
-      </c>
-      <c r="K87" s="19">
+      <c r="J87" s="14">
+        <v>0</v>
+      </c>
+      <c r="K87" s="16">
         <f>J87*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L87" s="19">
+      <c r="L87" s="16">
         <f>SUM(I87:K87)</f>
         <v>540</v>
       </c>
@@ -5487,42 +5539,42 @@
       </c>
     </row>
     <row r="89" spans="1:12" ht="12.75">
-      <c r="A89" s="17">
+      <c r="A89" s="14">
         <v>85</v>
       </c>
-      <c r="B89" s="18" t="s">
+      <c r="B89" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="C89" s="18" t="s">
+      <c r="C89" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="D89" s="18" t="str">
+      <c r="D89" s="15" t="str">
         <f>CONCATENATE(C89," (Code: ",B89,")")</f>
         <v>Sodium Bentonite (ordinary) (Code: GWDMR085)</v>
       </c>
-      <c r="E89" s="17" t="s">
+      <c r="E89" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="F89" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G89" s="19" t="s">
+      <c r="F89" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G89" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="H89" s="19" t="s">
+      <c r="H89" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="I89" s="17">
+      <c r="I89" s="14">
         <v>7000</v>
       </c>
-      <c r="J89" s="17">
-        <v>0</v>
-      </c>
-      <c r="K89" s="19">
+      <c r="J89" s="14">
+        <v>0</v>
+      </c>
+      <c r="K89" s="16">
         <f>J89*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L89" s="19">
+      <c r="L89" s="16">
         <f>SUM(I89:K89)</f>
         <v>7000</v>
       </c>
@@ -5569,42 +5621,42 @@
       </c>
     </row>
     <row r="91" spans="1:12" ht="12.75">
-      <c r="A91" s="17">
+      <c r="A91" s="14">
         <v>87</v>
       </c>
-      <c r="B91" s="18" t="s">
+      <c r="B91" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="C91" s="18" t="s">
+      <c r="C91" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="D91" s="18" t="str">
+      <c r="D91" s="15" t="str">
         <f>CONCATENATE(C91," (Code: ",B91,")")</f>
         <v>MS Casing pipe 450 mm dia, 6 mm thickness (Code: GWDMR087)</v>
       </c>
-      <c r="E91" s="17" t="s">
+      <c r="E91" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="F91" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G91" s="19" t="s">
+      <c r="F91" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G91" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="H91" s="19" t="s">
+      <c r="H91" s="16" t="s">
         <v>214</v>
       </c>
-      <c r="I91" s="17">
+      <c r="I91" s="14">
         <v>8450</v>
       </c>
-      <c r="J91" s="17">
-        <v>0</v>
-      </c>
-      <c r="K91" s="19">
+      <c r="J91" s="14">
+        <v>0</v>
+      </c>
+      <c r="K91" s="16">
         <f>J91*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L91" s="19">
+      <c r="L91" s="16">
         <f>SUM(I91:K91)</f>
         <v>8450</v>
       </c>
@@ -5635,7 +5687,7 @@
       <c r="H92" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I92" s="20">
+      <c r="I92" s="14">
         <v>180</v>
       </c>
       <c r="J92" s="14">
@@ -5651,42 +5703,42 @@
       </c>
     </row>
     <row r="93" spans="1:12" ht="12.75">
-      <c r="A93" s="17">
+      <c r="A93" s="14">
         <v>89</v>
       </c>
-      <c r="B93" s="18" t="s">
+      <c r="B93" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="C93" s="18" t="s">
+      <c r="C93" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="D93" s="18" t="str">
+      <c r="D93" s="15" t="str">
         <f>CONCATENATE(C93," (Code: ",B93,")")</f>
         <v>Coated mesh for placing inside filter tank (for recharge schemes) (Code: GWDMR089)</v>
       </c>
-      <c r="E93" s="17" t="s">
+      <c r="E93" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="F93" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G93" s="19" t="s">
+      <c r="F93" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G93" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H93" s="19" t="s">
+      <c r="H93" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I93" s="17">
+      <c r="I93" s="14">
         <v>300</v>
       </c>
-      <c r="J93" s="17">
-        <v>0</v>
-      </c>
-      <c r="K93" s="19">
+      <c r="J93" s="14">
+        <v>0</v>
+      </c>
+      <c r="K93" s="16">
         <f>J93*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L93" s="19">
+      <c r="L93" s="16">
         <f>SUM(I93:K93)</f>
         <v>300</v>
       </c>
@@ -5717,7 +5769,7 @@
       <c r="H94" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I94" s="20">
+      <c r="I94" s="14">
         <v>180</v>
       </c>
       <c r="J94" s="14">
@@ -5733,42 +5785,42 @@
       </c>
     </row>
     <row r="95" spans="1:12" ht="12.75">
-      <c r="A95" s="17">
+      <c r="A95" s="14">
         <v>91</v>
       </c>
-      <c r="B95" s="18" t="s">
+      <c r="B95" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="C95" s="18" t="s">
+      <c r="C95" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="D95" s="18" t="str">
+      <c r="D95" s="15" t="str">
         <f>CONCATENATE(C95," (Code: ",B95,")")</f>
         <v>Sieve mesh 140 mm (inside inspection chamber) (for recharge schemes) (Code: GWDMR091)</v>
       </c>
-      <c r="E95" s="17" t="s">
+      <c r="E95" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="F95" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G95" s="19" t="s">
+      <c r="F95" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G95" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="H95" s="19" t="s">
+      <c r="H95" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I95" s="17">
+      <c r="I95" s="14">
         <v>200</v>
       </c>
-      <c r="J95" s="17">
-        <v>0</v>
-      </c>
-      <c r="K95" s="19">
+      <c r="J95" s="14">
+        <v>0</v>
+      </c>
+      <c r="K95" s="16">
         <f>J95*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L95" s="19">
+      <c r="L95" s="16">
         <f>SUM(I95:K95)</f>
         <v>200</v>
       </c>
@@ -5799,7 +5851,7 @@
       <c r="H96" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="I96" s="20">
+      <c r="I96" s="14">
         <v>50</v>
       </c>
       <c r="J96" s="14">
@@ -5815,42 +5867,42 @@
       </c>
     </row>
     <row r="97" spans="1:12" ht="12.75">
-      <c r="A97" s="17">
+      <c r="A97" s="14">
         <v>93</v>
       </c>
-      <c r="B97" s="18" t="s">
+      <c r="B97" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C97" s="18" t="s">
+      <c r="C97" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D97" s="18" t="str">
+      <c r="D97" s="15" t="str">
         <f>CONCATENATE(C97," (Code: ",B97,")")</f>
         <v>PVC Wiring Pipe (Code: GWDMR093)</v>
       </c>
-      <c r="E97" s="17" t="s">
+      <c r="E97" s="14" t="s">
         <v>171</v>
       </c>
-      <c r="F97" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G97" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H97" s="19" t="s">
+      <c r="F97" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G97" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H97" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="I97" s="17">
+      <c r="I97" s="14">
         <v>30</v>
       </c>
-      <c r="J97" s="17">
-        <v>0</v>
-      </c>
-      <c r="K97" s="19">
+      <c r="J97" s="14">
+        <v>0</v>
+      </c>
+      <c r="K97" s="16">
         <f>J97*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L97" s="19">
+      <c r="L97" s="16">
         <f>SUM(I97:K97)</f>
         <v>30</v>
       </c>
@@ -5900,45 +5952,45 @@
       </c>
     </row>
     <row r="99" spans="1:12" ht="12.75">
-      <c r="A99" s="17">
+      <c r="A99" s="14">
         <v>95</v>
       </c>
-      <c r="B99" s="18" t="s">
+      <c r="B99" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="C99" s="18" t="str">
+      <c r="C99" s="15" t="str">
         <f>'[1]HP Repair Spares'!E2</f>
         <v>Head with welded components only without cover</v>
       </c>
-      <c r="D99" s="18" t="str">
+      <c r="D99" s="15" t="str">
         <f>CONCATENATE(C99," (Code: ",B99,")")</f>
         <v>Head with welded components only without cover (Code: GWDMR095)</v>
       </c>
-      <c r="E99" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F99" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G99" s="19" t="s">
+      <c r="E99" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F99" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G99" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H99" s="19" t="s">
+      <c r="H99" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I99" s="17">
+      <c r="I99" s="14">
         <f>'[1]HP Repair Spares'!F2</f>
         <v>2280</v>
       </c>
-      <c r="J99" s="17">
+      <c r="J99" s="14">
         <f>'[1]HP Repair Spares'!G2</f>
         <v>0</v>
       </c>
-      <c r="K99" s="19">
+      <c r="K99" s="16">
         <f>J99*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L99" s="19">
+      <c r="L99" s="16">
         <f>SUM(I99:K99)</f>
         <v>2280</v>
       </c>
@@ -5988,45 +6040,45 @@
       </c>
     </row>
     <row r="101" spans="1:12" ht="12.75">
-      <c r="A101" s="17">
-        <v>97</v>
-      </c>
-      <c r="B101" s="18" t="s">
+      <c r="A101" s="14">
+        <v>97</v>
+      </c>
+      <c r="B101" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="C101" s="18" t="str">
+      <c r="C101" s="15" t="str">
         <f>'[1]HP Repair Spares'!E4</f>
         <v>Additional Plate</v>
       </c>
-      <c r="D101" s="18" t="str">
+      <c r="D101" s="15" t="str">
         <f>CONCATENATE(C101," (Code: ",B101,")")</f>
         <v>Additional Plate (Code: GWDMR097)</v>
       </c>
-      <c r="E101" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F101" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G101" s="19" t="s">
+      <c r="E101" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F101" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G101" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H101" s="19" t="s">
+      <c r="H101" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I101" s="17">
+      <c r="I101" s="14">
         <f>'[1]HP Repair Spares'!F4</f>
         <v>450</v>
       </c>
-      <c r="J101" s="17">
+      <c r="J101" s="14">
         <f>'[1]HP Repair Spares'!G4</f>
         <v>0</v>
       </c>
-      <c r="K101" s="19">
+      <c r="K101" s="16">
         <f>J101*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L101" s="19">
+      <c r="L101" s="16">
         <f>SUM(I101:K101)</f>
         <v>450</v>
       </c>
@@ -6076,45 +6128,45 @@
       </c>
     </row>
     <row r="103" spans="1:12" ht="12.75">
-      <c r="A103" s="17">
+      <c r="A103" s="14">
         <v>99</v>
       </c>
-      <c r="B103" s="18" t="s">
+      <c r="B103" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="C103" s="18" t="str">
+      <c r="C103" s="15" t="str">
         <f>'[1]HP Repair Spares'!E6</f>
         <v>Chain with coupling</v>
       </c>
-      <c r="D103" s="18" t="str">
+      <c r="D103" s="15" t="str">
         <f>CONCATENATE(C103," (Code: ",B103,")")</f>
         <v>Chain with coupling (Code: GWDMR099)</v>
       </c>
-      <c r="E103" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F103" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G103" s="19" t="s">
+      <c r="E103" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F103" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G103" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H103" s="19" t="s">
+      <c r="H103" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I103" s="17">
+      <c r="I103" s="14">
         <f>'[1]HP Repair Spares'!F6</f>
         <v>240</v>
       </c>
-      <c r="J103" s="17">
+      <c r="J103" s="14">
         <f>'[1]HP Repair Spares'!G6</f>
         <v>0</v>
       </c>
-      <c r="K103" s="19">
+      <c r="K103" s="16">
         <f>J103*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L103" s="19">
+      <c r="L103" s="16">
         <f>SUM(I103:K103)</f>
         <v>240</v>
       </c>
@@ -6164,45 +6216,45 @@
       </c>
     </row>
     <row r="105" spans="1:12" ht="12.75">
-      <c r="A105" s="17">
+      <c r="A105" s="14">
         <v>101</v>
       </c>
-      <c r="B105" s="18" t="s">
+      <c r="B105" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="C105" s="18" t="str">
+      <c r="C105" s="15" t="str">
         <f>'[1]HP Repair Spares'!E8</f>
         <v>M 12 x 20 Hex Bolt for Top Head Cover</v>
       </c>
-      <c r="D105" s="18" t="str">
+      <c r="D105" s="15" t="str">
         <f>CONCATENATE(C105," (Code: ",B105,")")</f>
         <v>M 12 x 20 Hex Bolt for Top Head Cover (Code: GWDMR101)</v>
       </c>
-      <c r="E105" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F105" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G105" s="19" t="s">
+      <c r="E105" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F105" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G105" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H105" s="19" t="s">
+      <c r="H105" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I105" s="17">
+      <c r="I105" s="14">
         <f>'[1]HP Repair Spares'!F8</f>
         <v>18</v>
       </c>
-      <c r="J105" s="17">
+      <c r="J105" s="14">
         <f>'[1]HP Repair Spares'!G8</f>
         <v>0</v>
       </c>
-      <c r="K105" s="19">
+      <c r="K105" s="16">
         <f>J105*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L105" s="19">
+      <c r="L105" s="16">
         <f>SUM(I105:K105)</f>
         <v>18</v>
       </c>
@@ -6252,45 +6304,45 @@
       </c>
     </row>
     <row r="107" spans="1:12" ht="12.75">
-      <c r="A107" s="17">
+      <c r="A107" s="14">
         <v>103</v>
       </c>
-      <c r="B107" s="18" t="s">
+      <c r="B107" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="C107" s="18" t="str">
+      <c r="C107" s="15" t="str">
         <f>'[1]HP Repair Spares'!E10</f>
         <v>M 12 Nut</v>
       </c>
-      <c r="D107" s="18" t="str">
+      <c r="D107" s="15" t="str">
         <f>CONCATENATE(C107," (Code: ",B107,")")</f>
         <v>M 12 Nut (Code: GWDMR103)</v>
       </c>
-      <c r="E107" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F107" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G107" s="19" t="s">
+      <c r="E107" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F107" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G107" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H107" s="19" t="s">
+      <c r="H107" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I107" s="17">
+      <c r="I107" s="14">
         <f>'[1]HP Repair Spares'!F10</f>
         <v>12</v>
       </c>
-      <c r="J107" s="17">
+      <c r="J107" s="14">
         <f>'[1]HP Repair Spares'!G10</f>
         <v>0</v>
       </c>
-      <c r="K107" s="19">
+      <c r="K107" s="16">
         <f>J107*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L107" s="19">
+      <c r="L107" s="16">
         <f>SUM(I107:K107)</f>
         <v>12</v>
       </c>
@@ -6340,45 +6392,45 @@
       </c>
     </row>
     <row r="109" spans="1:12" ht="12.75">
-      <c r="A109" s="17">
+      <c r="A109" s="14">
         <v>105</v>
       </c>
-      <c r="B109" s="18" t="s">
+      <c r="B109" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="C109" s="18" t="str">
+      <c r="C109" s="15" t="str">
         <f>'[1]HP Repair Spares'!E12</f>
         <v>M 10 x 40 H.T Bolt</v>
       </c>
-      <c r="D109" s="18" t="str">
+      <c r="D109" s="15" t="str">
         <f>CONCATENATE(C109," (Code: ",B109,")")</f>
         <v>M 10 x 40 H.T Bolt (Code: GWDMR105)</v>
       </c>
-      <c r="E109" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F109" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G109" s="19" t="s">
+      <c r="E109" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F109" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G109" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H109" s="19" t="s">
+      <c r="H109" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I109" s="17">
+      <c r="I109" s="14">
         <f>'[1]HP Repair Spares'!F12</f>
         <v>18</v>
       </c>
-      <c r="J109" s="17">
+      <c r="J109" s="14">
         <f>'[1]HP Repair Spares'!G12</f>
         <v>0</v>
       </c>
-      <c r="K109" s="19">
+      <c r="K109" s="16">
         <f>J109*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L109" s="19">
+      <c r="L109" s="16">
         <f>SUM(I109:K109)</f>
         <v>18</v>
       </c>
@@ -6428,45 +6480,45 @@
       </c>
     </row>
     <row r="111" spans="1:12" ht="12.75">
-      <c r="A111" s="17">
+      <c r="A111" s="14">
         <v>107</v>
       </c>
-      <c r="B111" s="18" t="s">
+      <c r="B111" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C111" s="18" t="str">
+      <c r="C111" s="15" t="str">
         <f>'[1]HP Repair Spares'!E14</f>
         <v>Special Washer for Axle</v>
       </c>
-      <c r="D111" s="18" t="str">
+      <c r="D111" s="15" t="str">
         <f>CONCATENATE(C111," (Code: ",B111,")")</f>
         <v>Special Washer for Axle (Code: GWDMR107)</v>
       </c>
-      <c r="E111" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F111" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G111" s="19" t="s">
+      <c r="E111" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F111" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G111" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H111" s="19" t="s">
+      <c r="H111" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I111" s="17">
+      <c r="I111" s="14">
         <f>'[1]HP Repair Spares'!F14</f>
         <v>12</v>
       </c>
-      <c r="J111" s="17">
+      <c r="J111" s="14">
         <f>'[1]HP Repair Spares'!G14</f>
         <v>0</v>
       </c>
-      <c r="K111" s="19">
+      <c r="K111" s="16">
         <f>J111*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L111" s="19">
+      <c r="L111" s="16">
         <f>SUM(I111:K111)</f>
         <v>12</v>
       </c>
@@ -6516,45 +6568,45 @@
       </c>
     </row>
     <row r="113" spans="1:12" ht="12.75">
-      <c r="A113" s="17">
+      <c r="A113" s="14">
         <v>109</v>
       </c>
-      <c r="B113" s="18" t="s">
+      <c r="B113" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="C113" s="18" t="str">
+      <c r="C113" s="15" t="str">
         <f>'[1]HP Repair Spares'!E16</f>
         <v>C.I.Cylinder Body with liner</v>
       </c>
-      <c r="D113" s="18" t="str">
+      <c r="D113" s="15" t="str">
         <f>CONCATENATE(C113," (Code: ",B113,")")</f>
         <v>C.I.Cylinder Body with liner (Code: GWDMR109)</v>
       </c>
-      <c r="E113" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F113" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G113" s="19" t="s">
+      <c r="E113" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F113" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G113" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H113" s="19" t="s">
+      <c r="H113" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I113" s="17">
+      <c r="I113" s="14">
         <f>'[1]HP Repair Spares'!F16</f>
         <v>1080</v>
       </c>
-      <c r="J113" s="17">
+      <c r="J113" s="14">
         <f>'[1]HP Repair Spares'!G16</f>
         <v>0</v>
       </c>
-      <c r="K113" s="19">
+      <c r="K113" s="16">
         <f>J113*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L113" s="19">
+      <c r="L113" s="16">
         <f>SUM(I113:K113)</f>
         <v>1080</v>
       </c>
@@ -6604,45 +6656,45 @@
       </c>
     </row>
     <row r="115" spans="1:12" ht="12.75">
-      <c r="A115" s="17">
+      <c r="A115" s="14">
         <v>111</v>
       </c>
-      <c r="B115" s="18" t="s">
+      <c r="B115" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="C115" s="18" t="str">
+      <c r="C115" s="15" t="str">
         <f>'[1]HP Repair Spares'!E18</f>
         <v>Reducer cap</v>
       </c>
-      <c r="D115" s="18" t="str">
+      <c r="D115" s="15" t="str">
         <f>CONCATENATE(C115," (Code: ",B115,")")</f>
         <v>Reducer cap (Code: GWDMR111)</v>
       </c>
-      <c r="E115" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F115" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G115" s="19" t="s">
+      <c r="E115" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F115" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G115" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H115" s="19" t="s">
+      <c r="H115" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I115" s="17">
+      <c r="I115" s="14">
         <f>'[1]HP Repair Spares'!F18</f>
         <v>156</v>
       </c>
-      <c r="J115" s="17">
+      <c r="J115" s="14">
         <f>'[1]HP Repair Spares'!G18</f>
         <v>0</v>
       </c>
-      <c r="K115" s="19">
+      <c r="K115" s="16">
         <f>J115*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L115" s="19">
+      <c r="L115" s="16">
         <f>SUM(I115:K115)</f>
         <v>156</v>
       </c>
@@ -6692,45 +6744,45 @@
       </c>
     </row>
     <row r="117" spans="1:12" ht="12.75">
-      <c r="A117" s="17">
+      <c r="A117" s="14">
         <v>113</v>
       </c>
-      <c r="B117" s="18" t="s">
+      <c r="B117" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C117" s="18" t="str">
+      <c r="C117" s="15" t="str">
         <f>'[1]HP Repair Spares'!E20</f>
         <v>Spacer</v>
       </c>
-      <c r="D117" s="18" t="str">
+      <c r="D117" s="15" t="str">
         <f>CONCATENATE(C117," (Code: ",B117,")")</f>
         <v>Spacer (Code: GWDMR113)</v>
       </c>
-      <c r="E117" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F117" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G117" s="19" t="s">
+      <c r="E117" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F117" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G117" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H117" s="19" t="s">
+      <c r="H117" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I117" s="17">
+      <c r="I117" s="14">
         <f>'[1]HP Repair Spares'!F20</f>
         <v>228</v>
       </c>
-      <c r="J117" s="17">
+      <c r="J117" s="14">
         <f>'[1]HP Repair Spares'!G20</f>
         <v>0</v>
       </c>
-      <c r="K117" s="19">
+      <c r="K117" s="16">
         <f>J117*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L117" s="19">
+      <c r="L117" s="16">
         <f>SUM(I117:K117)</f>
         <v>228</v>
       </c>
@@ -6780,45 +6832,45 @@
       </c>
     </row>
     <row r="119" spans="1:12" ht="12.75">
-      <c r="A119" s="17">
+      <c r="A119" s="14">
         <v>115</v>
       </c>
-      <c r="B119" s="18" t="s">
+      <c r="B119" s="15" t="s">
         <v>251</v>
       </c>
-      <c r="C119" s="18" t="str">
+      <c r="C119" s="15" t="str">
         <f>'[1]HP Repair Spares'!E22</f>
         <v>Upper Valve ( one piece)</v>
       </c>
-      <c r="D119" s="18" t="str">
+      <c r="D119" s="15" t="str">
         <f>CONCATENATE(C119," (Code: ",B119,")")</f>
         <v>Upper Valve ( one piece) (Code: GWDMR115)</v>
       </c>
-      <c r="E119" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F119" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G119" s="19" t="s">
+      <c r="E119" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F119" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G119" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H119" s="19" t="s">
+      <c r="H119" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I119" s="17">
+      <c r="I119" s="14">
         <f>'[1]HP Repair Spares'!F22</f>
         <v>90</v>
       </c>
-      <c r="J119" s="17">
+      <c r="J119" s="14">
         <f>'[1]HP Repair Spares'!G22</f>
         <v>0</v>
       </c>
-      <c r="K119" s="19">
+      <c r="K119" s="16">
         <f>J119*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L119" s="19">
+      <c r="L119" s="16">
         <f>SUM(I119:K119)</f>
         <v>90</v>
       </c>
@@ -6868,45 +6920,45 @@
       </c>
     </row>
     <row r="121" spans="1:12" ht="12.75">
-      <c r="A121" s="17">
+      <c r="A121" s="14">
         <v>117</v>
       </c>
-      <c r="B121" s="18" t="s">
+      <c r="B121" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="C121" s="18" t="str">
+      <c r="C121" s="15" t="str">
         <f>'[1]HP Repair Spares'!E24</f>
         <v>Check valve seat</v>
       </c>
-      <c r="D121" s="18" t="str">
+      <c r="D121" s="15" t="str">
         <f>CONCATENATE(C121," (Code: ",B121,")")</f>
         <v>Check valve seat (Code: GWDMR117)</v>
       </c>
-      <c r="E121" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F121" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G121" s="19" t="s">
+      <c r="E121" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F121" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G121" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H121" s="19" t="s">
+      <c r="H121" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I121" s="17">
+      <c r="I121" s="14">
         <f>'[1]HP Repair Spares'!F24</f>
         <v>192</v>
       </c>
-      <c r="J121" s="17">
+      <c r="J121" s="14">
         <f>'[1]HP Repair Spares'!G24</f>
         <v>0</v>
       </c>
-      <c r="K121" s="19">
+      <c r="K121" s="16">
         <f>J121*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L121" s="19">
+      <c r="L121" s="16">
         <f>SUM(I121:K121)</f>
         <v>192</v>
       </c>
@@ -6956,45 +7008,45 @@
       </c>
     </row>
     <row r="123" spans="1:12" ht="12.75">
-      <c r="A123" s="17">
+      <c r="A123" s="14">
         <v>119</v>
       </c>
-      <c r="B123" s="18" t="s">
+      <c r="B123" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="C123" s="18" t="str">
+      <c r="C123" s="15" t="str">
         <f>'[1]HP Repair Spares'!E26</f>
         <v>Sealing ring (Nitrile Rubber)</v>
       </c>
-      <c r="D123" s="18" t="str">
+      <c r="D123" s="15" t="str">
         <f>CONCATENATE(C123," (Code: ",B123,")")</f>
         <v>Sealing ring (Nitrile Rubber) (Code: GWDMR119)</v>
       </c>
-      <c r="E123" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F123" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G123" s="19" t="s">
+      <c r="E123" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F123" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G123" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H123" s="19" t="s">
+      <c r="H123" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I123" s="17">
+      <c r="I123" s="14">
         <f>'[1]HP Repair Spares'!F26</f>
         <v>18</v>
       </c>
-      <c r="J123" s="17">
+      <c r="J123" s="14">
         <f>'[1]HP Repair Spares'!G26</f>
         <v>0</v>
       </c>
-      <c r="K123" s="19">
+      <c r="K123" s="16">
         <f>J123*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L123" s="19">
+      <c r="L123" s="16">
         <f>SUM(I123:K123)</f>
         <v>18</v>
       </c>
@@ -7044,45 +7096,45 @@
       </c>
     </row>
     <row r="125" spans="1:12" ht="12.75">
-      <c r="A125" s="17">
+      <c r="A125" s="14">
         <v>121</v>
       </c>
-      <c r="B125" s="18" t="s">
+      <c r="B125" s="15" t="s">
         <v>257</v>
       </c>
-      <c r="C125" s="18" t="str">
+      <c r="C125" s="15" t="str">
         <f>'[1]HP Repair Spares'!E28</f>
         <v>Rubber seating check valve</v>
       </c>
-      <c r="D125" s="18" t="str">
+      <c r="D125" s="15" t="str">
         <f>CONCATENATE(C125," (Code: ",B125,")")</f>
         <v>Rubber seating check valve (Code: GWDMR121)</v>
       </c>
-      <c r="E125" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F125" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G125" s="19" t="s">
+      <c r="E125" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F125" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G125" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H125" s="19" t="s">
+      <c r="H125" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I125" s="17">
+      <c r="I125" s="14">
         <f>'[1]HP Repair Spares'!F28</f>
         <v>12</v>
       </c>
-      <c r="J125" s="17">
+      <c r="J125" s="14">
         <f>'[1]HP Repair Spares'!G28</f>
         <v>0</v>
       </c>
-      <c r="K125" s="19">
+      <c r="K125" s="16">
         <f>J125*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L125" s="19">
+      <c r="L125" s="16">
         <f>SUM(I125:K125)</f>
         <v>12</v>
       </c>
@@ -7132,45 +7184,45 @@
       </c>
     </row>
     <row r="127" spans="1:12" ht="12.75">
-      <c r="A127" s="17">
+      <c r="A127" s="14">
         <v>123</v>
       </c>
-      <c r="B127" s="18" t="s">
+      <c r="B127" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="C127" s="18" t="str">
+      <c r="C127" s="15" t="str">
         <f>'[1]HP Repair Spares'!E30</f>
         <v>Upper valve Assembly comprising of SS Plunger rod, Plunger Yoke body, 2 spacer &amp; 2 bucket washers</v>
       </c>
-      <c r="D127" s="18" t="str">
+      <c r="D127" s="15" t="str">
         <f>CONCATENATE(C127," (Code: ",B127,")")</f>
         <v>Upper valve Assembly comprising of SS Plunger rod, Plunger Yoke body, 2 spacer &amp; 2 bucket washers (Code: GWDMR123)</v>
       </c>
-      <c r="E127" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F127" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G127" s="19" t="s">
+      <c r="E127" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F127" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G127" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H127" s="19" t="s">
+      <c r="H127" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I127" s="17">
+      <c r="I127" s="14">
         <f>'[1]HP Repair Spares'!F30</f>
         <v>1200</v>
       </c>
-      <c r="J127" s="17">
+      <c r="J127" s="14">
         <f>'[1]HP Repair Spares'!G30</f>
         <v>0</v>
       </c>
-      <c r="K127" s="19">
+      <c r="K127" s="16">
         <f>J127*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L127" s="19">
+      <c r="L127" s="16">
         <f>SUM(I127:K127)</f>
         <v>1200</v>
       </c>
@@ -7220,45 +7272,45 @@
       </c>
     </row>
     <row r="129" spans="1:12" ht="12.75">
-      <c r="A129" s="17">
+      <c r="A129" s="14">
         <v>125</v>
       </c>
-      <c r="B129" s="18" t="s">
+      <c r="B129" s="15" t="s">
         <v>261</v>
       </c>
-      <c r="C129" s="18" t="str">
+      <c r="C129" s="15" t="str">
         <f>'[1]HP Repair Spares'!E32</f>
         <v>Lower Valve Assembly comprising of Rubber Seat Retainer, Check valve guide and rubber seating</v>
       </c>
-      <c r="D129" s="18" t="str">
+      <c r="D129" s="15" t="str">
         <f>CONCATENATE(C129," (Code: ",B129,")")</f>
         <v>Lower Valve Assembly comprising of Rubber Seat Retainer, Check valve guide and rubber seating (Code: GWDMR125)</v>
       </c>
-      <c r="E129" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F129" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G129" s="19" t="s">
+      <c r="E129" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F129" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G129" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H129" s="19" t="s">
+      <c r="H129" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I129" s="17">
+      <c r="I129" s="14">
         <f>'[1]HP Repair Spares'!F32</f>
         <v>540</v>
       </c>
-      <c r="J129" s="17">
+      <c r="J129" s="14">
         <f>'[1]HP Repair Spares'!G32</f>
         <v>0</v>
       </c>
-      <c r="K129" s="19">
+      <c r="K129" s="16">
         <f>J129*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L129" s="19">
+      <c r="L129" s="16">
         <f>SUM(I129:K129)</f>
         <v>540</v>
       </c>
@@ -7308,45 +7360,45 @@
       </c>
     </row>
     <row r="131" spans="1:12" ht="12.75">
-      <c r="A131" s="17">
+      <c r="A131" s="14">
         <v>127</v>
       </c>
-      <c r="B131" s="18" t="s">
+      <c r="B131" s="15" t="s">
         <v>263</v>
       </c>
-      <c r="C131" s="18" t="str">
+      <c r="C131" s="15" t="str">
         <f>'[1]HP Repair Spares'!E34</f>
         <v>Pipe Sockets</v>
       </c>
-      <c r="D131" s="18" t="str">
+      <c r="D131" s="15" t="str">
         <f>CONCATENATE(C131," (Code: ",B131,")")</f>
         <v>Pipe Sockets (Code: GWDMR127)</v>
       </c>
-      <c r="E131" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F131" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G131" s="19" t="s">
+      <c r="E131" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F131" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G131" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H131" s="19" t="s">
+      <c r="H131" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I131" s="17">
+      <c r="I131" s="14">
         <f>'[1]HP Repair Spares'!F34</f>
         <v>120</v>
       </c>
-      <c r="J131" s="17">
+      <c r="J131" s="14">
         <f>'[1]HP Repair Spares'!G34</f>
         <v>0</v>
       </c>
-      <c r="K131" s="19">
+      <c r="K131" s="16">
         <f>J131*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L131" s="19">
+      <c r="L131" s="16">
         <f>SUM(I131:K131)</f>
         <v>120</v>
       </c>
@@ -7396,45 +7448,45 @@
       </c>
     </row>
     <row r="133" spans="1:12" ht="12.75">
-      <c r="A133" s="17">
+      <c r="A133" s="14">
         <v>129</v>
       </c>
-      <c r="B133" s="18" t="s">
+      <c r="B133" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="C133" s="18" t="str">
+      <c r="C133" s="15" t="str">
         <f>'[1]HP Repair Spares'!E36</f>
         <v>12 mm dia x 3 m electro galvanized</v>
       </c>
-      <c r="D133" s="18" t="str">
+      <c r="D133" s="15" t="str">
         <f>CONCATENATE(C133," (Code: ",B133,")")</f>
         <v>12 mm dia x 3 m electro galvanized (Code: GWDMR129)</v>
       </c>
-      <c r="E133" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F133" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G133" s="19" t="s">
+      <c r="E133" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F133" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G133" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H133" s="19" t="s">
+      <c r="H133" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I133" s="17">
+      <c r="I133" s="14">
         <f>'[1]HP Repair Spares'!F36</f>
         <v>336</v>
       </c>
-      <c r="J133" s="17">
+      <c r="J133" s="14">
         <f>'[1]HP Repair Spares'!G36</f>
         <v>0</v>
       </c>
-      <c r="K133" s="19">
+      <c r="K133" s="16">
         <f>J133*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L133" s="19">
+      <c r="L133" s="16">
         <f>SUM(I133:K133)</f>
         <v>336</v>
       </c>
@@ -7484,45 +7536,45 @@
       </c>
     </row>
     <row r="135" spans="1:12" ht="12.75">
-      <c r="A135" s="17">
+      <c r="A135" s="14">
         <v>131</v>
       </c>
-      <c r="B135" s="18" t="s">
+      <c r="B135" s="15" t="s">
         <v>267</v>
       </c>
-      <c r="C135" s="18" t="str">
+      <c r="C135" s="15" t="str">
         <f>'[1]HP Repair Spares'!E38</f>
         <v>Hex. Coupler 12 x 20 mm</v>
       </c>
-      <c r="D135" s="18" t="str">
+      <c r="D135" s="15" t="str">
         <f>CONCATENATE(C135," (Code: ",B135,")")</f>
         <v>Hex. Coupler 12 x 20 mm (Code: GWDMR131)</v>
       </c>
-      <c r="E135" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F135" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G135" s="19" t="s">
+      <c r="E135" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F135" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G135" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H135" s="19" t="s">
+      <c r="H135" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I135" s="17">
+      <c r="I135" s="14">
         <f>'[1]HP Repair Spares'!F38</f>
         <v>24</v>
       </c>
-      <c r="J135" s="17">
+      <c r="J135" s="14">
         <f>'[1]HP Repair Spares'!G38</f>
         <v>0</v>
       </c>
-      <c r="K135" s="19">
+      <c r="K135" s="16">
         <f>J135*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L135" s="19">
+      <c r="L135" s="16">
         <f>SUM(I135:K135)</f>
         <v>24</v>
       </c>
@@ -7564,53 +7616,53 @@
       </c>
       <c r="K136" s="16">
         <f>J136*($L$2-1)</f>
-        <v>124.554644</v>
+        <v>0</v>
       </c>
       <c r="L136" s="16">
         <f>SUM(I136:K136)</f>
-        <v>385.89464400000003</v>
+        <v>261.34</v>
       </c>
     </row>
     <row r="137" spans="1:12" ht="12.75">
-      <c r="A137" s="17">
+      <c r="A137" s="14">
         <v>133</v>
       </c>
-      <c r="B137" s="18" t="s">
+      <c r="B137" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="C137" s="18" t="str">
+      <c r="C137" s="15" t="str">
         <f>'[1]HP Repair Spares'!E40</f>
         <v>Cylinder Extra deep well hand pump</v>
       </c>
-      <c r="D137" s="18" t="str">
+      <c r="D137" s="15" t="str">
         <f>CONCATENATE(C137," (Code: ",B137,")")</f>
         <v>Cylinder Extra deep well hand pump (Code: GWDMR133)</v>
       </c>
-      <c r="E137" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F137" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G137" s="19" t="s">
+      <c r="E137" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F137" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G137" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H137" s="19" t="s">
+      <c r="H137" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I137" s="17">
+      <c r="I137" s="14">
         <f>'[1]HP Repair Spares'!F40</f>
         <v>4320</v>
       </c>
-      <c r="J137" s="17">
+      <c r="J137" s="14">
         <f>'[1]HP Repair Spares'!G40</f>
         <v>0</v>
       </c>
-      <c r="K137" s="19">
+      <c r="K137" s="16">
         <f>J137*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L137" s="19">
+      <c r="L137" s="16">
         <f>SUM(I137:K137)</f>
         <v>4320</v>
       </c>
@@ -7660,45 +7712,45 @@
       </c>
     </row>
     <row r="139" spans="1:12" ht="12.75">
-      <c r="A139" s="17">
+      <c r="A139" s="14">
         <v>135</v>
       </c>
-      <c r="B139" s="18" t="s">
+      <c r="B139" s="15" t="s">
         <v>271</v>
       </c>
-      <c r="C139" s="18" t="str">
+      <c r="C139" s="15" t="str">
         <f>'[1]HP Repair Spares'!E42</f>
         <v>ISI marked India Mark II (Standard) Deep well hand pumps confirming to IS: 15500 (Part II) 2004 complete with 10 Nos. GI pipe (B class) 3m long  32mm bore both end threaded with one end socket and 10 Nos connecting rods</v>
       </c>
-      <c r="D139" s="18" t="str">
+      <c r="D139" s="15" t="str">
         <f>CONCATENATE(C139," (Code: ",B139,")")</f>
         <v>ISI marked India Mark II (Standard) Deep well hand pumps confirming to IS: 15500 (Part II) 2004 complete with 10 Nos. GI pipe (B class) 3m long  32mm bore both end threaded with one end socket and 10 Nos connecting rods (Code: GWDMR135)</v>
       </c>
-      <c r="E139" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F139" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G139" s="19" t="s">
+      <c r="E139" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F139" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G139" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="H139" s="19" t="s">
+      <c r="H139" s="16" t="s">
         <v>230</v>
       </c>
-      <c r="I139" s="17">
+      <c r="I139" s="14">
         <f>'[1]HP Repair Spares'!F42</f>
         <v>31000</v>
       </c>
-      <c r="J139" s="17">
+      <c r="J139" s="14">
         <f>'[1]HP Repair Spares'!G42</f>
         <v>0</v>
       </c>
-      <c r="K139" s="19">
+      <c r="K139" s="16">
         <f>J139*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L139" s="19">
+      <c r="L139" s="16">
         <f>SUM(I139:K139)</f>
         <v>31000</v>
       </c>
@@ -7748,42 +7800,42 @@
       </c>
     </row>
     <row r="141" spans="1:12" ht="12.75">
-      <c r="A141" s="17">
+      <c r="A141" s="14">
         <v>137</v>
       </c>
-      <c r="B141" s="18" t="s">
+      <c r="B141" s="15" t="s">
         <v>273</v>
       </c>
-      <c r="C141" s="18" t="s">
+      <c r="C141" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="D141" s="18" t="str">
+      <c r="D141" s="15" t="str">
         <f>CONCATENATE(C141," (Code: ",B141,")")</f>
         <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 2500-6000 lph, Head 49-17m without Panel Board (Code: GWDMR137)</v>
       </c>
-      <c r="E141" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F141" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G141" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H141" s="19" t="s">
+      <c r="E141" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F141" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G141" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H141" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I141" s="19">
+      <c r="I141" s="16">
         <v>21162.53</v>
       </c>
-      <c r="J141" s="17">
-        <v>0</v>
-      </c>
-      <c r="K141" s="19">
+      <c r="J141" s="14">
+        <v>0</v>
+      </c>
+      <c r="K141" s="16">
         <f>J141*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L141" s="19">
+      <c r="L141" s="16">
         <f>SUM(I141:K141)</f>
         <v>21162.53</v>
       </c>
@@ -7830,42 +7882,42 @@
       </c>
     </row>
     <row r="143" spans="1:12" ht="12.75">
-      <c r="A143" s="17">
+      <c r="A143" s="14">
         <v>139</v>
       </c>
-      <c r="B143" s="18" t="s">
+      <c r="B143" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="C143" s="18" t="s">
+      <c r="C143" s="15" t="s">
         <v>279</v>
       </c>
-      <c r="D143" s="18" t="str">
+      <c r="D143" s="15" t="str">
         <f>CONCATENATE(C143," (Code: ",B143,")")</f>
         <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 1800-4320 lph, Head 65-39m without Panel Board (Code: GWDMR139)</v>
       </c>
-      <c r="E143" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F143" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G143" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H143" s="19" t="s">
+      <c r="E143" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F143" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G143" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H143" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I143" s="19">
+      <c r="I143" s="16">
         <v>21047.772000000001</v>
       </c>
-      <c r="J143" s="17">
-        <v>0</v>
-      </c>
-      <c r="K143" s="19">
+      <c r="J143" s="14">
+        <v>0</v>
+      </c>
+      <c r="K143" s="16">
         <f>J143*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L143" s="19">
+      <c r="L143" s="16">
         <f>SUM(I143:K143)</f>
         <v>21047.772000000001</v>
       </c>
@@ -7912,42 +7964,42 @@
       </c>
     </row>
     <row r="145" spans="1:12" ht="12.75">
-      <c r="A145" s="17">
+      <c r="A145" s="14">
         <v>141</v>
       </c>
-      <c r="B145" s="18" t="s">
+      <c r="B145" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="C145" s="18" t="s">
+      <c r="C145" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="D145" s="18" t="str">
+      <c r="D145" s="15" t="str">
         <f>CONCATENATE(C145," (Code: ",B145,")")</f>
         <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 1080-2880 lph, Head 91-50m without Panel Board (Code: GWDMR141)</v>
       </c>
-      <c r="E145" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F145" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G145" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H145" s="19" t="s">
+      <c r="E145" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F145" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G145" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H145" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I145" s="19">
+      <c r="I145" s="16">
         <v>22498.716</v>
       </c>
-      <c r="J145" s="17">
-        <v>0</v>
-      </c>
-      <c r="K145" s="19">
+      <c r="J145" s="14">
+        <v>0</v>
+      </c>
+      <c r="K145" s="16">
         <f>J145*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L145" s="19">
+      <c r="L145" s="16">
         <f>SUM(I145:K145)</f>
         <v>22498.716</v>
       </c>
@@ -7994,42 +8046,42 @@
       </c>
     </row>
     <row r="147" spans="1:12" ht="12.75">
-      <c r="A147" s="17">
+      <c r="A147" s="14">
         <v>143</v>
       </c>
-      <c r="B147" s="18" t="s">
+      <c r="B147" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="C147" s="18" t="s">
+      <c r="C147" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="D147" s="18" t="str">
+      <c r="D147" s="15" t="str">
         <f>CONCATENATE(C147," (Code: ",B147,")")</f>
         <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 1800-4320 lph, Head 83-52m without Panel Board (Code: GWDMR143)</v>
       </c>
-      <c r="E147" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F147" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G147" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H147" s="19" t="s">
+      <c r="E147" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F147" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G147" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H147" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I147" s="19">
+      <c r="I147" s="16">
         <v>23219.315999999999</v>
       </c>
-      <c r="J147" s="17">
-        <v>0</v>
-      </c>
-      <c r="K147" s="19">
+      <c r="J147" s="14">
+        <v>0</v>
+      </c>
+      <c r="K147" s="16">
         <f>J147*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L147" s="19">
+      <c r="L147" s="16">
         <f>SUM(I147:K147)</f>
         <v>23219.315999999999</v>
       </c>
@@ -8076,42 +8128,42 @@
       </c>
     </row>
     <row r="149" spans="1:12" ht="12.75">
-      <c r="A149" s="17">
+      <c r="A149" s="14">
         <v>145</v>
       </c>
-      <c r="B149" s="18" t="s">
+      <c r="B149" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="C149" s="18" t="s">
+      <c r="C149" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="D149" s="18" t="str">
+      <c r="D149" s="15" t="str">
         <f>CONCATENATE(C149," (Code: ",B149,")")</f>
         <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 500-3000 lph, Head 126-43m without Panel Board (Code: GWDMR145)</v>
       </c>
-      <c r="E149" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F149" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G149" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H149" s="19" t="s">
+      <c r="E149" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F149" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G149" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H149" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I149" s="19">
+      <c r="I149" s="16">
         <v>24159.199999999997</v>
       </c>
-      <c r="J149" s="17">
-        <v>0</v>
-      </c>
-      <c r="K149" s="19">
+      <c r="J149" s="14">
+        <v>0</v>
+      </c>
+      <c r="K149" s="16">
         <f>J149*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L149" s="19">
+      <c r="L149" s="16">
         <f>SUM(I149:K149)</f>
         <v>24159.20</v>
       </c>
@@ -8158,42 +8210,42 @@
       </c>
     </row>
     <row r="151" spans="1:12" ht="12.75">
-      <c r="A151" s="17">
+      <c r="A151" s="14">
         <v>147</v>
       </c>
-      <c r="B151" s="18" t="s">
+      <c r="B151" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="C151" s="18" t="s">
+      <c r="C151" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="D151" s="18" t="str">
+      <c r="D151" s="15" t="str">
         <f>CONCATENATE(C151," (Code: ",B151,")")</f>
         <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 500-3000 lph, Head 148-50m without Panel Board (Code: GWDMR147)</v>
       </c>
-      <c r="E151" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F151" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G151" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H151" s="19" t="s">
+      <c r="E151" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F151" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G151" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H151" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I151" s="19">
+      <c r="I151" s="16">
         <v>27980.534999999996</v>
       </c>
-      <c r="J151" s="17">
-        <v>0</v>
-      </c>
-      <c r="K151" s="19">
+      <c r="J151" s="14">
+        <v>0</v>
+      </c>
+      <c r="K151" s="16">
         <f>J151*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L151" s="19">
+      <c r="L151" s="16">
         <f>SUM(I151:K151)</f>
         <v>27980.535</v>
       </c>
@@ -8240,42 +8292,42 @@
       </c>
     </row>
     <row r="153" spans="1:12" ht="12.75">
-      <c r="A153" s="17">
+      <c r="A153" s="14">
         <v>149</v>
       </c>
-      <c r="B153" s="18" t="s">
+      <c r="B153" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="C153" s="18" t="s">
+      <c r="C153" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="D153" s="18" t="str">
+      <c r="D153" s="15" t="str">
         <f>CONCATENATE(C153," (Code: ",B153,")")</f>
         <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 5200-10600 lph, Head 57-18m without Panel Board (Code: GWDMR149)</v>
       </c>
-      <c r="E153" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F153" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G153" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H153" s="19" t="s">
+      <c r="E153" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F153" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G153" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H153" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I153" s="19">
+      <c r="I153" s="16">
         <v>29176.879999999997</v>
       </c>
-      <c r="J153" s="17">
-        <v>0</v>
-      </c>
-      <c r="K153" s="19">
+      <c r="J153" s="14">
+        <v>0</v>
+      </c>
+      <c r="K153" s="16">
         <f>J153*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L153" s="19">
+      <c r="L153" s="16">
         <f>SUM(I153:K153)</f>
         <v>29176.88</v>
       </c>
@@ -8322,42 +8374,42 @@
       </c>
     </row>
     <row r="155" spans="1:12" ht="12.75">
-      <c r="A155" s="17">
+      <c r="A155" s="14">
         <v>151</v>
       </c>
-      <c r="B155" s="18" t="s">
+      <c r="B155" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="C155" s="18" t="s">
+      <c r="C155" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="D155" s="18" t="str">
+      <c r="D155" s="15" t="str">
         <f>CONCATENATE(C155," (Code: ",B155,")")</f>
         <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 2100-5400 lph, Head 116-33m without Panel Board (Code: GWDMR151)</v>
       </c>
-      <c r="E155" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F155" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G155" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H155" s="19" t="s">
+      <c r="E155" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F155" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G155" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H155" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I155" s="19">
+      <c r="I155" s="16">
         <v>29037.499999999996</v>
       </c>
-      <c r="J155" s="17">
-        <v>0</v>
-      </c>
-      <c r="K155" s="19">
+      <c r="J155" s="14">
+        <v>0</v>
+      </c>
+      <c r="K155" s="16">
         <f>J155*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L155" s="19">
+      <c r="L155" s="16">
         <f>SUM(I155:K155)</f>
         <v>29037.50</v>
       </c>
@@ -8404,42 +8456,42 @@
       </c>
     </row>
     <row r="157" spans="1:12" ht="12.75">
-      <c r="A157" s="17">
+      <c r="A157" s="14">
         <v>153</v>
       </c>
-      <c r="B157" s="18" t="s">
+      <c r="B157" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="C157" s="18" t="s">
+      <c r="C157" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="D157" s="18" t="str">
+      <c r="D157" s="15" t="str">
         <f>CONCATENATE(C157," (Code: ",B157,")")</f>
         <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 500-3000 lph, Head 194-65m without Panel Board (Code: GWDMR153)</v>
       </c>
-      <c r="E157" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F157" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G157" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H157" s="19" t="s">
+      <c r="E157" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F157" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G157" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H157" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I157" s="19">
+      <c r="I157" s="16">
         <v>37864.90</v>
       </c>
-      <c r="J157" s="17">
-        <v>0</v>
-      </c>
-      <c r="K157" s="19">
+      <c r="J157" s="14">
+        <v>0</v>
+      </c>
+      <c r="K157" s="16">
         <f>J157*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L157" s="19">
+      <c r="L157" s="16">
         <f>SUM(I157:K157)</f>
         <v>37864.90</v>
       </c>
@@ -8486,42 +8538,42 @@
       </c>
     </row>
     <row r="159" spans="1:12" ht="12.75">
-      <c r="A159" s="17">
+      <c r="A159" s="14">
         <v>155</v>
       </c>
-      <c r="B159" s="18" t="s">
+      <c r="B159" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="C159" s="18" t="s">
+      <c r="C159" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="D159" s="18" t="str">
+      <c r="D159" s="15" t="str">
         <f>CONCATENATE(C159," (Code: ",B159,")")</f>
         <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 500-1800 lph, Head 247-104m without Panel Board (Code: GWDMR155)</v>
       </c>
-      <c r="E159" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F159" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G159" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H159" s="19" t="s">
+      <c r="E159" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F159" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G159" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H159" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I159" s="19">
+      <c r="I159" s="16">
         <v>47333.447999999997</v>
       </c>
-      <c r="J159" s="17">
-        <v>0</v>
-      </c>
-      <c r="K159" s="19">
+      <c r="J159" s="14">
+        <v>0</v>
+      </c>
+      <c r="K159" s="16">
         <f>J159*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L159" s="19">
+      <c r="L159" s="16">
         <f>SUM(I159:K159)</f>
         <v>47333.447999999997</v>
       </c>
@@ -8568,42 +8620,42 @@
       </c>
     </row>
     <row r="161" spans="1:12" ht="12.75">
-      <c r="A161" s="17">
+      <c r="A161" s="14">
         <v>157</v>
       </c>
-      <c r="B161" s="18" t="s">
+      <c r="B161" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="C161" s="18" t="s">
+      <c r="C161" s="15" t="s">
         <v>315</v>
       </c>
-      <c r="D161" s="18" t="str">
+      <c r="D161" s="15" t="str">
         <f>CONCATENATE(C161," (Code: ",B161,")")</f>
         <v>Supply of Single Phase Submersible Pump 3 HP, Discharge 3240-7200 lph, Head 110-42m without Panel Board (Code: GWDMR157)</v>
       </c>
-      <c r="E161" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F161" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G161" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H161" s="19" t="s">
+      <c r="E161" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F161" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G161" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H161" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I161" s="19">
+      <c r="I161" s="16">
         <v>37138.962500000001</v>
       </c>
-      <c r="J161" s="17">
-        <v>0</v>
-      </c>
-      <c r="K161" s="19">
+      <c r="J161" s="14">
+        <v>0</v>
+      </c>
+      <c r="K161" s="16">
         <f>J161*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L161" s="19">
+      <c r="L161" s="16">
         <f>SUM(I161:K161)</f>
         <v>37138.962500000001</v>
       </c>
@@ -8650,42 +8702,42 @@
       </c>
     </row>
     <row r="163" spans="1:12" ht="12.75">
-      <c r="A163" s="17">
+      <c r="A163" s="14">
         <v>159</v>
       </c>
-      <c r="B163" s="18" t="s">
+      <c r="B163" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="C163" s="18" t="s">
+      <c r="C163" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="D163" s="18" t="str">
+      <c r="D163" s="15" t="str">
         <f>CONCATENATE(C163," (Code: ",B163,")")</f>
         <v>Supply of Single Phase Submersible Pump 5 HP, Discharge 4320-10080 lph, Head 150-82m without Panel Board (Code: GWDMR159)</v>
       </c>
-      <c r="E163" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F163" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G163" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H163" s="19" t="s">
+      <c r="E163" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F163" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G163" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H163" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I163" s="19">
+      <c r="I163" s="16">
         <v>45301.984499999999</v>
       </c>
-      <c r="J163" s="17">
-        <v>0</v>
-      </c>
-      <c r="K163" s="19">
+      <c r="J163" s="14">
+        <v>0</v>
+      </c>
+      <c r="K163" s="16">
         <f>J163*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L163" s="19">
+      <c r="L163" s="16">
         <f>SUM(I163:K163)</f>
         <v>45301.984499999999</v>
       </c>
@@ -8732,42 +8784,42 @@
       </c>
     </row>
     <row r="165" spans="1:12" ht="12.75">
-      <c r="A165" s="17">
+      <c r="A165" s="14">
         <v>161</v>
       </c>
-      <c r="B165" s="18" t="s">
+      <c r="B165" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="C165" s="18" t="s">
+      <c r="C165" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="D165" s="18" t="str">
+      <c r="D165" s="15" t="str">
         <f>CONCATENATE(C165," (Code: ",B165,")")</f>
         <v>Supply of Three Phase Submersible Pump 10 HP, Discharge 6000-18000 lph, Head 146-90m without Panel Board (Code: GWDMR161)</v>
       </c>
-      <c r="E165" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F165" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G165" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H165" s="19" t="s">
+      <c r="E165" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F165" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G165" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H165" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I165" s="19">
+      <c r="I165" s="16">
         <v>74549.715999999986</v>
       </c>
-      <c r="J165" s="17">
-        <v>0</v>
-      </c>
-      <c r="K165" s="19">
+      <c r="J165" s="14">
+        <v>0</v>
+      </c>
+      <c r="K165" s="16">
         <f>J165*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L165" s="19">
+      <c r="L165" s="16">
         <f>SUM(I165:K165)</f>
         <v>74549.716</v>
       </c>
@@ -8814,42 +8866,42 @@
       </c>
     </row>
     <row r="167" spans="1:12" ht="12.75">
-      <c r="A167" s="17">
+      <c r="A167" s="14">
         <v>163</v>
       </c>
-      <c r="B167" s="18" t="s">
+      <c r="B167" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="C167" s="18" t="s">
+      <c r="C167" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="D167" s="18" t="str">
+      <c r="D167" s="15" t="str">
         <f>CONCATENATE(C167," (Code: ",B167,")")</f>
         <v>Supply of Three Phase Submersible Pump 10 HP, Discharge 5000-14000 lph, Head 205-110m without Panel Board (Code: GWDMR163)</v>
       </c>
-      <c r="E167" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F167" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G167" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H167" s="19" t="s">
+      <c r="E167" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F167" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G167" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H167" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I167" s="19">
+      <c r="I167" s="16">
         <v>93543.725499999986</v>
       </c>
-      <c r="J167" s="17">
-        <v>0</v>
-      </c>
-      <c r="K167" s="19">
+      <c r="J167" s="14">
+        <v>0</v>
+      </c>
+      <c r="K167" s="16">
         <f>J167*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L167" s="19">
+      <c r="L167" s="16">
         <f>SUM(I167:K167)</f>
         <v>93543.7255</v>
       </c>
@@ -8896,42 +8948,42 @@
       </c>
     </row>
     <row r="169" spans="1:12" ht="12.75">
-      <c r="A169" s="17">
+      <c r="A169" s="14">
         <v>165</v>
       </c>
-      <c r="B169" s="18" t="s">
+      <c r="B169" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="C169" s="18" t="s">
+      <c r="C169" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="D169" s="18" t="str">
+      <c r="D169" s="15" t="str">
         <f>CONCATENATE(C169," (Code: ",B169,")")</f>
         <v>Supply of Three Phase Submersible Pump 12.5 HP, Discharge 3600-25200 lph, Head 157-41m without Panel Board (Code: GWDMR165)</v>
       </c>
-      <c r="E169" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F169" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G169" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H169" s="19" t="s">
+      <c r="E169" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F169" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G169" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H169" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I169" s="19">
+      <c r="I169" s="16">
         <v>77646.274999999994</v>
       </c>
-      <c r="J169" s="17">
-        <v>0</v>
-      </c>
-      <c r="K169" s="19">
+      <c r="J169" s="14">
+        <v>0</v>
+      </c>
+      <c r="K169" s="16">
         <f>J169*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L169" s="19">
+      <c r="L169" s="16">
         <f>SUM(I169:K169)</f>
         <v>77646.274999999994</v>
       </c>
@@ -8978,42 +9030,42 @@
       </c>
     </row>
     <row r="171" spans="1:12" ht="12.75">
-      <c r="A171" s="17">
+      <c r="A171" s="14">
         <v>167</v>
       </c>
-      <c r="B171" s="18" t="s">
+      <c r="B171" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="C171" s="18" t="s">
+      <c r="C171" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="D171" s="18" t="str">
+      <c r="D171" s="15" t="str">
         <f>CONCATENATE(C171," (Code: ",B171,")")</f>
         <v>Supply of Three Phase Submersible Pump 12.5 HP, Discharge 5000-14000 lph, Head 242-129m without Panel Board (Code: GWDMR167)</v>
       </c>
-      <c r="E171" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F171" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G171" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H171" s="19" t="s">
+      <c r="E171" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F171" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G171" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H171" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I171" s="19">
+      <c r="I171" s="16">
         <v>103464.09699999999</v>
       </c>
-      <c r="J171" s="17">
-        <v>0</v>
-      </c>
-      <c r="K171" s="19">
+      <c r="J171" s="14">
+        <v>0</v>
+      </c>
+      <c r="K171" s="16">
         <f>J171*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L171" s="19">
+      <c r="L171" s="16">
         <f>SUM(I171:K171)</f>
         <v>103464.09699999999</v>
       </c>
@@ -9060,42 +9112,42 @@
       </c>
     </row>
     <row r="173" spans="1:12" ht="12.75">
-      <c r="A173" s="17">
+      <c r="A173" s="14">
         <v>169</v>
       </c>
-      <c r="B173" s="18" t="s">
+      <c r="B173" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="C173" s="18" t="s">
+      <c r="C173" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="D173" s="18" t="str">
+      <c r="D173" s="15" t="str">
         <f>CONCATENATE(C173," (Code: ",B173,")")</f>
         <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 5200-10600 lph, Head 86-27m without Panel Board (Code: GWDMR169)</v>
       </c>
-      <c r="E173" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F173" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G173" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H173" s="19" t="s">
+      <c r="E173" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F173" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G173" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H173" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I173" s="19">
+      <c r="I173" s="16">
         <v>33242.13</v>
       </c>
-      <c r="J173" s="17">
-        <v>0</v>
-      </c>
-      <c r="K173" s="19">
+      <c r="J173" s="14">
+        <v>0</v>
+      </c>
+      <c r="K173" s="16">
         <f>J173*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L173" s="19">
+      <c r="L173" s="16">
         <f>SUM(I173:K173)</f>
         <v>33242.13</v>
       </c>
@@ -9142,42 +9194,42 @@
       </c>
     </row>
     <row r="175" spans="1:12" ht="12.75">
-      <c r="A175" s="17">
+      <c r="A175" s="14">
         <v>171</v>
       </c>
-      <c r="B175" s="18" t="s">
+      <c r="B175" s="15" t="s">
         <v>342</v>
       </c>
-      <c r="C175" s="18" t="s">
+      <c r="C175" s="15" t="s">
         <v>343</v>
       </c>
-      <c r="D175" s="18" t="str">
+      <c r="D175" s="15" t="str">
         <f>CONCATENATE(C175," (Code: ",B175,")")</f>
         <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 2500-6000 lph, Head 147-51m without Panel Board (Code: GWDMR171)</v>
       </c>
-      <c r="E175" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F175" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G175" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H175" s="19" t="s">
+      <c r="E175" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F175" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G175" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H175" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I175" s="19">
+      <c r="I175" s="16">
         <v>40652.50</v>
       </c>
-      <c r="J175" s="17">
-        <v>0</v>
-      </c>
-      <c r="K175" s="19">
+      <c r="J175" s="14">
+        <v>0</v>
+      </c>
+      <c r="K175" s="16">
         <f>J175*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L175" s="19">
+      <c r="L175" s="16">
         <f>SUM(I175:K175)</f>
         <v>40652.50</v>
       </c>
@@ -9224,42 +9276,42 @@
       </c>
     </row>
     <row r="177" spans="1:12" ht="12.75">
-      <c r="A177" s="17">
+      <c r="A177" s="14">
         <v>173</v>
       </c>
-      <c r="B177" s="18" t="s">
+      <c r="B177" s="15" t="s">
         <v>346</v>
       </c>
-      <c r="C177" s="18" t="s">
+      <c r="C177" s="15" t="s">
         <v>347</v>
       </c>
-      <c r="D177" s="18" t="str">
+      <c r="D177" s="15" t="str">
         <f>CONCATENATE(C177," (Code: ",B177,")")</f>
         <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 1200-2800 lph, Head 184-86m without Panel Board (Code: GWDMR173)</v>
       </c>
-      <c r="E177" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F177" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G177" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H177" s="19" t="s">
+      <c r="E177" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F177" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G177" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H177" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I177" s="19">
+      <c r="I177" s="16">
         <v>38391.059499999996</v>
       </c>
-      <c r="J177" s="17">
-        <v>0</v>
-      </c>
-      <c r="K177" s="19">
+      <c r="J177" s="14">
+        <v>0</v>
+      </c>
+      <c r="K177" s="16">
         <f>J177*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L177" s="19">
+      <c r="L177" s="16">
         <f>SUM(I177:K177)</f>
         <v>38391.059500000003</v>
       </c>
@@ -9306,42 +9358,42 @@
       </c>
     </row>
     <row r="179" spans="1:12" ht="12.75">
-      <c r="A179" s="17">
+      <c r="A179" s="14">
         <v>175</v>
       </c>
-      <c r="B179" s="18" t="s">
+      <c r="B179" s="15" t="s">
         <v>350</v>
       </c>
-      <c r="C179" s="18" t="s">
+      <c r="C179" s="15" t="s">
         <v>351</v>
       </c>
-      <c r="D179" s="18" t="str">
+      <c r="D179" s="15" t="str">
         <f>CONCATENATE(C179," (Code: ",B179,")")</f>
         <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 1200-2800 lph, Head 245-98m without Panel Board (Code: GWDMR175)</v>
       </c>
-      <c r="E179" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F179" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G179" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H179" s="19" t="s">
+      <c r="E179" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F179" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G179" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H179" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I179" s="19">
+      <c r="I179" s="16">
         <v>53114.233500000002</v>
       </c>
-      <c r="J179" s="17">
-        <v>0</v>
-      </c>
-      <c r="K179" s="19">
+      <c r="J179" s="14">
+        <v>0</v>
+      </c>
+      <c r="K179" s="16">
         <f>J179*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L179" s="19">
+      <c r="L179" s="16">
         <f>SUM(I179:K179)</f>
         <v>53114.233500000002</v>
       </c>
@@ -9388,42 +9440,42 @@
       </c>
     </row>
     <row r="181" spans="1:12" ht="12.75">
-      <c r="A181" s="17">
+      <c r="A181" s="14">
         <v>177</v>
       </c>
-      <c r="B181" s="18" t="s">
+      <c r="B181" s="15" t="s">
         <v>354</v>
       </c>
-      <c r="C181" s="18" t="s">
+      <c r="C181" s="15" t="s">
         <v>355</v>
       </c>
-      <c r="D181" s="18" t="str">
+      <c r="D181" s="15" t="str">
         <f>CONCATENATE(C181," (Code: ",B181,")")</f>
         <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 7200-15000 lph, Head 78-41m without Panel Board (Code: GWDMR177)</v>
       </c>
-      <c r="E181" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F181" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G181" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H181" s="19" t="s">
+      <c r="E181" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F181" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G181" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H181" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I181" s="19">
+      <c r="I181" s="16">
         <v>55751.999999999993</v>
       </c>
-      <c r="J181" s="17">
-        <v>0</v>
-      </c>
-      <c r="K181" s="19">
+      <c r="J181" s="14">
+        <v>0</v>
+      </c>
+      <c r="K181" s="16">
         <f>J181*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L181" s="19">
+      <c r="L181" s="16">
         <f>SUM(I181:K181)</f>
         <v>55752</v>
       </c>
@@ -9470,42 +9522,42 @@
       </c>
     </row>
     <row r="183" spans="1:12" ht="12.75">
-      <c r="A183" s="17">
+      <c r="A183" s="14">
         <v>179</v>
       </c>
-      <c r="B183" s="18" t="s">
+      <c r="B183" s="15" t="s">
         <v>358</v>
       </c>
-      <c r="C183" s="18" t="s">
+      <c r="C183" s="15" t="s">
         <v>359</v>
       </c>
-      <c r="D183" s="18" t="str">
+      <c r="D183" s="15" t="str">
         <f>CONCATENATE(C183," (Code: ",B183,")")</f>
         <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 5000-14000 lph, Head 102-55m without Panel Board (Code: GWDMR179)</v>
       </c>
-      <c r="E183" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F183" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G183" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H183" s="19" t="s">
+      <c r="E183" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F183" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G183" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H183" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I183" s="19">
+      <c r="I183" s="16">
         <v>63505.01249999999</v>
       </c>
-      <c r="J183" s="17">
-        <v>0</v>
-      </c>
-      <c r="K183" s="19">
+      <c r="J183" s="14">
+        <v>0</v>
+      </c>
+      <c r="K183" s="16">
         <f>J183*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L183" s="19">
+      <c r="L183" s="16">
         <f>SUM(I183:K183)</f>
         <v>63505.012499999997</v>
       </c>
@@ -9552,42 +9604,42 @@
       </c>
     </row>
     <row r="185" spans="1:12" ht="12.75">
-      <c r="A185" s="17">
+      <c r="A185" s="14">
         <v>181</v>
       </c>
-      <c r="B185" s="18" t="s">
+      <c r="B185" s="15" t="s">
         <v>362</v>
       </c>
-      <c r="C185" s="18" t="s">
+      <c r="C185" s="15" t="s">
         <v>363</v>
       </c>
-      <c r="D185" s="18" t="str">
+      <c r="D185" s="15" t="str">
         <f>CONCATENATE(C185," (Code: ",B185,")")</f>
         <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 3000-9000 lph, Head 140-72m without Panel Board (Code: GWDMR181)</v>
       </c>
-      <c r="E185" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F185" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G185" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H185" s="19" t="s">
+      <c r="E185" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F185" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G185" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H185" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I185" s="19">
+      <c r="I185" s="16">
         <v>65052.130499999999</v>
       </c>
-      <c r="J185" s="17">
-        <v>0</v>
-      </c>
-      <c r="K185" s="19">
+      <c r="J185" s="14">
+        <v>0</v>
+      </c>
+      <c r="K185" s="16">
         <f>J185*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L185" s="19">
+      <c r="L185" s="16">
         <f>SUM(I185:K185)</f>
         <v>65052.130499999999</v>
       </c>
@@ -9634,42 +9686,42 @@
       </c>
     </row>
     <row r="187" spans="1:12" ht="12.75">
-      <c r="A187" s="17">
+      <c r="A187" s="14">
         <v>183</v>
       </c>
-      <c r="B187" s="18" t="s">
+      <c r="B187" s="15" t="s">
         <v>366</v>
       </c>
-      <c r="C187" s="18" t="s">
+      <c r="C187" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="D187" s="18" t="str">
+      <c r="D187" s="15" t="str">
         <f>CONCATENATE(C187," (Code: ",B187,")")</f>
         <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 2000-6000 lph, Head 195-120m without Panel Board (Code: GWDMR183)</v>
       </c>
-      <c r="E187" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F187" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G187" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H187" s="19" t="s">
+      <c r="E187" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F187" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G187" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H187" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I187" s="19">
+      <c r="I187" s="16">
         <v>56820.579999999994</v>
       </c>
-      <c r="J187" s="17">
-        <v>0</v>
-      </c>
-      <c r="K187" s="19">
+      <c r="J187" s="14">
+        <v>0</v>
+      </c>
+      <c r="K187" s="16">
         <f>J187*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L187" s="19">
+      <c r="L187" s="16">
         <f>SUM(I187:K187)</f>
         <v>56820.58</v>
       </c>
@@ -9716,42 +9768,42 @@
       </c>
     </row>
     <row r="189" spans="1:12" ht="12.75">
-      <c r="A189" s="17">
+      <c r="A189" s="14">
         <v>185</v>
       </c>
-      <c r="B189" s="18" t="s">
+      <c r="B189" s="15" t="s">
         <v>370</v>
       </c>
-      <c r="C189" s="18" t="s">
+      <c r="C189" s="15" t="s">
         <v>371</v>
       </c>
-      <c r="D189" s="18" t="str">
+      <c r="D189" s="15" t="str">
         <f>CONCATENATE(C189," (Code: ",B189,")")</f>
         <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 2500-6000 lph, Head 285-70m without Panel Board (Code: GWDMR185)</v>
       </c>
-      <c r="E189" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F189" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G189" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H189" s="19" t="s">
+      <c r="E189" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F189" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G189" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H189" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I189" s="19">
+      <c r="I189" s="16">
         <v>61559.499999999993</v>
       </c>
-      <c r="J189" s="17">
-        <v>0</v>
-      </c>
-      <c r="K189" s="19">
+      <c r="J189" s="14">
+        <v>0</v>
+      </c>
+      <c r="K189" s="16">
         <f>J189*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L189" s="19">
+      <c r="L189" s="16">
         <f>SUM(I189:K189)</f>
         <v>61559.50</v>
       </c>
@@ -9798,42 +9850,42 @@
       </c>
     </row>
     <row r="191" spans="1:12" ht="12.75">
-      <c r="A191" s="17">
+      <c r="A191" s="14">
         <v>187</v>
       </c>
-      <c r="B191" s="18" t="s">
+      <c r="B191" s="15" t="s">
         <v>374</v>
       </c>
-      <c r="C191" s="18" t="s">
+      <c r="C191" s="15" t="s">
         <v>375</v>
       </c>
-      <c r="D191" s="18" t="str">
+      <c r="D191" s="15" t="str">
         <f>CONCATENATE(C191," (Code: ",B191,")")</f>
         <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 12000-30000 lph, Head 74-29m without Panel Board (Code: GWDMR187)</v>
       </c>
-      <c r="E191" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F191" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G191" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H191" s="19" t="s">
+      <c r="E191" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F191" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G191" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H191" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I191" s="19">
+      <c r="I191" s="16">
         <v>61559.499999999993</v>
       </c>
-      <c r="J191" s="17">
-        <v>0</v>
-      </c>
-      <c r="K191" s="19">
+      <c r="J191" s="14">
+        <v>0</v>
+      </c>
+      <c r="K191" s="16">
         <f>J191*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L191" s="19">
+      <c r="L191" s="16">
         <f>SUM(I191:K191)</f>
         <v>61559.50</v>
       </c>
@@ -9880,42 +9932,42 @@
       </c>
     </row>
     <row r="193" spans="1:12" ht="12.75">
-      <c r="A193" s="17">
+      <c r="A193" s="14">
         <v>189</v>
       </c>
-      <c r="B193" s="18" t="s">
+      <c r="B193" s="15" t="s">
         <v>378</v>
       </c>
-      <c r="C193" s="18" t="s">
+      <c r="C193" s="15" t="s">
         <v>379</v>
       </c>
-      <c r="D193" s="18" t="str">
+      <c r="D193" s="15" t="str">
         <f>CONCATENATE(C193," (Code: ",B193,")")</f>
         <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 6000-18000 lph, Head 112-69m without Panel Board (Code: GWDMR189)</v>
       </c>
-      <c r="E193" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F193" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G193" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H193" s="19" t="s">
+      <c r="E193" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F193" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G193" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H193" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I193" s="19">
+      <c r="I193" s="16">
         <v>67216.005000000005</v>
       </c>
-      <c r="J193" s="17">
-        <v>0</v>
-      </c>
-      <c r="K193" s="19">
+      <c r="J193" s="14">
+        <v>0</v>
+      </c>
+      <c r="K193" s="16">
         <f>J193*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L193" s="19">
+      <c r="L193" s="16">
         <f>SUM(I193:K193)</f>
         <v>67216.005000000005</v>
       </c>
@@ -9962,42 +10014,42 @@
       </c>
     </row>
     <row r="195" spans="1:12" ht="12.75">
-      <c r="A195" s="17">
+      <c r="A195" s="14">
         <v>191</v>
       </c>
-      <c r="B195" s="18" t="s">
+      <c r="B195" s="15" t="s">
         <v>382</v>
       </c>
-      <c r="C195" s="18" t="s">
+      <c r="C195" s="15" t="s">
         <v>383</v>
       </c>
-      <c r="D195" s="18" t="str">
+      <c r="D195" s="15" t="str">
         <f>CONCATENATE(C195," (Code: ",B195,")")</f>
         <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 5000-14000 lph, Head 158-85m without Panel Board (Code: GWDMR191)</v>
       </c>
-      <c r="E195" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F195" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G195" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H195" s="19" t="s">
+      <c r="E195" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F195" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G195" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H195" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I195" s="19">
+      <c r="I195" s="16">
         <v>74094.407999999996</v>
       </c>
-      <c r="J195" s="17">
-        <v>0</v>
-      </c>
-      <c r="K195" s="19">
+      <c r="J195" s="14">
+        <v>0</v>
+      </c>
+      <c r="K195" s="16">
         <f>J195*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L195" s="19">
+      <c r="L195" s="16">
         <f>SUM(I195:K195)</f>
         <v>74094.407999999996</v>
       </c>
@@ -10044,44 +10096,85 @@
       </c>
     </row>
     <row r="197" spans="1:12" ht="12.75">
-      <c r="A197" s="17">
+      <c r="A197" s="14">
         <v>193</v>
       </c>
-      <c r="B197" s="18" t="s">
+      <c r="B197" s="15" t="s">
         <v>386</v>
       </c>
-      <c r="C197" s="18" t="s">
+      <c r="C197" s="15" t="s">
         <v>387</v>
       </c>
-      <c r="D197" s="18" t="str">
+      <c r="D197" s="15" t="str">
         <f>CONCATENATE(C197," (Code: ",B197,")")</f>
         <v>32 A DP switch with indicator modular (MR1017) (Code: GWDMR193)</v>
       </c>
-      <c r="E197" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="F197" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="G197" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="H197" s="19" t="s">
+      <c r="E197" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F197" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G197" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H197" s="16" t="s">
         <v>275</v>
       </c>
-      <c r="I197" s="19">
+      <c r="I197" s="16">
         <v>432</v>
       </c>
-      <c r="J197" s="17">
-        <v>0</v>
-      </c>
-      <c r="K197" s="19">
+      <c r="J197" s="14">
+        <v>0</v>
+      </c>
+      <c r="K197" s="16">
         <f>J197*($L$2-1)</f>
         <v>0</v>
       </c>
-      <c r="L197" s="19">
+      <c r="L197" s="16">
         <f>SUM(I197:K197)</f>
         <v>432</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" ht="12.75">
+      <c r="A198" s="14">
+        <v>194</v>
+      </c>
+      <c r="B198" s="15" t="s">
+        <v>388</v>
+      </c>
+      <c r="C198" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="D198" s="15" t="str">
+        <f>CONCATENATE(C198," (Code: ",B198,")")</f>
+        <v>S&amp;F Digital Timer Switch (Code: GWDMR194)</v>
+      </c>
+      <c r="E198" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F198" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G198" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="H198" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="I198" s="16">
+        <v>6500</v>
+      </c>
+      <c r="J198" s="14">
+        <v>0</v>
+      </c>
+      <c r="K198" s="16">
+        <f>J198*($L$2-1)</f>
+        <v>0</v>
+      </c>
+      <c r="L198" s="16">
+        <f>SUM(I198:K198)</f>
+        <v>6500</v>
       </c>
     </row>
   </sheetData>
@@ -10096,5 +10189,8 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts>
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/Side Bar Files/GWD Data/GWD MR Abstract.xlsx
+++ b/Side Bar Files/GWD Data/GWD MR Abstract.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="391">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="389">
   <si>
     <t>GWD Revised Market Rates 2025</t>
   </si>
@@ -420,12 +420,6 @@
   </si>
   <si>
     <t>S&amp;F PVC Coupling 50 mm (DG)</t>
-  </si>
-  <si>
-    <t>GWDMR051</t>
-  </si>
-  <si>
-    <t>S&amp;F PVC Coupling 63 mm (DG)</t>
   </si>
   <si>
     <t>GWDMR052</t>
@@ -1238,7 +1232,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1254,6 +1248,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAD1DC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1361,32 +1361,18 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1436,14 +1422,17 @@
     <xf numFmtId="4" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="15" builtinId="5"/>
-    <cellStyle name="Currency" xfId="16" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
-    <cellStyle name="Comma" xfId="18" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
@@ -1573,7 +1562,6 @@
       <sheetName val="GI Works"/>
       <sheetName val="Gravel for TWC"/>
       <sheetName val="Gutter&amp;Clamp"/>
-      <sheetName val="HDPE Pipe PRICE"/>
       <sheetName val="HP Erection and Pullout"/>
       <sheetName val="HP Repair Labour"/>
       <sheetName val="HP Repair Spares"/>
@@ -1593,9 +1581,11 @@
       <sheetName val="PVC Fittings PRICE"/>
       <sheetName val="PVC on Wall (Concealed) PRICE"/>
       <sheetName val="PVC on Wall PRICE"/>
+      <sheetName val="PVC on Wall"/>
+      <sheetName val="PVC wo Trench PRICE"/>
       <sheetName val="PVC wo Trench"/>
+      <sheetName val="PVC With Trench PRICE"/>
       <sheetName val="PVC With Trench"/>
-      <sheetName val="PVC With Trench PRICE"/>
       <sheetName val="Scaffolding"/>
       <sheetName val="Services"/>
       <sheetName val="TW Casing Pipes"/>
@@ -1604,6 +1594,9 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
+      <sheetName val="Derived"/>
+      <sheetName val="LMR"/>
+      <sheetName val="PAMR39"/>
       <sheetName val="ZCost Index"/>
     </sheetNames>
     <sheetDataSet>
@@ -1651,13 +1644,17 @@
       <sheetData sheetId="41"/>
       <sheetData sheetId="42"/>
       <sheetData sheetId="43"/>
+      <sheetData sheetId="44"/>
+      <sheetData sheetId="45"/>
+      <sheetData sheetId="46"/>
+      <sheetData sheetId="47"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_2" displayName="Table_2" ref="A3:L198">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table_2" displayName="Table_2" ref="A3:L197">
   <tableColumns count="12">
     <tableColumn id="1" name="Sl No"/>
     <tableColumn id="2" name="Code"/>
@@ -1972,8 +1969,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8272A8AB-D3E8-4EC4-9C8C-E2B6EAA3B9A7}">
-  <dimension ref="A1:L198"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70888093-A0FC-4BA7-ABC4-4853744BBAA6}">
+  <dimension ref="A1:L197"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:12" ht="12.75">
@@ -4048,7 +4045,7 @@
         <v>128</v>
       </c>
       <c r="I52" s="14">
-        <v>18.50</v>
+        <v>9</v>
       </c>
       <c r="J52" s="14">
         <v>28.46</v>
@@ -4059,7 +4056,7 @@
       </c>
       <c r="L52" s="16">
         <f>SUM(I52:K52)</f>
-        <v>46.96</v>
+        <v>37.46</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="12.75">
@@ -4089,7 +4086,7 @@
         <v>128</v>
       </c>
       <c r="I53" s="14">
-        <v>22.50</v>
+        <v>13</v>
       </c>
       <c r="J53" s="14">
         <v>28.46</v>
@@ -4100,7 +4097,7 @@
       </c>
       <c r="L53" s="16">
         <f>SUM(I53:K53)</f>
-        <v>50.96</v>
+        <v>41.46</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="12.75">
@@ -4130,7 +4127,7 @@
         <v>128</v>
       </c>
       <c r="I54" s="14">
-        <v>25.50</v>
+        <v>18</v>
       </c>
       <c r="J54" s="14">
         <v>28.46</v>
@@ -4141,7 +4138,7 @@
       </c>
       <c r="L54" s="16">
         <f>SUM(I54:K54)</f>
-        <v>53.96</v>
+        <v>46.46</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="12.75">
@@ -4156,7 +4153,7 @@
       </c>
       <c r="D55" s="15" t="str">
         <f>CONCATENATE(C55," (Code: ",B55,")")</f>
-        <v>S&amp;F PVC Coupling 63 mm (DG) (Code: GWDMR051)</v>
+        <v>GI Bend 32 mm (Code: GWDMR052)</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>18</v>
@@ -4165,16 +4162,16 @@
         <v>19</v>
       </c>
       <c r="G55" s="16" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="I55" s="14">
-        <v>28.46</v>
+        <v>132</v>
       </c>
       <c r="J55" s="14">
-        <v>29.77</v>
+        <v>0</v>
       </c>
       <c r="K55" s="16">
         <f>J55*($L$2-1)</f>
@@ -4182,7 +4179,7 @@
       </c>
       <c r="L55" s="16">
         <f>SUM(I55:K55)</f>
-        <v>58.23</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="12.75">
@@ -4190,14 +4187,14 @@
         <v>52</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D56" s="15" t="str">
         <f>CONCATENATE(C56," (Code: ",B56,")")</f>
-        <v>GI Bend 32 mm (Code: GWDMR052)</v>
+        <v>GI Bend 40 mm (Code: GWDMR053)</v>
       </c>
       <c r="E56" s="14" t="s">
         <v>18</v>
@@ -4209,10 +4206,10 @@
         <v>97</v>
       </c>
       <c r="H56" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I56" s="14">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="J56" s="14">
         <v>0</v>
@@ -4223,7 +4220,7 @@
       </c>
       <c r="L56" s="16">
         <f>SUM(I56:K56)</f>
-        <v>132</v>
+        <v>162</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="12.75">
@@ -4238,7 +4235,7 @@
       </c>
       <c r="D57" s="15" t="str">
         <f>CONCATENATE(C57," (Code: ",B57,")")</f>
-        <v>GI Bend 40 mm (Code: GWDMR053)</v>
+        <v>GI Bend 50 mm (Code: GWDMR054)</v>
       </c>
       <c r="E57" s="14" t="s">
         <v>18</v>
@@ -4250,10 +4247,10 @@
         <v>97</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I57" s="14">
-        <v>162</v>
+        <v>246</v>
       </c>
       <c r="J57" s="14">
         <v>0</v>
@@ -4264,7 +4261,7 @@
       </c>
       <c r="L57" s="16">
         <f>SUM(I57:K57)</f>
-        <v>162</v>
+        <v>246</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="12.75">
@@ -4279,7 +4276,7 @@
       </c>
       <c r="D58" s="15" t="str">
         <f>CONCATENATE(C58," (Code: ",B58,")")</f>
-        <v>GI Bend 50 mm (Code: GWDMR054)</v>
+        <v>GI Bend 65 mm (Code: GWDMR055)</v>
       </c>
       <c r="E58" s="14" t="s">
         <v>18</v>
@@ -4291,10 +4288,10 @@
         <v>97</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I58" s="14">
-        <v>246</v>
+        <v>414</v>
       </c>
       <c r="J58" s="14">
         <v>0</v>
@@ -4305,7 +4302,7 @@
       </c>
       <c r="L58" s="16">
         <f>SUM(I58:K58)</f>
-        <v>246</v>
+        <v>414</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="12.75">
@@ -4320,7 +4317,7 @@
       </c>
       <c r="D59" s="15" t="str">
         <f>CONCATENATE(C59," (Code: ",B59,")")</f>
-        <v>GI Bend 65 mm (Code: GWDMR055)</v>
+        <v>GI Socket 32 mm (Code: GWDMR056)</v>
       </c>
       <c r="E59" s="14" t="s">
         <v>18</v>
@@ -4332,10 +4329,10 @@
         <v>97</v>
       </c>
       <c r="H59" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I59" s="14">
-        <v>414</v>
+        <v>51.11</v>
       </c>
       <c r="J59" s="14">
         <v>0</v>
@@ -4346,7 +4343,7 @@
       </c>
       <c r="L59" s="16">
         <f>SUM(I59:K59)</f>
-        <v>414</v>
+        <v>51.11</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="12.75">
@@ -4361,7 +4358,7 @@
       </c>
       <c r="D60" s="15" t="str">
         <f>CONCATENATE(C60," (Code: ",B60,")")</f>
-        <v>GI Socket 32 mm (Code: GWDMR056)</v>
+        <v>GI Socket 40 mm (Code: GWDMR057)</v>
       </c>
       <c r="E60" s="14" t="s">
         <v>18</v>
@@ -4373,10 +4370,10 @@
         <v>97</v>
       </c>
       <c r="H60" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I60" s="14">
-        <v>51.11</v>
+        <v>69.69</v>
       </c>
       <c r="J60" s="14">
         <v>0</v>
@@ -4387,7 +4384,7 @@
       </c>
       <c r="L60" s="16">
         <f>SUM(I60:K60)</f>
-        <v>51.11</v>
+        <v>69.69</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="12.75">
@@ -4402,7 +4399,7 @@
       </c>
       <c r="D61" s="15" t="str">
         <f>CONCATENATE(C61," (Code: ",B61,")")</f>
-        <v>GI Socket 40 mm (Code: GWDMR057)</v>
+        <v>GI Socket 50 mm (Code: GWDMR058)</v>
       </c>
       <c r="E61" s="14" t="s">
         <v>18</v>
@@ -4414,10 +4411,10 @@
         <v>97</v>
       </c>
       <c r="H61" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I61" s="14">
-        <v>69.69</v>
+        <v>92.92</v>
       </c>
       <c r="J61" s="14">
         <v>0</v>
@@ -4428,7 +4425,7 @@
       </c>
       <c r="L61" s="16">
         <f>SUM(I61:K61)</f>
-        <v>69.69</v>
+        <v>92.92</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="12.75">
@@ -4443,7 +4440,7 @@
       </c>
       <c r="D62" s="15" t="str">
         <f>CONCATENATE(C62," (Code: ",B62,")")</f>
-        <v>GI Socket 50 mm (Code: GWDMR058)</v>
+        <v>GI Socket 65 mm (Code: GWDMR059)</v>
       </c>
       <c r="E62" s="14" t="s">
         <v>18</v>
@@ -4455,10 +4452,10 @@
         <v>97</v>
       </c>
       <c r="H62" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I62" s="14">
-        <v>92.92</v>
+        <v>127.77</v>
       </c>
       <c r="J62" s="14">
         <v>0</v>
@@ -4469,7 +4466,7 @@
       </c>
       <c r="L62" s="16">
         <f>SUM(I62:K62)</f>
-        <v>92.92</v>
+        <v>127.77</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="12.75">
@@ -4484,7 +4481,7 @@
       </c>
       <c r="D63" s="15" t="str">
         <f>CONCATENATE(C63," (Code: ",B63,")")</f>
-        <v>GI Socket 65 mm (Code: GWDMR059)</v>
+        <v>GI Tee 32 mm (Code: GWDMR060)</v>
       </c>
       <c r="E63" s="14" t="s">
         <v>18</v>
@@ -4496,10 +4493,10 @@
         <v>97</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I63" s="14">
-        <v>127.77</v>
+        <v>150</v>
       </c>
       <c r="J63" s="14">
         <v>0</v>
@@ -4510,7 +4507,7 @@
       </c>
       <c r="L63" s="16">
         <f>SUM(I63:K63)</f>
-        <v>127.77</v>
+        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="12.75">
@@ -4525,7 +4522,7 @@
       </c>
       <c r="D64" s="15" t="str">
         <f>CONCATENATE(C64," (Code: ",B64,")")</f>
-        <v>GI Tee 32 mm (Code: GWDMR060)</v>
+        <v>GI Tee 40 mm (Code: GWDMR061)</v>
       </c>
       <c r="E64" s="14" t="s">
         <v>18</v>
@@ -4537,10 +4534,10 @@
         <v>97</v>
       </c>
       <c r="H64" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I64" s="14">
-        <v>150</v>
+        <v>270</v>
       </c>
       <c r="J64" s="14">
         <v>0</v>
@@ -4551,7 +4548,7 @@
       </c>
       <c r="L64" s="16">
         <f>SUM(I64:K64)</f>
-        <v>150</v>
+        <v>270</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="12.75">
@@ -4566,7 +4563,7 @@
       </c>
       <c r="D65" s="15" t="str">
         <f>CONCATENATE(C65," (Code: ",B65,")")</f>
-        <v>GI Tee 40 mm (Code: GWDMR061)</v>
+        <v>GI Tee 50 mm (Code: GWDMR062)</v>
       </c>
       <c r="E65" s="14" t="s">
         <v>18</v>
@@ -4578,10 +4575,10 @@
         <v>97</v>
       </c>
       <c r="H65" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I65" s="14">
-        <v>270</v>
+        <v>324</v>
       </c>
       <c r="J65" s="14">
         <v>0</v>
@@ -4592,7 +4589,7 @@
       </c>
       <c r="L65" s="16">
         <f>SUM(I65:K65)</f>
-        <v>270</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="12.75">
@@ -4607,7 +4604,7 @@
       </c>
       <c r="D66" s="15" t="str">
         <f>CONCATENATE(C66," (Code: ",B66,")")</f>
-        <v>GI Tee 50 mm (Code: GWDMR062)</v>
+        <v>GI Tee 65 mm (Code: GWDMR063)</v>
       </c>
       <c r="E66" s="14" t="s">
         <v>18</v>
@@ -4619,10 +4616,10 @@
         <v>97</v>
       </c>
       <c r="H66" s="16" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="I66" s="14">
-        <v>324</v>
+        <v>636</v>
       </c>
       <c r="J66" s="14">
         <v>0</v>
@@ -4633,7 +4630,7 @@
       </c>
       <c r="L66" s="16">
         <f>SUM(I66:K66)</f>
-        <v>324</v>
+        <v>636</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="12.75">
@@ -4648,7 +4645,7 @@
       </c>
       <c r="D67" s="15" t="str">
         <f>CONCATENATE(C67," (Code: ",B67,")")</f>
-        <v>GI Tee 65 mm (Code: GWDMR063)</v>
+        <v>Compressor pump 1.5 HP single phase (Code: GWDMR064)</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>18</v>
@@ -4660,10 +4657,10 @@
         <v>97</v>
       </c>
       <c r="H67" s="16" t="s">
-        <v>137</v>
+        <v>160</v>
       </c>
       <c r="I67" s="14">
-        <v>636</v>
+        <v>23970</v>
       </c>
       <c r="J67" s="14">
         <v>0</v>
@@ -4674,7 +4671,7 @@
       </c>
       <c r="L67" s="16">
         <f>SUM(I67:K67)</f>
-        <v>636</v>
+        <v>23970</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="12.75">
@@ -4682,14 +4679,14 @@
         <v>64</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D68" s="15" t="str">
         <f>CONCATENATE(C68," (Code: ",B68,")")</f>
-        <v>Compressor pump 1.5 HP single phase (Code: GWDMR064)</v>
+        <v>Compressor pump 2 HP single phase (Code: GWDMR065)</v>
       </c>
       <c r="E68" s="14" t="s">
         <v>18</v>
@@ -4701,10 +4698,10 @@
         <v>97</v>
       </c>
       <c r="H68" s="16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I68" s="14">
-        <v>23970</v>
+        <v>27540</v>
       </c>
       <c r="J68" s="14">
         <v>0</v>
@@ -4715,7 +4712,7 @@
       </c>
       <c r="L68" s="16">
         <f>SUM(I68:K68)</f>
-        <v>23970</v>
+        <v>27540</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="12.75">
@@ -4730,7 +4727,7 @@
       </c>
       <c r="D69" s="15" t="str">
         <f>CONCATENATE(C69," (Code: ",B69,")")</f>
-        <v>Compressor pump 2 HP single phase (Code: GWDMR065)</v>
+        <v>Compressor pump 5 HP three phase (Code: GWDMR066)</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>18</v>
@@ -4742,10 +4739,10 @@
         <v>97</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I69" s="14">
-        <v>27540</v>
+        <v>38760</v>
       </c>
       <c r="J69" s="14">
         <v>0</v>
@@ -4756,7 +4753,7 @@
       </c>
       <c r="L69" s="16">
         <f>SUM(I69:K69)</f>
-        <v>27540</v>
+        <v>38760</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="12.75">
@@ -4771,7 +4768,7 @@
       </c>
       <c r="D70" s="15" t="str">
         <f>CONCATENATE(C70," (Code: ",B70,")")</f>
-        <v>Compressor pump 5 HP three phase (Code: GWDMR066)</v>
+        <v>Compressor pump 7.5 HP three phase (Code: GWDMR067)</v>
       </c>
       <c r="E70" s="14" t="s">
         <v>18</v>
@@ -4783,10 +4780,10 @@
         <v>97</v>
       </c>
       <c r="H70" s="16" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="I70" s="14">
-        <v>38760</v>
+        <v>51000</v>
       </c>
       <c r="J70" s="14">
         <v>0</v>
@@ -4797,7 +4794,7 @@
       </c>
       <c r="L70" s="16">
         <f>SUM(I70:K70)</f>
-        <v>38760</v>
+        <v>51000</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="12.75">
@@ -4812,10 +4809,10 @@
       </c>
       <c r="D71" s="15" t="str">
         <f>CONCATENATE(C71," (Code: ",B71,")")</f>
-        <v>Compressor pump 7.5 HP three phase (Code: GWDMR067)</v>
+        <v>12 mm thick nylon rope (Code: GWDMR068)</v>
       </c>
       <c r="E71" s="14" t="s">
-        <v>18</v>
+        <v>169</v>
       </c>
       <c r="F71" s="16" t="s">
         <v>19</v>
@@ -4824,10 +4821,10 @@
         <v>97</v>
       </c>
       <c r="H71" s="16" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="I71" s="14">
-        <v>51000</v>
+        <v>38.40</v>
       </c>
       <c r="J71" s="14">
         <v>0</v>
@@ -4838,7 +4835,7 @@
       </c>
       <c r="L71" s="16">
         <f>SUM(I71:K71)</f>
-        <v>51000</v>
+        <v>38.40</v>
       </c>
     </row>
     <row r="72" spans="1:12" ht="12.75">
@@ -4846,17 +4843,17 @@
         <v>68</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D72" s="15" t="str">
         <f>CONCATENATE(C72," (Code: ",B72,")")</f>
-        <v>12 mm thick nylon rope (Code: GWDMR068)</v>
+        <v>14 mm thick nylon rope (Code: GWDMR069)</v>
       </c>
       <c r="E72" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F72" s="16" t="s">
         <v>19</v>
@@ -4865,10 +4862,10 @@
         <v>97</v>
       </c>
       <c r="H72" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I72" s="14">
-        <v>38.40</v>
+        <v>49.20</v>
       </c>
       <c r="J72" s="14">
         <v>0</v>
@@ -4879,7 +4876,7 @@
       </c>
       <c r="L72" s="16">
         <f>SUM(I72:K72)</f>
-        <v>38.40</v>
+        <v>49.20</v>
       </c>
     </row>
     <row r="73" spans="1:12" ht="12.75">
@@ -4894,10 +4891,10 @@
       </c>
       <c r="D73" s="15" t="str">
         <f>CONCATENATE(C73," (Code: ",B73,")")</f>
-        <v>14 mm thick nylon rope (Code: GWDMR069)</v>
+        <v>16 mm thick nylon rope (Code: GWDMR070)</v>
       </c>
       <c r="E73" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F73" s="16" t="s">
         <v>19</v>
@@ -4906,10 +4903,10 @@
         <v>97</v>
       </c>
       <c r="H73" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I73" s="14">
-        <v>49.20</v>
+        <v>56.40</v>
       </c>
       <c r="J73" s="14">
         <v>0</v>
@@ -4920,7 +4917,7 @@
       </c>
       <c r="L73" s="16">
         <f>SUM(I73:K73)</f>
-        <v>49.20</v>
+        <v>56.40</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="12.75">
@@ -4935,10 +4932,10 @@
       </c>
       <c r="D74" s="15" t="str">
         <f>CONCATENATE(C74," (Code: ",B74,")")</f>
-        <v>16 mm thick nylon rope (Code: GWDMR070)</v>
+        <v>Steel rope (Code: GWDMR071)</v>
       </c>
       <c r="E74" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F74" s="16" t="s">
         <v>19</v>
@@ -4947,10 +4944,10 @@
         <v>97</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I74" s="14">
-        <v>56.40</v>
+        <v>114</v>
       </c>
       <c r="J74" s="14">
         <v>0</v>
@@ -4961,7 +4958,7 @@
       </c>
       <c r="L74" s="16">
         <f>SUM(I74:K74)</f>
-        <v>56.40</v>
+        <v>114</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="12.75">
@@ -4976,10 +4973,10 @@
       </c>
       <c r="D75" s="15" t="str">
         <f>CONCATENATE(C75," (Code: ",B75,")")</f>
-        <v>Steel rope (Code: GWDMR071)</v>
+        <v>32 mm dia UPVC pipe (Code: GWDMR072)</v>
       </c>
       <c r="E75" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F75" s="16" t="s">
         <v>19</v>
@@ -4988,10 +4985,10 @@
         <v>97</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I75" s="14">
-        <v>114</v>
+        <v>270</v>
       </c>
       <c r="J75" s="14">
         <v>0</v>
@@ -5002,7 +4999,7 @@
       </c>
       <c r="L75" s="16">
         <f>SUM(I75:K75)</f>
-        <v>114</v>
+        <v>270</v>
       </c>
     </row>
     <row r="76" spans="1:12" ht="12.75">
@@ -5017,10 +5014,10 @@
       </c>
       <c r="D76" s="15" t="str">
         <f>CONCATENATE(C76," (Code: ",B76,")")</f>
-        <v>32 mm dia UPVC pipe (Code: GWDMR072)</v>
+        <v>40 mm dia UPVC pipe (Code: GWDMR073)</v>
       </c>
       <c r="E76" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F76" s="16" t="s">
         <v>19</v>
@@ -5029,10 +5026,10 @@
         <v>97</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I76" s="14">
-        <v>270</v>
+        <v>354</v>
       </c>
       <c r="J76" s="14">
         <v>0</v>
@@ -5043,7 +5040,7 @@
       </c>
       <c r="L76" s="16">
         <f>SUM(I76:K76)</f>
-        <v>270</v>
+        <v>354</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="12.75">
@@ -5058,10 +5055,10 @@
       </c>
       <c r="D77" s="15" t="str">
         <f>CONCATENATE(C77," (Code: ",B77,")")</f>
-        <v>40 mm dia UPVC pipe (Code: GWDMR073)</v>
+        <v>50 mm dia UPVC pipe (Code: GWDMR074)</v>
       </c>
       <c r="E77" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F77" s="16" t="s">
         <v>19</v>
@@ -5070,10 +5067,10 @@
         <v>97</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I77" s="14">
-        <v>354</v>
+        <v>468</v>
       </c>
       <c r="J77" s="14">
         <v>0</v>
@@ -5084,7 +5081,7 @@
       </c>
       <c r="L77" s="16">
         <f>SUM(I77:K77)</f>
-        <v>354</v>
+        <v>468</v>
       </c>
     </row>
     <row r="78" spans="1:12" ht="12.75">
@@ -5099,10 +5096,10 @@
       </c>
       <c r="D78" s="15" t="str">
         <f>CONCATENATE(C78," (Code: ",B78,")")</f>
-        <v>50 mm dia UPVC pipe (Code: GWDMR074)</v>
+        <v>63 mm dia UPVC pipe (Code: GWDMR075)</v>
       </c>
       <c r="E78" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F78" s="16" t="s">
         <v>19</v>
@@ -5111,10 +5108,10 @@
         <v>97</v>
       </c>
       <c r="H78" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I78" s="14">
-        <v>468</v>
+        <v>552</v>
       </c>
       <c r="J78" s="14">
         <v>0</v>
@@ -5125,7 +5122,7 @@
       </c>
       <c r="L78" s="16">
         <f>SUM(I78:K78)</f>
-        <v>468</v>
+        <v>552</v>
       </c>
     </row>
     <row r="79" spans="1:12" ht="12.75">
@@ -5135,15 +5132,15 @@
       <c r="B79" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="C79" s="15" t="s">
+      <c r="C79" s="17" t="s">
         <v>186</v>
       </c>
       <c r="D79" s="15" t="str">
         <f>CONCATENATE(C79," (Code: ",B79,")")</f>
-        <v>63 mm dia UPVC pipe (Code: GWDMR075)</v>
+        <v>20 mm dia HDPE pipe (DG) (8kg) (Code: GWDMR076)</v>
       </c>
       <c r="E79" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F79" s="16" t="s">
         <v>19</v>
@@ -5152,10 +5149,10 @@
         <v>97</v>
       </c>
       <c r="H79" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I79" s="14">
-        <v>552</v>
+        <v>15</v>
       </c>
       <c r="J79" s="14">
         <v>0</v>
@@ -5166,7 +5163,7 @@
       </c>
       <c r="L79" s="16">
         <f>SUM(I79:K79)</f>
-        <v>552</v>
+        <v>15</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="12.75">
@@ -5176,15 +5173,15 @@
       <c r="B80" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="C80" s="15" t="s">
+      <c r="C80" s="17" t="s">
         <v>188</v>
       </c>
       <c r="D80" s="15" t="str">
         <f>CONCATENATE(C80," (Code: ",B80,")")</f>
-        <v>20 mm dia HDPE pipe (DG) (8kg) (Code: GWDMR076)</v>
+        <v>32 mm dia HDPE pipe (DG) (8kg) (Code: GWDMR077)</v>
       </c>
       <c r="E80" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F80" s="16" t="s">
         <v>19</v>
@@ -5193,10 +5190,10 @@
         <v>97</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I80" s="14">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="J80" s="14">
         <v>0</v>
@@ -5207,7 +5204,7 @@
       </c>
       <c r="L80" s="16">
         <f>SUM(I80:K80)</f>
-        <v>15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="81" spans="1:12" ht="12.75">
@@ -5217,15 +5214,15 @@
       <c r="B81" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="C81" s="15" t="s">
+      <c r="C81" s="17" t="s">
         <v>190</v>
       </c>
       <c r="D81" s="15" t="str">
         <f>CONCATENATE(C81," (Code: ",B81,")")</f>
-        <v>32 mm dia HDPE pipe (DG) (8kg) (Code: GWDMR077)</v>
+        <v>40 mm dia HDPE pipe (DG) (8kg) (Code: GWDMR078)</v>
       </c>
       <c r="E81" s="14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F81" s="16" t="s">
         <v>19</v>
@@ -5234,10 +5231,10 @@
         <v>97</v>
       </c>
       <c r="H81" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I81" s="14">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J81" s="14">
         <v>0</v>
@@ -5248,7 +5245,7 @@
       </c>
       <c r="L81" s="16">
         <f>SUM(I81:K81)</f>
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="82" spans="1:12" ht="12.75">
@@ -5263,10 +5260,10 @@
       </c>
       <c r="D82" s="15" t="str">
         <f>CONCATENATE(C82," (Code: ",B82,")")</f>
-        <v>40 mm dia HDPE pipe (DG) (8kg) (Code: GWDMR078)</v>
+        <v>32 mm SS Adapter (Code: GWDMR079)</v>
       </c>
       <c r="E82" s="14" t="s">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="F82" s="16" t="s">
         <v>19</v>
@@ -5275,10 +5272,10 @@
         <v>97</v>
       </c>
       <c r="H82" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I82" s="14">
-        <v>50</v>
+        <v>804</v>
       </c>
       <c r="J82" s="14">
         <v>0</v>
@@ -5289,7 +5286,7 @@
       </c>
       <c r="L82" s="16">
         <f>SUM(I82:K82)</f>
-        <v>50</v>
+        <v>804</v>
       </c>
     </row>
     <row r="83" spans="1:12" ht="12.75">
@@ -5304,7 +5301,7 @@
       </c>
       <c r="D83" s="15" t="str">
         <f>CONCATENATE(C83," (Code: ",B83,")")</f>
-        <v>32 mm SS Adapter (Code: GWDMR079)</v>
+        <v>40 mm SS Adapter (Code: GWDMR080)</v>
       </c>
       <c r="E83" s="14" t="s">
         <v>18</v>
@@ -5316,10 +5313,10 @@
         <v>97</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I83" s="14">
-        <v>804</v>
+        <v>960</v>
       </c>
       <c r="J83" s="14">
         <v>0</v>
@@ -5330,7 +5327,7 @@
       </c>
       <c r="L83" s="16">
         <f>SUM(I83:K83)</f>
-        <v>804</v>
+        <v>960</v>
       </c>
     </row>
     <row r="84" spans="1:12" ht="12.75">
@@ -5345,7 +5342,7 @@
       </c>
       <c r="D84" s="15" t="str">
         <f>CONCATENATE(C84," (Code: ",B84,")")</f>
-        <v>40 mm SS Adapter (Code: GWDMR080)</v>
+        <v>50 mm SS Adapter (Code: GWDMR081)</v>
       </c>
       <c r="E84" s="14" t="s">
         <v>18</v>
@@ -5357,10 +5354,10 @@
         <v>97</v>
       </c>
       <c r="H84" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I84" s="14">
-        <v>960</v>
+        <v>1200</v>
       </c>
       <c r="J84" s="14">
         <v>0</v>
@@ -5371,7 +5368,7 @@
       </c>
       <c r="L84" s="16">
         <f>SUM(I84:K84)</f>
-        <v>960</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="85" spans="1:12" ht="12.75">
@@ -5386,7 +5383,7 @@
       </c>
       <c r="D85" s="15" t="str">
         <f>CONCATENATE(C85," (Code: ",B85,")")</f>
-        <v>50 mm SS Adapter (Code: GWDMR081)</v>
+        <v>50 mm UPVC Union (Code: GWDMR082)</v>
       </c>
       <c r="E85" s="14" t="s">
         <v>18</v>
@@ -5398,10 +5395,10 @@
         <v>97</v>
       </c>
       <c r="H85" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I85" s="14">
-        <v>1200</v>
+        <v>360</v>
       </c>
       <c r="J85" s="14">
         <v>0</v>
@@ -5412,7 +5409,7 @@
       </c>
       <c r="L85" s="16">
         <f>SUM(I85:K85)</f>
-        <v>1200</v>
+        <v>360</v>
       </c>
     </row>
     <row r="86" spans="1:12" ht="12.75">
@@ -5427,7 +5424,7 @@
       </c>
       <c r="D86" s="15" t="str">
         <f>CONCATENATE(C86," (Code: ",B86,")")</f>
-        <v>50 mm UPVC Union (Code: GWDMR082)</v>
+        <v>63 mm UPVC Union (Code: GWDMR083)</v>
       </c>
       <c r="E86" s="14" t="s">
         <v>18</v>
@@ -5439,10 +5436,10 @@
         <v>97</v>
       </c>
       <c r="H86" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I86" s="14">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="J86" s="14">
         <v>0</v>
@@ -5453,7 +5450,7 @@
       </c>
       <c r="L86" s="16">
         <f>SUM(I86:K86)</f>
-        <v>360</v>
+        <v>540</v>
       </c>
     </row>
     <row r="87" spans="1:12" ht="12.75">
@@ -5468,7 +5465,7 @@
       </c>
       <c r="D87" s="15" t="str">
         <f>CONCATENATE(C87," (Code: ",B87,")")</f>
-        <v>63 mm UPVC Union (Code: GWDMR083)</v>
+        <v>75 mm UPVC Union (Code: GWDMR084)</v>
       </c>
       <c r="E87" s="14" t="s">
         <v>18</v>
@@ -5480,10 +5477,10 @@
         <v>97</v>
       </c>
       <c r="H87" s="16" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I87" s="14">
-        <v>540</v>
+        <v>1200</v>
       </c>
       <c r="J87" s="14">
         <v>0</v>
@@ -5494,7 +5491,7 @@
       </c>
       <c r="L87" s="16">
         <f>SUM(I87:K87)</f>
-        <v>540</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="88" spans="1:12" ht="12.75">
@@ -5509,22 +5506,22 @@
       </c>
       <c r="D88" s="15" t="str">
         <f>CONCATENATE(C88," (Code: ",B88,")")</f>
-        <v>75 mm UPVC Union (Code: GWDMR084)</v>
+        <v>Sodium Bentonite (ordinary) (Code: GWDMR085)</v>
       </c>
       <c r="E88" s="14" t="s">
-        <v>18</v>
+        <v>205</v>
       </c>
       <c r="F88" s="16" t="s">
         <v>19</v>
       </c>
       <c r="G88" s="16" t="s">
-        <v>97</v>
+        <v>206</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="I88" s="14">
-        <v>1200</v>
+        <v>7000</v>
       </c>
       <c r="J88" s="14">
         <v>0</v>
@@ -5535,7 +5532,7 @@
       </c>
       <c r="L88" s="16">
         <f>SUM(I88:K88)</f>
-        <v>1200</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="89" spans="1:12" ht="12.75">
@@ -5543,29 +5540,29 @@
         <v>85</v>
       </c>
       <c r="B89" s="15" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C89" s="15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="D89" s="15" t="str">
         <f>CONCATENATE(C89," (Code: ",B89,")")</f>
-        <v>Sodium Bentonite (ordinary) (Code: GWDMR085)</v>
+        <v>Sodium Bentonite (Super) (Code: GWDMR086)</v>
       </c>
       <c r="E89" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="F89" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G89" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="H89" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="F89" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G89" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="H89" s="16" t="s">
-        <v>209</v>
-      </c>
       <c r="I89" s="14">
-        <v>7000</v>
+        <v>13500</v>
       </c>
       <c r="J89" s="14">
         <v>0</v>
@@ -5576,7 +5573,7 @@
       </c>
       <c r="L89" s="16">
         <f>SUM(I89:K89)</f>
-        <v>7000</v>
+        <v>13500</v>
       </c>
     </row>
     <row r="90" spans="1:12" ht="12.75">
@@ -5591,22 +5588,22 @@
       </c>
       <c r="D90" s="15" t="str">
         <f>CONCATENATE(C90," (Code: ",B90,")")</f>
-        <v>Sodium Bentonite (Super) (Code: GWDMR086)</v>
+        <v>MS Casing pipe 450 mm dia, 6 mm thickness (Code: GWDMR087)</v>
       </c>
       <c r="E90" s="14" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="F90" s="16" t="s">
         <v>19</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="H90" s="16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="I90" s="14">
-        <v>13500</v>
+        <v>8450</v>
       </c>
       <c r="J90" s="14">
         <v>0</v>
@@ -5617,7 +5614,7 @@
       </c>
       <c r="L90" s="16">
         <f>SUM(I90:K90)</f>
-        <v>13500</v>
+        <v>8450</v>
       </c>
     </row>
     <row r="91" spans="1:12" ht="12.75">
@@ -5625,29 +5622,29 @@
         <v>87</v>
       </c>
       <c r="B91" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C91" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D91" s="15" t="str">
         <f>CONCATENATE(C91," (Code: ",B91,")")</f>
-        <v>MS Casing pipe 450 mm dia, 6 mm thickness (Code: GWDMR087)</v>
+        <v>Fibre mesh for placing inside filter tank (for recharge schemes) (Code: GWDMR088)</v>
       </c>
       <c r="E91" s="14" t="s">
-        <v>171</v>
+        <v>215</v>
       </c>
       <c r="F91" s="16" t="s">
         <v>19</v>
       </c>
       <c r="G91" s="16" t="s">
-        <v>208</v>
+        <v>35</v>
       </c>
       <c r="H91" s="16" t="s">
-        <v>214</v>
+        <v>36</v>
       </c>
       <c r="I91" s="14">
-        <v>8450</v>
+        <v>180</v>
       </c>
       <c r="J91" s="14">
         <v>0</v>
@@ -5658,7 +5655,7 @@
       </c>
       <c r="L91" s="16">
         <f>SUM(I91:K91)</f>
-        <v>8450</v>
+        <v>180</v>
       </c>
     </row>
     <row r="92" spans="1:12" ht="12.75">
@@ -5666,17 +5663,17 @@
         <v>88</v>
       </c>
       <c r="B92" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C92" s="15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D92" s="15" t="str">
         <f>CONCATENATE(C92," (Code: ",B92,")")</f>
-        <v>Fibre mesh for placing inside filter tank (for recharge schemes) (Code: GWDMR088)</v>
+        <v>Coated mesh for placing inside filter tank (for recharge schemes) (Code: GWDMR089)</v>
       </c>
       <c r="E92" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F92" s="16" t="s">
         <v>19</v>
@@ -5688,7 +5685,7 @@
         <v>36</v>
       </c>
       <c r="I92" s="14">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="J92" s="14">
         <v>0</v>
@@ -5699,7 +5696,7 @@
       </c>
       <c r="L92" s="16">
         <f>SUM(I92:K92)</f>
-        <v>180</v>
+        <v>300</v>
       </c>
     </row>
     <row r="93" spans="1:12" ht="12.75">
@@ -5714,10 +5711,10 @@
       </c>
       <c r="D93" s="15" t="str">
         <f>CONCATENATE(C93," (Code: ",B93,")")</f>
-        <v>Coated mesh for placing inside filter tank (for recharge schemes) (Code: GWDMR089)</v>
+        <v>Sieve mesh 110 mm (inside inspection chamber) (for recharge schemes) (Code: GWDMR090)</v>
       </c>
       <c r="E93" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F93" s="16" t="s">
         <v>19</v>
@@ -5729,7 +5726,7 @@
         <v>36</v>
       </c>
       <c r="I93" s="14">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="J93" s="14">
         <v>0</v>
@@ -5740,7 +5737,7 @@
       </c>
       <c r="L93" s="16">
         <f>SUM(I93:K93)</f>
-        <v>300</v>
+        <v>180</v>
       </c>
     </row>
     <row r="94" spans="1:12" ht="12.75">
@@ -5755,10 +5752,10 @@
       </c>
       <c r="D94" s="15" t="str">
         <f>CONCATENATE(C94," (Code: ",B94,")")</f>
-        <v>Sieve mesh 110 mm (inside inspection chamber) (for recharge schemes) (Code: GWDMR090)</v>
+        <v>Sieve mesh 140 mm (inside inspection chamber) (for recharge schemes) (Code: GWDMR091)</v>
       </c>
       <c r="E94" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F94" s="16" t="s">
         <v>19</v>
@@ -5770,7 +5767,7 @@
         <v>36</v>
       </c>
       <c r="I94" s="14">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="J94" s="14">
         <v>0</v>
@@ -5781,7 +5778,7 @@
       </c>
       <c r="L94" s="16">
         <f>SUM(I94:K94)</f>
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
     <row r="95" spans="1:12" ht="12.75">
@@ -5796,10 +5793,10 @@
       </c>
       <c r="D95" s="15" t="str">
         <f>CONCATENATE(C95," (Code: ",B95,")")</f>
-        <v>Sieve mesh 140 mm (inside inspection chamber) (for recharge schemes) (Code: GWDMR091)</v>
+        <v>Plastic net for covering pipe (for recharge schemes) (Code: GWDMR092)</v>
       </c>
       <c r="E95" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F95" s="16" t="s">
         <v>19</v>
@@ -5811,7 +5808,7 @@
         <v>36</v>
       </c>
       <c r="I95" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="J95" s="14">
         <v>0</v>
@@ -5822,7 +5819,7 @@
       </c>
       <c r="L95" s="16">
         <f>SUM(I95:K95)</f>
-        <v>200</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="12.75">
@@ -5837,22 +5834,22 @@
       </c>
       <c r="D96" s="15" t="str">
         <f>CONCATENATE(C96," (Code: ",B96,")")</f>
-        <v>Plastic net for covering pipe (for recharge schemes) (Code: GWDMR092)</v>
+        <v>PVC Wiring Pipe (Code: GWDMR093)</v>
       </c>
       <c r="E96" s="14" t="s">
-        <v>217</v>
+        <v>169</v>
       </c>
       <c r="F96" s="16" t="s">
         <v>19</v>
       </c>
       <c r="G96" s="16" t="s">
-        <v>35</v>
+        <v>97</v>
       </c>
       <c r="H96" s="16" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I96" s="14">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="J96" s="14">
         <v>0</v>
@@ -5863,7 +5860,7 @@
       </c>
       <c r="L96" s="16">
         <f>SUM(I96:K96)</f>
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97" spans="1:12" ht="12.75">
@@ -5873,29 +5870,32 @@
       <c r="B97" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C97" s="15" t="s">
-        <v>227</v>
+      <c r="C97" s="15" t="str">
+        <f>'[1]HP Repair Spares'!E1</f>
+        <v>Head Assembly complete (with Head, Handle, Ball Bearings and  Chain Assembly)</v>
       </c>
       <c r="D97" s="15" t="str">
         <f>CONCATENATE(C97," (Code: ",B97,")")</f>
-        <v>PVC Wiring Pipe (Code: GWDMR093)</v>
+        <v>Head Assembly complete (with Head, Handle, Ball Bearings and  Chain Assembly) (Code: GWDMR094)</v>
       </c>
       <c r="E97" s="14" t="s">
-        <v>171</v>
+        <v>18</v>
       </c>
       <c r="F97" s="16" t="s">
         <v>19</v>
       </c>
       <c r="G97" s="16" t="s">
-        <v>97</v>
+        <v>227</v>
       </c>
       <c r="H97" s="16" t="s">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="I97" s="14">
-        <v>30</v>
+        <f>'[1]HP Repair Spares'!F1</f>
+        <v>4800</v>
       </c>
       <c r="J97" s="14">
+        <f>'[1]HP Repair Spares'!G1</f>
         <v>0</v>
       </c>
       <c r="K97" s="16">
@@ -5904,7 +5904,7 @@
       </c>
       <c r="L97" s="16">
         <f>SUM(I97:K97)</f>
-        <v>30</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="98" spans="1:12" ht="12.75">
@@ -5912,15 +5912,15 @@
         <v>94</v>
       </c>
       <c r="B98" s="15" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C98" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E1</f>
-        <v>Head Assembly complete (with Head, Handle, Ball Bearings and  Chain Assembly)</v>
+        <f>'[1]HP Repair Spares'!E2</f>
+        <v>Head with welded components only without cover</v>
       </c>
       <c r="D98" s="15" t="str">
         <f>CONCATENATE(C98," (Code: ",B98,")")</f>
-        <v>Head Assembly complete (with Head, Handle, Ball Bearings and  Chain Assembly) (Code: GWDMR094)</v>
+        <v>Head with welded components only without cover (Code: GWDMR095)</v>
       </c>
       <c r="E98" s="14" t="s">
         <v>18</v>
@@ -5929,17 +5929,17 @@
         <v>19</v>
       </c>
       <c r="G98" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H98" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I98" s="14">
-        <f>'[1]HP Repair Spares'!F1</f>
-        <v>4800</v>
+        <f>'[1]HP Repair Spares'!F2</f>
+        <v>2280</v>
       </c>
       <c r="J98" s="14">
-        <f>'[1]HP Repair Spares'!G1</f>
+        <f>'[1]HP Repair Spares'!G2</f>
         <v>0</v>
       </c>
       <c r="K98" s="16">
@@ -5948,7 +5948,7 @@
       </c>
       <c r="L98" s="16">
         <f>SUM(I98:K98)</f>
-        <v>4800</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="99" spans="1:12" ht="12.75">
@@ -5956,15 +5956,15 @@
         <v>95</v>
       </c>
       <c r="B99" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C99" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E2</f>
-        <v>Head with welded components only without cover</v>
+        <f>'[1]HP Repair Spares'!E3</f>
+        <v>Handle (welded components only)</v>
       </c>
       <c r="D99" s="15" t="str">
         <f>CONCATENATE(C99," (Code: ",B99,")")</f>
-        <v>Head with welded components only without cover (Code: GWDMR095)</v>
+        <v>Handle (welded components only) (Code: GWDMR096)</v>
       </c>
       <c r="E99" s="14" t="s">
         <v>18</v>
@@ -5973,17 +5973,17 @@
         <v>19</v>
       </c>
       <c r="G99" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H99" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I99" s="14">
-        <f>'[1]HP Repair Spares'!F2</f>
-        <v>2280</v>
+        <f>'[1]HP Repair Spares'!F3</f>
+        <v>1800</v>
       </c>
       <c r="J99" s="14">
-        <f>'[1]HP Repair Spares'!G2</f>
+        <f>'[1]HP Repair Spares'!G3</f>
         <v>0</v>
       </c>
       <c r="K99" s="16">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="L99" s="16">
         <f>SUM(I99:K99)</f>
-        <v>2280</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="100" spans="1:12" ht="12.75">
@@ -6000,15 +6000,15 @@
         <v>96</v>
       </c>
       <c r="B100" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C100" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E3</f>
-        <v>Handle (welded components only)</v>
+        <f>'[1]HP Repair Spares'!E4</f>
+        <v>Additional Plate</v>
       </c>
       <c r="D100" s="15" t="str">
         <f>CONCATENATE(C100," (Code: ",B100,")")</f>
-        <v>Handle (welded components only) (Code: GWDMR096)</v>
+        <v>Additional Plate (Code: GWDMR097)</v>
       </c>
       <c r="E100" s="14" t="s">
         <v>18</v>
@@ -6017,17 +6017,17 @@
         <v>19</v>
       </c>
       <c r="G100" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H100" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I100" s="14">
-        <f>'[1]HP Repair Spares'!F3</f>
-        <v>1800</v>
+        <f>'[1]HP Repair Spares'!F4</f>
+        <v>450</v>
       </c>
       <c r="J100" s="14">
-        <f>'[1]HP Repair Spares'!G3</f>
+        <f>'[1]HP Repair Spares'!G4</f>
         <v>0</v>
       </c>
       <c r="K100" s="16">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="L100" s="16">
         <f>SUM(I100:K100)</f>
-        <v>1800</v>
+        <v>450</v>
       </c>
     </row>
     <row r="101" spans="1:12" ht="12.75">
@@ -6044,15 +6044,15 @@
         <v>97</v>
       </c>
       <c r="B101" s="15" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C101" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E4</f>
-        <v>Additional Plate</v>
+        <f>'[1]HP Repair Spares'!E5</f>
+        <v>Ball Bearing 6204 Z</v>
       </c>
       <c r="D101" s="15" t="str">
         <f>CONCATENATE(C101," (Code: ",B101,")")</f>
-        <v>Additional Plate (Code: GWDMR097)</v>
+        <v>Ball Bearing 6204 Z (Code: GWDMR098)</v>
       </c>
       <c r="E101" s="14" t="s">
         <v>18</v>
@@ -6061,17 +6061,17 @@
         <v>19</v>
       </c>
       <c r="G101" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H101" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I101" s="14">
-        <f>'[1]HP Repair Spares'!F4</f>
-        <v>450</v>
+        <f>'[1]HP Repair Spares'!F5</f>
+        <v>216</v>
       </c>
       <c r="J101" s="14">
-        <f>'[1]HP Repair Spares'!G4</f>
+        <f>'[1]HP Repair Spares'!G5</f>
         <v>0</v>
       </c>
       <c r="K101" s="16">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="L101" s="16">
         <f>SUM(I101:K101)</f>
-        <v>450</v>
+        <v>216</v>
       </c>
     </row>
     <row r="102" spans="1:12" ht="12.75">
@@ -6088,15 +6088,15 @@
         <v>98</v>
       </c>
       <c r="B102" s="15" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C102" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E5</f>
-        <v>Ball Bearing 6204 Z</v>
+        <f>'[1]HP Repair Spares'!E6</f>
+        <v>Chain with coupling</v>
       </c>
       <c r="D102" s="15" t="str">
         <f>CONCATENATE(C102," (Code: ",B102,")")</f>
-        <v>Ball Bearing 6204 Z (Code: GWDMR098)</v>
+        <v>Chain with coupling (Code: GWDMR099)</v>
       </c>
       <c r="E102" s="14" t="s">
         <v>18</v>
@@ -6105,17 +6105,17 @@
         <v>19</v>
       </c>
       <c r="G102" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H102" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I102" s="14">
-        <f>'[1]HP Repair Spares'!F5</f>
-        <v>216</v>
+        <f>'[1]HP Repair Spares'!F6</f>
+        <v>240</v>
       </c>
       <c r="J102" s="14">
-        <f>'[1]HP Repair Spares'!G5</f>
+        <f>'[1]HP Repair Spares'!G6</f>
         <v>0</v>
       </c>
       <c r="K102" s="16">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="L102" s="16">
         <f>SUM(I102:K102)</f>
-        <v>216</v>
+        <v>240</v>
       </c>
     </row>
     <row r="103" spans="1:12" ht="12.75">
@@ -6132,15 +6132,15 @@
         <v>99</v>
       </c>
       <c r="B103" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C103" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E6</f>
-        <v>Chain with coupling</v>
+        <f>'[1]HP Repair Spares'!E7</f>
+        <v>Spacer for Axle Pin</v>
       </c>
       <c r="D103" s="15" t="str">
         <f>CONCATENATE(C103," (Code: ",B103,")")</f>
-        <v>Chain with coupling (Code: GWDMR099)</v>
+        <v>Spacer for Axle Pin (Code: GWDMR100)</v>
       </c>
       <c r="E103" s="14" t="s">
         <v>18</v>
@@ -6149,17 +6149,17 @@
         <v>19</v>
       </c>
       <c r="G103" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H103" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I103" s="14">
-        <f>'[1]HP Repair Spares'!F6</f>
-        <v>240</v>
+        <f>'[1]HP Repair Spares'!F7</f>
+        <v>24</v>
       </c>
       <c r="J103" s="14">
-        <f>'[1]HP Repair Spares'!G6</f>
+        <f>'[1]HP Repair Spares'!G7</f>
         <v>0</v>
       </c>
       <c r="K103" s="16">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="L103" s="16">
         <f>SUM(I103:K103)</f>
-        <v>240</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="12.75">
@@ -6176,15 +6176,15 @@
         <v>100</v>
       </c>
       <c r="B104" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C104" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E7</f>
-        <v>Spacer for Axle Pin</v>
+        <f>'[1]HP Repair Spares'!E8</f>
+        <v>M 12 x 20 Hex Bolt for Top Head Cover</v>
       </c>
       <c r="D104" s="15" t="str">
         <f>CONCATENATE(C104," (Code: ",B104,")")</f>
-        <v>Spacer for Axle Pin (Code: GWDMR100)</v>
+        <v>M 12 x 20 Hex Bolt for Top Head Cover (Code: GWDMR101)</v>
       </c>
       <c r="E104" s="14" t="s">
         <v>18</v>
@@ -6193,17 +6193,17 @@
         <v>19</v>
       </c>
       <c r="G104" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H104" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I104" s="14">
-        <f>'[1]HP Repair Spares'!F7</f>
-        <v>24</v>
+        <f>'[1]HP Repair Spares'!F8</f>
+        <v>18</v>
       </c>
       <c r="J104" s="14">
-        <f>'[1]HP Repair Spares'!G7</f>
+        <f>'[1]HP Repair Spares'!G8</f>
         <v>0</v>
       </c>
       <c r="K104" s="16">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="L104" s="16">
         <f>SUM(I104:K104)</f>
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="105" spans="1:12" ht="12.75">
@@ -6220,15 +6220,15 @@
         <v>101</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C105" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E8</f>
-        <v>M 12 x 20 Hex Bolt for Top Head Cover</v>
+        <f>'[1]HP Repair Spares'!E9</f>
+        <v>M 12 x 40 Hex Bolt</v>
       </c>
       <c r="D105" s="15" t="str">
         <f>CONCATENATE(C105," (Code: ",B105,")")</f>
-        <v>M 12 x 20 Hex Bolt for Top Head Cover (Code: GWDMR101)</v>
+        <v>M 12 x 40 Hex Bolt (Code: GWDMR102)</v>
       </c>
       <c r="E105" s="14" t="s">
         <v>18</v>
@@ -6237,17 +6237,17 @@
         <v>19</v>
       </c>
       <c r="G105" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H105" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I105" s="14">
-        <f>'[1]HP Repair Spares'!F8</f>
+        <f>'[1]HP Repair Spares'!F9</f>
         <v>18</v>
       </c>
       <c r="J105" s="14">
-        <f>'[1]HP Repair Spares'!G8</f>
+        <f>'[1]HP Repair Spares'!G9</f>
         <v>0</v>
       </c>
       <c r="K105" s="16">
@@ -6264,15 +6264,15 @@
         <v>102</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C106" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E9</f>
-        <v>M 12 x 40 Hex Bolt</v>
+        <f>'[1]HP Repair Spares'!E10</f>
+        <v>M 12 Nut</v>
       </c>
       <c r="D106" s="15" t="str">
         <f>CONCATENATE(C106," (Code: ",B106,")")</f>
-        <v>M 12 x 40 Hex Bolt (Code: GWDMR102)</v>
+        <v>M 12 Nut (Code: GWDMR103)</v>
       </c>
       <c r="E106" s="14" t="s">
         <v>18</v>
@@ -6281,17 +6281,17 @@
         <v>19</v>
       </c>
       <c r="G106" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H106" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I106" s="14">
-        <f>'[1]HP Repair Spares'!F9</f>
-        <v>18</v>
+        <f>'[1]HP Repair Spares'!F10</f>
+        <v>12</v>
       </c>
       <c r="J106" s="14">
-        <f>'[1]HP Repair Spares'!G9</f>
+        <f>'[1]HP Repair Spares'!G10</f>
         <v>0</v>
       </c>
       <c r="K106" s="16">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="L106" s="16">
         <f>SUM(I106:K106)</f>
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107" spans="1:12" ht="12.75">
@@ -6308,15 +6308,15 @@
         <v>103</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C107" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E10</f>
-        <v>M 12 Nut</v>
+        <f>'[1]HP Repair Spares'!E11</f>
+        <v>M.12 Washer</v>
       </c>
       <c r="D107" s="15" t="str">
         <f>CONCATENATE(C107," (Code: ",B107,")")</f>
-        <v>M 12 Nut (Code: GWDMR103)</v>
+        <v>M.12 Washer (Code: GWDMR104)</v>
       </c>
       <c r="E107" s="14" t="s">
         <v>18</v>
@@ -6325,17 +6325,17 @@
         <v>19</v>
       </c>
       <c r="G107" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H107" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I107" s="14">
-        <f>'[1]HP Repair Spares'!F10</f>
+        <f>'[1]HP Repair Spares'!F11</f>
         <v>12</v>
       </c>
       <c r="J107" s="14">
-        <f>'[1]HP Repair Spares'!G10</f>
+        <f>'[1]HP Repair Spares'!G11</f>
         <v>0</v>
       </c>
       <c r="K107" s="16">
@@ -6352,15 +6352,15 @@
         <v>104</v>
       </c>
       <c r="B108" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C108" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E11</f>
-        <v>M.12 Washer</v>
+        <f>'[1]HP Repair Spares'!E12</f>
+        <v>M 10 x 40 H.T Bolt</v>
       </c>
       <c r="D108" s="15" t="str">
         <f>CONCATENATE(C108," (Code: ",B108,")")</f>
-        <v>M.12 Washer (Code: GWDMR104)</v>
+        <v>M 10 x 40 H.T Bolt (Code: GWDMR105)</v>
       </c>
       <c r="E108" s="14" t="s">
         <v>18</v>
@@ -6369,17 +6369,17 @@
         <v>19</v>
       </c>
       <c r="G108" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H108" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I108" s="14">
-        <f>'[1]HP Repair Spares'!F11</f>
-        <v>12</v>
+        <f>'[1]HP Repair Spares'!F12</f>
+        <v>18</v>
       </c>
       <c r="J108" s="14">
-        <f>'[1]HP Repair Spares'!G11</f>
+        <f>'[1]HP Repair Spares'!G12</f>
         <v>0</v>
       </c>
       <c r="K108" s="16">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="L108" s="16">
         <f>SUM(I108:K108)</f>
-        <v>12</v>
+        <v>18</v>
       </c>
     </row>
     <row r="109" spans="1:12" ht="12.75">
@@ -6396,15 +6396,15 @@
         <v>105</v>
       </c>
       <c r="B109" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C109" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E12</f>
-        <v>M 10 x 40 H.T Bolt</v>
+        <f>'[1]HP Repair Spares'!E13</f>
+        <v>M.10 Nylon Nut</v>
       </c>
       <c r="D109" s="15" t="str">
         <f>CONCATENATE(C109," (Code: ",B109,")")</f>
-        <v>M 10 x 40 H.T Bolt (Code: GWDMR105)</v>
+        <v>M.10 Nylon Nut (Code: GWDMR106)</v>
       </c>
       <c r="E109" s="14" t="s">
         <v>18</v>
@@ -6413,17 +6413,17 @@
         <v>19</v>
       </c>
       <c r="G109" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H109" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I109" s="14">
-        <f>'[1]HP Repair Spares'!F12</f>
-        <v>18</v>
+        <f>'[1]HP Repair Spares'!F13</f>
+        <v>12</v>
       </c>
       <c r="J109" s="14">
-        <f>'[1]HP Repair Spares'!G12</f>
+        <f>'[1]HP Repair Spares'!G13</f>
         <v>0</v>
       </c>
       <c r="K109" s="16">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="L109" s="16">
         <f>SUM(I109:K109)</f>
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110" spans="1:12" ht="12.75">
@@ -6440,15 +6440,15 @@
         <v>106</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C110" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E13</f>
-        <v>M.10 Nylon Nut</v>
+        <f>'[1]HP Repair Spares'!E14</f>
+        <v>Special Washer for Axle</v>
       </c>
       <c r="D110" s="15" t="str">
         <f>CONCATENATE(C110," (Code: ",B110,")")</f>
-        <v>M.10 Nylon Nut (Code: GWDMR106)</v>
+        <v>Special Washer for Axle (Code: GWDMR107)</v>
       </c>
       <c r="E110" s="14" t="s">
         <v>18</v>
@@ -6457,17 +6457,17 @@
         <v>19</v>
       </c>
       <c r="G110" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H110" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I110" s="14">
-        <f>'[1]HP Repair Spares'!F13</f>
+        <f>'[1]HP Repair Spares'!F14</f>
         <v>12</v>
       </c>
       <c r="J110" s="14">
-        <f>'[1]HP Repair Spares'!G13</f>
+        <f>'[1]HP Repair Spares'!G14</f>
         <v>0</v>
       </c>
       <c r="K110" s="16">
@@ -6484,15 +6484,15 @@
         <v>107</v>
       </c>
       <c r="B111" s="15" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C111" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E14</f>
-        <v>Special Washer for Axle</v>
+        <f>'[1]HP Repair Spares'!E15</f>
+        <v>Cylinder Assembly Complete</v>
       </c>
       <c r="D111" s="15" t="str">
         <f>CONCATENATE(C111," (Code: ",B111,")")</f>
-        <v>Special Washer for Axle (Code: GWDMR107)</v>
+        <v>Cylinder Assembly Complete (Code: GWDMR108)</v>
       </c>
       <c r="E111" s="14" t="s">
         <v>18</v>
@@ -6501,17 +6501,17 @@
         <v>19</v>
       </c>
       <c r="G111" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H111" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I111" s="14">
-        <f>'[1]HP Repair Spares'!F14</f>
-        <v>12</v>
+        <f>'[1]HP Repair Spares'!F15</f>
+        <v>3000</v>
       </c>
       <c r="J111" s="14">
-        <f>'[1]HP Repair Spares'!G14</f>
+        <f>'[1]HP Repair Spares'!G15</f>
         <v>0</v>
       </c>
       <c r="K111" s="16">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="L111" s="16">
         <f>SUM(I111:K111)</f>
-        <v>12</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="112" spans="1:12" ht="12.75">
@@ -6528,15 +6528,15 @@
         <v>108</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C112" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E15</f>
-        <v>Cylinder Assembly Complete</v>
+        <f>'[1]HP Repair Spares'!E16</f>
+        <v>C.I.Cylinder Body with liner</v>
       </c>
       <c r="D112" s="15" t="str">
         <f>CONCATENATE(C112," (Code: ",B112,")")</f>
-        <v>Cylinder Assembly Complete (Code: GWDMR108)</v>
+        <v>C.I.Cylinder Body with liner (Code: GWDMR109)</v>
       </c>
       <c r="E112" s="14" t="s">
         <v>18</v>
@@ -6545,17 +6545,17 @@
         <v>19</v>
       </c>
       <c r="G112" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H112" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I112" s="14">
-        <f>'[1]HP Repair Spares'!F15</f>
-        <v>3000</v>
+        <f>'[1]HP Repair Spares'!F16</f>
+        <v>1080</v>
       </c>
       <c r="J112" s="14">
-        <f>'[1]HP Repair Spares'!G15</f>
+        <f>'[1]HP Repair Spares'!G16</f>
         <v>0</v>
       </c>
       <c r="K112" s="16">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="L112" s="16">
         <f>SUM(I112:K112)</f>
-        <v>3000</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="113" spans="1:12" ht="12.75">
@@ -6572,15 +6572,15 @@
         <v>109</v>
       </c>
       <c r="B113" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C113" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E16</f>
-        <v>C.I.Cylinder Body with liner</v>
+        <f>'[1]HP Repair Spares'!E17</f>
+        <v>Plunger Rod S.S</v>
       </c>
       <c r="D113" s="15" t="str">
         <f>CONCATENATE(C113," (Code: ",B113,")")</f>
-        <v>C.I.Cylinder Body with liner (Code: GWDMR109)</v>
+        <v>Plunger Rod S.S (Code: GWDMR110)</v>
       </c>
       <c r="E113" s="14" t="s">
         <v>18</v>
@@ -6589,17 +6589,17 @@
         <v>19</v>
       </c>
       <c r="G113" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H113" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I113" s="14">
-        <f>'[1]HP Repair Spares'!F16</f>
-        <v>1080</v>
+        <f>'[1]HP Repair Spares'!F17</f>
+        <v>216</v>
       </c>
       <c r="J113" s="14">
-        <f>'[1]HP Repair Spares'!G16</f>
+        <f>'[1]HP Repair Spares'!G17</f>
         <v>0</v>
       </c>
       <c r="K113" s="16">
@@ -6608,7 +6608,7 @@
       </c>
       <c r="L113" s="16">
         <f>SUM(I113:K113)</f>
-        <v>1080</v>
+        <v>216</v>
       </c>
     </row>
     <row r="114" spans="1:12" ht="12.75">
@@ -6616,15 +6616,15 @@
         <v>110</v>
       </c>
       <c r="B114" s="15" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C114" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E17</f>
-        <v>Plunger Rod S.S</v>
+        <f>'[1]HP Repair Spares'!E18</f>
+        <v>Reducer cap</v>
       </c>
       <c r="D114" s="15" t="str">
         <f>CONCATENATE(C114," (Code: ",B114,")")</f>
-        <v>Plunger Rod S.S (Code: GWDMR110)</v>
+        <v>Reducer cap (Code: GWDMR111)</v>
       </c>
       <c r="E114" s="14" t="s">
         <v>18</v>
@@ -6633,17 +6633,17 @@
         <v>19</v>
       </c>
       <c r="G114" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H114" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I114" s="14">
-        <f>'[1]HP Repair Spares'!F17</f>
-        <v>216</v>
+        <f>'[1]HP Repair Spares'!F18</f>
+        <v>156</v>
       </c>
       <c r="J114" s="14">
-        <f>'[1]HP Repair Spares'!G17</f>
+        <f>'[1]HP Repair Spares'!G18</f>
         <v>0</v>
       </c>
       <c r="K114" s="16">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="L114" s="16">
         <f>SUM(I114:K114)</f>
-        <v>216</v>
+        <v>156</v>
       </c>
     </row>
     <row r="115" spans="1:12" ht="12.75">
@@ -6660,15 +6660,15 @@
         <v>111</v>
       </c>
       <c r="B115" s="15" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C115" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E18</f>
-        <v>Reducer cap</v>
+        <f>'[1]HP Repair Spares'!E19</f>
+        <v>Plunger Yoke body</v>
       </c>
       <c r="D115" s="15" t="str">
         <f>CONCATENATE(C115," (Code: ",B115,")")</f>
-        <v>Reducer cap (Code: GWDMR111)</v>
+        <v>Plunger Yoke body (Code: GWDMR112)</v>
       </c>
       <c r="E115" s="14" t="s">
         <v>18</v>
@@ -6677,17 +6677,17 @@
         <v>19</v>
       </c>
       <c r="G115" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H115" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I115" s="14">
-        <f>'[1]HP Repair Spares'!F18</f>
-        <v>156</v>
+        <f>'[1]HP Repair Spares'!F19</f>
+        <v>288</v>
       </c>
       <c r="J115" s="14">
-        <f>'[1]HP Repair Spares'!G18</f>
+        <f>'[1]HP Repair Spares'!G19</f>
         <v>0</v>
       </c>
       <c r="K115" s="16">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="L115" s="16">
         <f>SUM(I115:K115)</f>
-        <v>156</v>
+        <v>288</v>
       </c>
     </row>
     <row r="116" spans="1:12" ht="12.75">
@@ -6704,15 +6704,15 @@
         <v>112</v>
       </c>
       <c r="B116" s="15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C116" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E19</f>
-        <v>Plunger Yoke body</v>
+        <f>'[1]HP Repair Spares'!E20</f>
+        <v>Spacer</v>
       </c>
       <c r="D116" s="15" t="str">
         <f>CONCATENATE(C116," (Code: ",B116,")")</f>
-        <v>Plunger Yoke body (Code: GWDMR112)</v>
+        <v>Spacer (Code: GWDMR113)</v>
       </c>
       <c r="E116" s="14" t="s">
         <v>18</v>
@@ -6721,17 +6721,17 @@
         <v>19</v>
       </c>
       <c r="G116" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H116" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I116" s="14">
-        <f>'[1]HP Repair Spares'!F19</f>
-        <v>288</v>
+        <f>'[1]HP Repair Spares'!F20</f>
+        <v>228</v>
       </c>
       <c r="J116" s="14">
-        <f>'[1]HP Repair Spares'!G19</f>
+        <f>'[1]HP Repair Spares'!G20</f>
         <v>0</v>
       </c>
       <c r="K116" s="16">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="L116" s="16">
         <f>SUM(I116:K116)</f>
-        <v>288</v>
+        <v>228</v>
       </c>
     </row>
     <row r="117" spans="1:12" ht="12.75">
@@ -6748,15 +6748,15 @@
         <v>113</v>
       </c>
       <c r="B117" s="15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C117" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E20</f>
-        <v>Spacer</v>
+        <f>'[1]HP Repair Spares'!E21</f>
+        <v>Follower</v>
       </c>
       <c r="D117" s="15" t="str">
         <f>CONCATENATE(C117," (Code: ",B117,")")</f>
-        <v>Spacer (Code: GWDMR113)</v>
+        <v>Follower (Code: GWDMR114)</v>
       </c>
       <c r="E117" s="14" t="s">
         <v>18</v>
@@ -6765,17 +6765,17 @@
         <v>19</v>
       </c>
       <c r="G117" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H117" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I117" s="14">
-        <f>'[1]HP Repair Spares'!F20</f>
-        <v>228</v>
+        <f>'[1]HP Repair Spares'!F21</f>
+        <v>252</v>
       </c>
       <c r="J117" s="14">
-        <f>'[1]HP Repair Spares'!G20</f>
+        <f>'[1]HP Repair Spares'!G21</f>
         <v>0</v>
       </c>
       <c r="K117" s="16">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="L117" s="16">
         <f>SUM(I117:K117)</f>
-        <v>228</v>
+        <v>252</v>
       </c>
     </row>
     <row r="118" spans="1:12" ht="12.75">
@@ -6792,15 +6792,15 @@
         <v>114</v>
       </c>
       <c r="B118" s="15" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C118" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E21</f>
-        <v>Follower</v>
+        <f>'[1]HP Repair Spares'!E22</f>
+        <v>Upper Valve ( one piece)</v>
       </c>
       <c r="D118" s="15" t="str">
         <f>CONCATENATE(C118," (Code: ",B118,")")</f>
-        <v>Follower (Code: GWDMR114)</v>
+        <v>Upper Valve ( one piece) (Code: GWDMR115)</v>
       </c>
       <c r="E118" s="14" t="s">
         <v>18</v>
@@ -6809,17 +6809,17 @@
         <v>19</v>
       </c>
       <c r="G118" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H118" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I118" s="14">
-        <f>'[1]HP Repair Spares'!F21</f>
-        <v>252</v>
+        <f>'[1]HP Repair Spares'!F22</f>
+        <v>90</v>
       </c>
       <c r="J118" s="14">
-        <f>'[1]HP Repair Spares'!G21</f>
+        <f>'[1]HP Repair Spares'!G22</f>
         <v>0</v>
       </c>
       <c r="K118" s="16">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="L118" s="16">
         <f>SUM(I118:K118)</f>
-        <v>252</v>
+        <v>90</v>
       </c>
     </row>
     <row r="119" spans="1:12" ht="12.75">
@@ -6836,15 +6836,15 @@
         <v>115</v>
       </c>
       <c r="B119" s="15" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C119" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E22</f>
-        <v>Upper Valve ( one piece)</v>
+        <f>'[1]HP Repair Spares'!E23</f>
+        <v>Check valve guide</v>
       </c>
       <c r="D119" s="15" t="str">
         <f>CONCATENATE(C119," (Code: ",B119,")")</f>
-        <v>Upper Valve ( one piece) (Code: GWDMR115)</v>
+        <v>Check valve guide (Code: GWDMR116)</v>
       </c>
       <c r="E119" s="14" t="s">
         <v>18</v>
@@ -6853,17 +6853,17 @@
         <v>19</v>
       </c>
       <c r="G119" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H119" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I119" s="14">
-        <f>'[1]HP Repair Spares'!F22</f>
-        <v>90</v>
+        <f>'[1]HP Repair Spares'!F23</f>
+        <v>120</v>
       </c>
       <c r="J119" s="14">
-        <f>'[1]HP Repair Spares'!G22</f>
+        <f>'[1]HP Repair Spares'!G23</f>
         <v>0</v>
       </c>
       <c r="K119" s="16">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="L119" s="16">
         <f>SUM(I119:K119)</f>
-        <v>90</v>
+        <v>120</v>
       </c>
     </row>
     <row r="120" spans="1:12" ht="12.75">
@@ -6880,15 +6880,15 @@
         <v>116</v>
       </c>
       <c r="B120" s="15" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C120" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E23</f>
-        <v>Check valve guide</v>
+        <f>'[1]HP Repair Spares'!E24</f>
+        <v>Check valve seat</v>
       </c>
       <c r="D120" s="15" t="str">
         <f>CONCATENATE(C120," (Code: ",B120,")")</f>
-        <v>Check valve guide (Code: GWDMR116)</v>
+        <v>Check valve seat (Code: GWDMR117)</v>
       </c>
       <c r="E120" s="14" t="s">
         <v>18</v>
@@ -6897,17 +6897,17 @@
         <v>19</v>
       </c>
       <c r="G120" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H120" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I120" s="14">
-        <f>'[1]HP Repair Spares'!F23</f>
-        <v>120</v>
+        <f>'[1]HP Repair Spares'!F24</f>
+        <v>192</v>
       </c>
       <c r="J120" s="14">
-        <f>'[1]HP Repair Spares'!G23</f>
+        <f>'[1]HP Repair Spares'!G24</f>
         <v>0</v>
       </c>
       <c r="K120" s="16">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="L120" s="16">
         <f>SUM(I120:K120)</f>
-        <v>120</v>
+        <v>192</v>
       </c>
     </row>
     <row r="121" spans="1:12" ht="12.75">
@@ -6924,15 +6924,15 @@
         <v>117</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C121" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E24</f>
-        <v>Check valve seat</v>
+        <f>'[1]HP Repair Spares'!E25</f>
+        <v>Rubber seat Retainer</v>
       </c>
       <c r="D121" s="15" t="str">
         <f>CONCATENATE(C121," (Code: ",B121,")")</f>
-        <v>Check valve seat (Code: GWDMR117)</v>
+        <v>Rubber seat Retainer (Code: GWDMR118)</v>
       </c>
       <c r="E121" s="14" t="s">
         <v>18</v>
@@ -6941,17 +6941,17 @@
         <v>19</v>
       </c>
       <c r="G121" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H121" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I121" s="14">
-        <f>'[1]HP Repair Spares'!F24</f>
-        <v>192</v>
+        <f>'[1]HP Repair Spares'!F25</f>
+        <v>96</v>
       </c>
       <c r="J121" s="14">
-        <f>'[1]HP Repair Spares'!G24</f>
+        <f>'[1]HP Repair Spares'!G25</f>
         <v>0</v>
       </c>
       <c r="K121" s="16">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="L121" s="16">
         <f>SUM(I121:K121)</f>
-        <v>192</v>
+        <v>96</v>
       </c>
     </row>
     <row r="122" spans="1:12" ht="12.75">
@@ -6968,15 +6968,15 @@
         <v>118</v>
       </c>
       <c r="B122" s="15" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C122" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E25</f>
-        <v>Rubber seat Retainer</v>
+        <f>'[1]HP Repair Spares'!E26</f>
+        <v>Sealing ring (Nitrile Rubber)</v>
       </c>
       <c r="D122" s="15" t="str">
         <f>CONCATENATE(C122," (Code: ",B122,")")</f>
-        <v>Rubber seat Retainer (Code: GWDMR118)</v>
+        <v>Sealing ring (Nitrile Rubber) (Code: GWDMR119)</v>
       </c>
       <c r="E122" s="14" t="s">
         <v>18</v>
@@ -6985,17 +6985,17 @@
         <v>19</v>
       </c>
       <c r="G122" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H122" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I122" s="14">
-        <f>'[1]HP Repair Spares'!F25</f>
-        <v>96</v>
+        <f>'[1]HP Repair Spares'!F26</f>
+        <v>18</v>
       </c>
       <c r="J122" s="14">
-        <f>'[1]HP Repair Spares'!G25</f>
+        <f>'[1]HP Repair Spares'!G26</f>
         <v>0</v>
       </c>
       <c r="K122" s="16">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="L122" s="16">
         <f>SUM(I122:K122)</f>
-        <v>96</v>
+        <v>18</v>
       </c>
     </row>
     <row r="123" spans="1:12" ht="12.75">
@@ -7012,15 +7012,15 @@
         <v>119</v>
       </c>
       <c r="B123" s="15" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C123" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E26</f>
-        <v>Sealing ring (Nitrile Rubber)</v>
+        <f>'[1]HP Repair Spares'!E27</f>
+        <v>Rubber seating upper valve</v>
       </c>
       <c r="D123" s="15" t="str">
         <f>CONCATENATE(C123," (Code: ",B123,")")</f>
-        <v>Sealing ring (Nitrile Rubber) (Code: GWDMR119)</v>
+        <v>Rubber seating upper valve (Code: GWDMR120)</v>
       </c>
       <c r="E123" s="14" t="s">
         <v>18</v>
@@ -7029,17 +7029,17 @@
         <v>19</v>
       </c>
       <c r="G123" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H123" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I123" s="14">
-        <f>'[1]HP Repair Spares'!F26</f>
-        <v>18</v>
+        <f>'[1]HP Repair Spares'!F27</f>
+        <v>12</v>
       </c>
       <c r="J123" s="14">
-        <f>'[1]HP Repair Spares'!G26</f>
+        <f>'[1]HP Repair Spares'!G27</f>
         <v>0</v>
       </c>
       <c r="K123" s="16">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="L123" s="16">
         <f>SUM(I123:K123)</f>
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124" spans="1:12" ht="12.75">
@@ -7056,15 +7056,15 @@
         <v>120</v>
       </c>
       <c r="B124" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C124" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E27</f>
-        <v>Rubber seating upper valve</v>
+        <f>'[1]HP Repair Spares'!E28</f>
+        <v>Rubber seating check valve</v>
       </c>
       <c r="D124" s="15" t="str">
         <f>CONCATENATE(C124," (Code: ",B124,")")</f>
-        <v>Rubber seating upper valve (Code: GWDMR120)</v>
+        <v>Rubber seating check valve (Code: GWDMR121)</v>
       </c>
       <c r="E124" s="14" t="s">
         <v>18</v>
@@ -7073,17 +7073,17 @@
         <v>19</v>
       </c>
       <c r="G124" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H124" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I124" s="14">
-        <f>'[1]HP Repair Spares'!F27</f>
+        <f>'[1]HP Repair Spares'!F28</f>
         <v>12</v>
       </c>
       <c r="J124" s="14">
-        <f>'[1]HP Repair Spares'!G27</f>
+        <f>'[1]HP Repair Spares'!G28</f>
         <v>0</v>
       </c>
       <c r="K124" s="16">
@@ -7100,15 +7100,15 @@
         <v>121</v>
       </c>
       <c r="B125" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C125" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E28</f>
-        <v>Rubber seating check valve</v>
+        <f>'[1]HP Repair Spares'!E29</f>
+        <v>Pump Bucket (Nitrile Rubber)</v>
       </c>
       <c r="D125" s="15" t="str">
         <f>CONCATENATE(C125," (Code: ",B125,")")</f>
-        <v>Rubber seating check valve (Code: GWDMR121)</v>
+        <v>Pump Bucket (Nitrile Rubber) (Code: GWDMR122)</v>
       </c>
       <c r="E125" s="14" t="s">
         <v>18</v>
@@ -7117,17 +7117,17 @@
         <v>19</v>
       </c>
       <c r="G125" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H125" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I125" s="14">
-        <f>'[1]HP Repair Spares'!F28</f>
-        <v>12</v>
+        <f>'[1]HP Repair Spares'!F29</f>
+        <v>30</v>
       </c>
       <c r="J125" s="14">
-        <f>'[1]HP Repair Spares'!G28</f>
+        <f>'[1]HP Repair Spares'!G29</f>
         <v>0</v>
       </c>
       <c r="K125" s="16">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="L125" s="16">
         <f>SUM(I125:K125)</f>
-        <v>12</v>
+        <v>30</v>
       </c>
     </row>
     <row r="126" spans="1:12" ht="12.75">
@@ -7144,15 +7144,15 @@
         <v>122</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C126" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E29</f>
-        <v>Pump Bucket (Nitrile Rubber)</v>
+        <f>'[1]HP Repair Spares'!E30</f>
+        <v>Upper valve Assembly comprising of SS Plunger rod, Plunger Yoke body, 2 spacer &amp; 2 bucket washers</v>
       </c>
       <c r="D126" s="15" t="str">
         <f>CONCATENATE(C126," (Code: ",B126,")")</f>
-        <v>Pump Bucket (Nitrile Rubber) (Code: GWDMR122)</v>
+        <v>Upper valve Assembly comprising of SS Plunger rod, Plunger Yoke body, 2 spacer &amp; 2 bucket washers (Code: GWDMR123)</v>
       </c>
       <c r="E126" s="14" t="s">
         <v>18</v>
@@ -7161,17 +7161,17 @@
         <v>19</v>
       </c>
       <c r="G126" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H126" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I126" s="14">
-        <f>'[1]HP Repair Spares'!F29</f>
-        <v>30</v>
+        <f>'[1]HP Repair Spares'!F30</f>
+        <v>1200</v>
       </c>
       <c r="J126" s="14">
-        <f>'[1]HP Repair Spares'!G29</f>
+        <f>'[1]HP Repair Spares'!G30</f>
         <v>0</v>
       </c>
       <c r="K126" s="16">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="L126" s="16">
         <f>SUM(I126:K126)</f>
-        <v>30</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="127" spans="1:12" ht="12.75">
@@ -7188,15 +7188,15 @@
         <v>123</v>
       </c>
       <c r="B127" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C127" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E30</f>
-        <v>Upper valve Assembly comprising of SS Plunger rod, Plunger Yoke body, 2 spacer &amp; 2 bucket washers</v>
+        <f>'[1]HP Repair Spares'!E31</f>
+        <v>Same as above but without plunger rod</v>
       </c>
       <c r="D127" s="15" t="str">
         <f>CONCATENATE(C127," (Code: ",B127,")")</f>
-        <v>Upper valve Assembly comprising of SS Plunger rod, Plunger Yoke body, 2 spacer &amp; 2 bucket washers (Code: GWDMR123)</v>
+        <v>Same as above but without plunger rod (Code: GWDMR124)</v>
       </c>
       <c r="E127" s="14" t="s">
         <v>18</v>
@@ -7205,17 +7205,17 @@
         <v>19</v>
       </c>
       <c r="G127" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H127" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I127" s="14">
-        <f>'[1]HP Repair Spares'!F30</f>
-        <v>1200</v>
+        <f>'[1]HP Repair Spares'!F31</f>
+        <v>1080</v>
       </c>
       <c r="J127" s="14">
-        <f>'[1]HP Repair Spares'!G30</f>
+        <f>'[1]HP Repair Spares'!G31</f>
         <v>0</v>
       </c>
       <c r="K127" s="16">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="L127" s="16">
         <f>SUM(I127:K127)</f>
-        <v>1200</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="128" spans="1:12" ht="12.75">
@@ -7232,15 +7232,15 @@
         <v>124</v>
       </c>
       <c r="B128" s="15" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C128" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E31</f>
-        <v>Same as above but without plunger rod</v>
+        <f>'[1]HP Repair Spares'!E32</f>
+        <v>Lower Valve Assembly comprising of Rubber Seat Retainer, Check valve guide and rubber seating</v>
       </c>
       <c r="D128" s="15" t="str">
         <f>CONCATENATE(C128," (Code: ",B128,")")</f>
-        <v>Same as above but without plunger rod (Code: GWDMR124)</v>
+        <v>Lower Valve Assembly comprising of Rubber Seat Retainer, Check valve guide and rubber seating (Code: GWDMR125)</v>
       </c>
       <c r="E128" s="14" t="s">
         <v>18</v>
@@ -7249,17 +7249,17 @@
         <v>19</v>
       </c>
       <c r="G128" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H128" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I128" s="14">
-        <f>'[1]HP Repair Spares'!F31</f>
-        <v>1080</v>
+        <f>'[1]HP Repair Spares'!F32</f>
+        <v>540</v>
       </c>
       <c r="J128" s="14">
-        <f>'[1]HP Repair Spares'!G31</f>
+        <f>'[1]HP Repair Spares'!G32</f>
         <v>0</v>
       </c>
       <c r="K128" s="16">
@@ -7268,7 +7268,7 @@
       </c>
       <c r="L128" s="16">
         <f>SUM(I128:K128)</f>
-        <v>1080</v>
+        <v>540</v>
       </c>
     </row>
     <row r="129" spans="1:12" ht="12.75">
@@ -7276,15 +7276,15 @@
         <v>125</v>
       </c>
       <c r="B129" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C129" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E32</f>
-        <v>Lower Valve Assembly comprising of Rubber Seat Retainer, Check valve guide and rubber seating</v>
+        <f>'[1]HP Repair Spares'!E33</f>
+        <v>Water Tank</v>
       </c>
       <c r="D129" s="15" t="str">
         <f>CONCATENATE(C129," (Code: ",B129,")")</f>
-        <v>Lower Valve Assembly comprising of Rubber Seat Retainer, Check valve guide and rubber seating (Code: GWDMR125)</v>
+        <v>Water Tank (Code: GWDMR126)</v>
       </c>
       <c r="E129" s="14" t="s">
         <v>18</v>
@@ -7293,17 +7293,17 @@
         <v>19</v>
       </c>
       <c r="G129" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H129" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I129" s="14">
-        <f>'[1]HP Repair Spares'!F32</f>
-        <v>540</v>
+        <f>'[1]HP Repair Spares'!F33</f>
+        <v>1800</v>
       </c>
       <c r="J129" s="14">
-        <f>'[1]HP Repair Spares'!G32</f>
+        <f>'[1]HP Repair Spares'!G33</f>
         <v>0</v>
       </c>
       <c r="K129" s="16">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="L129" s="16">
         <f>SUM(I129:K129)</f>
-        <v>540</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="130" spans="1:12" ht="12.75">
@@ -7320,15 +7320,15 @@
         <v>126</v>
       </c>
       <c r="B130" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C130" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E33</f>
-        <v>Water Tank</v>
+        <f>'[1]HP Repair Spares'!E34</f>
+        <v>Pipe Sockets</v>
       </c>
       <c r="D130" s="15" t="str">
         <f>CONCATENATE(C130," (Code: ",B130,")")</f>
-        <v>Water Tank (Code: GWDMR126)</v>
+        <v>Pipe Sockets (Code: GWDMR127)</v>
       </c>
       <c r="E130" s="14" t="s">
         <v>18</v>
@@ -7337,17 +7337,17 @@
         <v>19</v>
       </c>
       <c r="G130" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H130" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I130" s="14">
-        <f>'[1]HP Repair Spares'!F33</f>
-        <v>1800</v>
+        <f>'[1]HP Repair Spares'!F34</f>
+        <v>120</v>
       </c>
       <c r="J130" s="14">
-        <f>'[1]HP Repair Spares'!G33</f>
+        <f>'[1]HP Repair Spares'!G34</f>
         <v>0</v>
       </c>
       <c r="K130" s="16">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="L130" s="16">
         <f>SUM(I130:K130)</f>
-        <v>1800</v>
+        <v>120</v>
       </c>
     </row>
     <row r="131" spans="1:12" ht="12.75">
@@ -7364,15 +7364,15 @@
         <v>127</v>
       </c>
       <c r="B131" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C131" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E34</f>
-        <v>Pipe Sockets</v>
+        <f>'[1]HP Repair Spares'!E35</f>
+        <v>Pedestal (Ordinary)</v>
       </c>
       <c r="D131" s="15" t="str">
         <f>CONCATENATE(C131," (Code: ",B131,")")</f>
-        <v>Pipe Sockets (Code: GWDMR127)</v>
+        <v>Pedestal (Ordinary) (Code: GWDMR128)</v>
       </c>
       <c r="E131" s="14" t="s">
         <v>18</v>
@@ -7381,17 +7381,17 @@
         <v>19</v>
       </c>
       <c r="G131" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H131" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I131" s="14">
-        <f>'[1]HP Repair Spares'!F34</f>
-        <v>120</v>
+        <f>'[1]HP Repair Spares'!F35</f>
+        <v>3120</v>
       </c>
       <c r="J131" s="14">
-        <f>'[1]HP Repair Spares'!G34</f>
+        <f>'[1]HP Repair Spares'!G35</f>
         <v>0</v>
       </c>
       <c r="K131" s="16">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="L131" s="16">
         <f>SUM(I131:K131)</f>
-        <v>120</v>
+        <v>3120</v>
       </c>
     </row>
     <row r="132" spans="1:12" ht="12.75">
@@ -7408,15 +7408,15 @@
         <v>128</v>
       </c>
       <c r="B132" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C132" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E35</f>
-        <v>Pedestal (Ordinary)</v>
+        <f>'[1]HP Repair Spares'!E36</f>
+        <v>12 mm dia x 3 m electro galvanized</v>
       </c>
       <c r="D132" s="15" t="str">
         <f>CONCATENATE(C132," (Code: ",B132,")")</f>
-        <v>Pedestal (Ordinary) (Code: GWDMR128)</v>
+        <v>12 mm dia x 3 m electro galvanized (Code: GWDMR129)</v>
       </c>
       <c r="E132" s="14" t="s">
         <v>18</v>
@@ -7425,17 +7425,17 @@
         <v>19</v>
       </c>
       <c r="G132" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H132" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I132" s="14">
-        <f>'[1]HP Repair Spares'!F35</f>
-        <v>3120</v>
+        <f>'[1]HP Repair Spares'!F36</f>
+        <v>336</v>
       </c>
       <c r="J132" s="14">
-        <f>'[1]HP Repair Spares'!G35</f>
+        <f>'[1]HP Repair Spares'!G36</f>
         <v>0</v>
       </c>
       <c r="K132" s="16">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="L132" s="16">
         <f>SUM(I132:K132)</f>
-        <v>3120</v>
+        <v>336</v>
       </c>
     </row>
     <row r="133" spans="1:12" ht="12.75">
@@ -7452,15 +7452,15 @@
         <v>129</v>
       </c>
       <c r="B133" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C133" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E36</f>
-        <v>12 mm dia x 3 m electro galvanized</v>
+        <f>'[1]HP Repair Spares'!E37</f>
+        <v>Hex. Coupler 12 x 50 mm</v>
       </c>
       <c r="D133" s="15" t="str">
         <f>CONCATENATE(C133," (Code: ",B133,")")</f>
-        <v>12 mm dia x 3 m electro galvanized (Code: GWDMR129)</v>
+        <v>Hex. Coupler 12 x 50 mm (Code: GWDMR130)</v>
       </c>
       <c r="E133" s="14" t="s">
         <v>18</v>
@@ -7469,17 +7469,17 @@
         <v>19</v>
       </c>
       <c r="G133" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H133" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I133" s="14">
-        <f>'[1]HP Repair Spares'!F36</f>
-        <v>336</v>
+        <f>'[1]HP Repair Spares'!F37</f>
+        <v>30</v>
       </c>
       <c r="J133" s="14">
-        <f>'[1]HP Repair Spares'!G36</f>
+        <f>'[1]HP Repair Spares'!G37</f>
         <v>0</v>
       </c>
       <c r="K133" s="16">
@@ -7488,7 +7488,7 @@
       </c>
       <c r="L133" s="16">
         <f>SUM(I133:K133)</f>
-        <v>336</v>
+        <v>30</v>
       </c>
     </row>
     <row r="134" spans="1:12" ht="12.75">
@@ -7496,15 +7496,15 @@
         <v>130</v>
       </c>
       <c r="B134" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C134" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E37</f>
-        <v>Hex. Coupler 12 x 50 mm</v>
+        <f>'[1]HP Repair Spares'!E38</f>
+        <v>Hex. Coupler 12 x 20 mm</v>
       </c>
       <c r="D134" s="15" t="str">
         <f>CONCATENATE(C134," (Code: ",B134,")")</f>
-        <v>Hex. Coupler 12 x 50 mm (Code: GWDMR130)</v>
+        <v>Hex. Coupler 12 x 20 mm (Code: GWDMR131)</v>
       </c>
       <c r="E134" s="14" t="s">
         <v>18</v>
@@ -7513,17 +7513,17 @@
         <v>19</v>
       </c>
       <c r="G134" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H134" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I134" s="14">
-        <f>'[1]HP Repair Spares'!F37</f>
-        <v>30</v>
+        <f>'[1]HP Repair Spares'!F38</f>
+        <v>24</v>
       </c>
       <c r="J134" s="14">
-        <f>'[1]HP Repair Spares'!G37</f>
+        <f>'[1]HP Repair Spares'!G38</f>
         <v>0</v>
       </c>
       <c r="K134" s="16">
@@ -7532,7 +7532,7 @@
       </c>
       <c r="L134" s="16">
         <f>SUM(I134:K134)</f>
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="135" spans="1:12" ht="12.75">
@@ -7540,15 +7540,15 @@
         <v>131</v>
       </c>
       <c r="B135" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C135" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E38</f>
-        <v>Hex. Coupler 12 x 20 mm</v>
+        <f>'[1]HP Repair Spares'!E39</f>
+        <v>GI Riser pipe (B class) 3 m long 32mm bore size both end threaded with one end socket (Code: 1548 - Including Water Charge and CPOH)</v>
       </c>
       <c r="D135" s="15" t="str">
         <f>CONCATENATE(C135," (Code: ",B135,")")</f>
-        <v>Hex. Coupler 12 x 20 mm (Code: GWDMR131)</v>
+        <v>GI Riser pipe (B class) 3 m long 32mm bore size both end threaded with one end socket (Code: 1548 - Including Water Charge and CPOH) (Code: GWDMR132)</v>
       </c>
       <c r="E135" s="14" t="s">
         <v>18</v>
@@ -7557,18 +7557,18 @@
         <v>19</v>
       </c>
       <c r="G135" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H135" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I135" s="14">
-        <f>'[1]HP Repair Spares'!F38</f>
-        <v>24</v>
+        <f>'[1]HP Repair Spares'!F39</f>
+        <v>0</v>
       </c>
       <c r="J135" s="14">
-        <f>'[1]HP Repair Spares'!G38</f>
-        <v>0</v>
+        <f>'[1]HP Repair Spares'!G39</f>
+        <v>261.34</v>
       </c>
       <c r="K135" s="16">
         <f>J135*($L$2-1)</f>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="L135" s="16">
         <f>SUM(I135:K135)</f>
-        <v>24</v>
+        <v>261.34</v>
       </c>
     </row>
     <row r="136" spans="1:12" ht="12.75">
@@ -7584,15 +7584,15 @@
         <v>132</v>
       </c>
       <c r="B136" s="15" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C136" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E39</f>
-        <v>GI Riser pipe (B class) 3 m long 32mm bore size both end threaded with one end socket (Code: 1548 - Including Water Charge and CPOH)</v>
+        <f>'[1]HP Repair Spares'!E40</f>
+        <v>Cylinder Extra deep well hand pump</v>
       </c>
       <c r="D136" s="15" t="str">
         <f>CONCATENATE(C136," (Code: ",B136,")")</f>
-        <v>GI Riser pipe (B class) 3 m long 32mm bore size both end threaded with one end socket (Code: 1548 - Including Water Charge and CPOH) (Code: GWDMR132)</v>
+        <v>Cylinder Extra deep well hand pump (Code: GWDMR133)</v>
       </c>
       <c r="E136" s="14" t="s">
         <v>18</v>
@@ -7601,18 +7601,18 @@
         <v>19</v>
       </c>
       <c r="G136" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H136" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I136" s="14">
-        <f>'[1]HP Repair Spares'!F39</f>
-        <v>0</v>
+        <f>'[1]HP Repair Spares'!F40</f>
+        <v>4320</v>
       </c>
       <c r="J136" s="14">
-        <f>'[1]HP Repair Spares'!G39</f>
-        <v>261.34</v>
+        <f>'[1]HP Repair Spares'!G40</f>
+        <v>0</v>
       </c>
       <c r="K136" s="16">
         <f>J136*($L$2-1)</f>
@@ -7620,7 +7620,7 @@
       </c>
       <c r="L136" s="16">
         <f>SUM(I136:K136)</f>
-        <v>261.34</v>
+        <v>4320</v>
       </c>
     </row>
     <row r="137" spans="1:12" ht="12.75">
@@ -7628,15 +7628,15 @@
         <v>133</v>
       </c>
       <c r="B137" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C137" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E40</f>
-        <v>Cylinder Extra deep well hand pump</v>
+        <f>'[1]HP Repair Spares'!E41</f>
+        <v>Head Assembly for extra deep well pump with T</v>
       </c>
       <c r="D137" s="15" t="str">
         <f>CONCATENATE(C137," (Code: ",B137,")")</f>
-        <v>Cylinder Extra deep well hand pump (Code: GWDMR133)</v>
+        <v>Head Assembly for extra deep well pump with T (Code: GWDMR134)</v>
       </c>
       <c r="E137" s="14" t="s">
         <v>18</v>
@@ -7645,17 +7645,17 @@
         <v>19</v>
       </c>
       <c r="G137" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H137" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I137" s="14">
-        <f>'[1]HP Repair Spares'!F40</f>
-        <v>4320</v>
+        <f>'[1]HP Repair Spares'!F41</f>
+        <v>7200</v>
       </c>
       <c r="J137" s="14">
-        <f>'[1]HP Repair Spares'!G40</f>
+        <f>'[1]HP Repair Spares'!G41</f>
         <v>0</v>
       </c>
       <c r="K137" s="16">
@@ -7664,7 +7664,7 @@
       </c>
       <c r="L137" s="16">
         <f>SUM(I137:K137)</f>
-        <v>4320</v>
+        <v>7200</v>
       </c>
     </row>
     <row r="138" spans="1:12" ht="12.75">
@@ -7672,15 +7672,15 @@
         <v>134</v>
       </c>
       <c r="B138" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C138" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E41</f>
-        <v>Head Assembly for extra deep well pump with T</v>
+        <f>'[1]HP Repair Spares'!E42</f>
+        <v>ISI marked India Mark II (Standard) Deep well hand pumps confirming to IS: 15500 (Part II) 2004 complete with 10 Nos. GI pipe (B class) 3m long  32mm bore both end threaded with one end socket and 10 Nos connecting rods</v>
       </c>
       <c r="D138" s="15" t="str">
         <f>CONCATENATE(C138," (Code: ",B138,")")</f>
-        <v>Head Assembly for extra deep well pump with T (Code: GWDMR134)</v>
+        <v>ISI marked India Mark II (Standard) Deep well hand pumps confirming to IS: 15500 (Part II) 2004 complete with 10 Nos. GI pipe (B class) 3m long  32mm bore both end threaded with one end socket and 10 Nos connecting rods (Code: GWDMR135)</v>
       </c>
       <c r="E138" s="14" t="s">
         <v>18</v>
@@ -7689,17 +7689,17 @@
         <v>19</v>
       </c>
       <c r="G138" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H138" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I138" s="14">
-        <f>'[1]HP Repair Spares'!F41</f>
-        <v>7200</v>
+        <f>'[1]HP Repair Spares'!F42</f>
+        <v>31000</v>
       </c>
       <c r="J138" s="14">
-        <f>'[1]HP Repair Spares'!G41</f>
+        <f>'[1]HP Repair Spares'!G42</f>
         <v>0</v>
       </c>
       <c r="K138" s="16">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="L138" s="16">
         <f>SUM(I138:K138)</f>
-        <v>7200</v>
+        <v>31000</v>
       </c>
     </row>
     <row r="139" spans="1:12" ht="12.75">
@@ -7716,15 +7716,15 @@
         <v>135</v>
       </c>
       <c r="B139" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C139" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E42</f>
-        <v>ISI marked India Mark II (Standard) Deep well hand pumps confirming to IS: 15500 (Part II) 2004 complete with 10 Nos. GI pipe (B class) 3m long  32mm bore both end threaded with one end socket and 10 Nos connecting rods</v>
+        <f>'[1]HP Repair Spares'!E43</f>
+        <v>ISI marked India Mark II (Standard) Extra Deep well hand pumps confirming to IS: 15500 (Part II) 2004 complete with 20 Nos. GI pipe (B class) 3m long  32mm bore both end threaded with one end socket and 20 Nos connecting rods</v>
       </c>
       <c r="D139" s="15" t="str">
         <f>CONCATENATE(C139," (Code: ",B139,")")</f>
-        <v>ISI marked India Mark II (Standard) Deep well hand pumps confirming to IS: 15500 (Part II) 2004 complete with 10 Nos. GI pipe (B class) 3m long  32mm bore both end threaded with one end socket and 10 Nos connecting rods (Code: GWDMR135)</v>
+        <v>ISI marked India Mark II (Standard) Extra Deep well hand pumps confirming to IS: 15500 (Part II) 2004 complete with 20 Nos. GI pipe (B class) 3m long  32mm bore both end threaded with one end socket and 20 Nos connecting rods (Code: GWDMR136)</v>
       </c>
       <c r="E139" s="14" t="s">
         <v>18</v>
@@ -7733,17 +7733,17 @@
         <v>19</v>
       </c>
       <c r="G139" s="16" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="H139" s="16" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="I139" s="14">
-        <f>'[1]HP Repair Spares'!F42</f>
-        <v>31000</v>
+        <f>'[1]HP Repair Spares'!F43</f>
+        <v>49000</v>
       </c>
       <c r="J139" s="14">
-        <f>'[1]HP Repair Spares'!G42</f>
+        <f>'[1]HP Repair Spares'!G43</f>
         <v>0</v>
       </c>
       <c r="K139" s="16">
@@ -7752,7 +7752,7 @@
       </c>
       <c r="L139" s="16">
         <f>SUM(I139:K139)</f>
-        <v>31000</v>
+        <v>49000</v>
       </c>
     </row>
     <row r="140" spans="1:12" ht="12.75">
@@ -7760,15 +7760,14 @@
         <v>136</v>
       </c>
       <c r="B140" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="C140" s="15" t="s">
         <v>272</v>
-      </c>
-      <c r="C140" s="15" t="str">
-        <f>'[1]HP Repair Spares'!E43</f>
-        <v>ISI marked India Mark II (Standard) Extra Deep well hand pumps confirming to IS: 15500 (Part II) 2004 complete with 20 Nos. GI pipe (B class) 3m long  32mm bore both end threaded with one end socket and 20 Nos connecting rods</v>
       </c>
       <c r="D140" s="15" t="str">
         <f>CONCATENATE(C140," (Code: ",B140,")")</f>
-        <v>ISI marked India Mark II (Standard) Extra Deep well hand pumps confirming to IS: 15500 (Part II) 2004 complete with 20 Nos. GI pipe (B class) 3m long  32mm bore both end threaded with one end socket and 20 Nos connecting rods (Code: GWDMR136)</v>
+        <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 2500-6000 lph, Head 49-17m without Panel Board (Code: GWDMR137)</v>
       </c>
       <c r="E140" s="14" t="s">
         <v>18</v>
@@ -7777,17 +7776,15 @@
         <v>19</v>
       </c>
       <c r="G140" s="16" t="s">
-        <v>229</v>
+        <v>97</v>
       </c>
       <c r="H140" s="16" t="s">
-        <v>230</v>
-      </c>
-      <c r="I140" s="14">
-        <f>'[1]HP Repair Spares'!F43</f>
-        <v>49000</v>
+        <v>273</v>
+      </c>
+      <c r="I140" s="16">
+        <v>21162.53</v>
       </c>
       <c r="J140" s="14">
-        <f>'[1]HP Repair Spares'!G43</f>
         <v>0</v>
       </c>
       <c r="K140" s="16">
@@ -7796,7 +7793,7 @@
       </c>
       <c r="L140" s="16">
         <f>SUM(I140:K140)</f>
-        <v>49000</v>
+        <v>21162.53</v>
       </c>
     </row>
     <row r="141" spans="1:12" ht="12.75">
@@ -7804,14 +7801,14 @@
         <v>137</v>
       </c>
       <c r="B141" s="15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C141" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D141" s="15" t="str">
         <f>CONCATENATE(C141," (Code: ",B141,")")</f>
-        <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 2500-6000 lph, Head 49-17m without Panel Board (Code: GWDMR137)</v>
+        <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 2500-6000 lph, Head 57-14m without Panel Board (Code: GWDMR138)</v>
       </c>
       <c r="E141" s="14" t="s">
         <v>18</v>
@@ -7823,10 +7820,10 @@
         <v>97</v>
       </c>
       <c r="H141" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I141" s="16">
-        <v>21162.53</v>
+        <v>22126.575000000001</v>
       </c>
       <c r="J141" s="14">
         <v>0</v>
@@ -7837,7 +7834,7 @@
       </c>
       <c r="L141" s="16">
         <f>SUM(I141:K141)</f>
-        <v>21162.53</v>
+        <v>22126.575000000001</v>
       </c>
     </row>
     <row r="142" spans="1:12" ht="12.75">
@@ -7852,7 +7849,7 @@
       </c>
       <c r="D142" s="15" t="str">
         <f>CONCATENATE(C142," (Code: ",B142,")")</f>
-        <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 2500-6000 lph, Head 57-14m without Panel Board (Code: GWDMR138)</v>
+        <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 1800-4320 lph, Head 65-39m without Panel Board (Code: GWDMR139)</v>
       </c>
       <c r="E142" s="14" t="s">
         <v>18</v>
@@ -7864,10 +7861,10 @@
         <v>97</v>
       </c>
       <c r="H142" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I142" s="16">
-        <v>22126.575000000001</v>
+        <v>21047.772000000001</v>
       </c>
       <c r="J142" s="14">
         <v>0</v>
@@ -7878,7 +7875,7 @@
       </c>
       <c r="L142" s="16">
         <f>SUM(I142:K142)</f>
-        <v>22126.575000000001</v>
+        <v>21047.772000000001</v>
       </c>
     </row>
     <row r="143" spans="1:12" ht="12.75">
@@ -7893,7 +7890,7 @@
       </c>
       <c r="D143" s="15" t="str">
         <f>CONCATENATE(C143," (Code: ",B143,")")</f>
-        <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 1800-4320 lph, Head 65-39m without Panel Board (Code: GWDMR139)</v>
+        <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 2500-6000 lph, Head 69-17m without Panel Board (Code: GWDMR140)</v>
       </c>
       <c r="E143" s="14" t="s">
         <v>18</v>
@@ -7905,10 +7902,10 @@
         <v>97</v>
       </c>
       <c r="H143" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I143" s="16">
-        <v>21047.772000000001</v>
+        <v>24391.499999999996</v>
       </c>
       <c r="J143" s="14">
         <v>0</v>
@@ -7919,7 +7916,7 @@
       </c>
       <c r="L143" s="16">
         <f>SUM(I143:K143)</f>
-        <v>21047.772000000001</v>
+        <v>24391.50</v>
       </c>
     </row>
     <row r="144" spans="1:12" ht="12.75">
@@ -7934,7 +7931,7 @@
       </c>
       <c r="D144" s="15" t="str">
         <f>CONCATENATE(C144," (Code: ",B144,")")</f>
-        <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 2500-6000 lph, Head 69-17m without Panel Board (Code: GWDMR140)</v>
+        <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 1080-2880 lph, Head 91-50m without Panel Board (Code: GWDMR141)</v>
       </c>
       <c r="E144" s="14" t="s">
         <v>18</v>
@@ -7946,10 +7943,10 @@
         <v>97</v>
       </c>
       <c r="H144" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I144" s="16">
-        <v>24391.499999999996</v>
+        <v>22498.716</v>
       </c>
       <c r="J144" s="14">
         <v>0</v>
@@ -7960,7 +7957,7 @@
       </c>
       <c r="L144" s="16">
         <f>SUM(I144:K144)</f>
-        <v>24391.50</v>
+        <v>22498.716</v>
       </c>
     </row>
     <row r="145" spans="1:12" ht="12.75">
@@ -7975,7 +7972,7 @@
       </c>
       <c r="D145" s="15" t="str">
         <f>CONCATENATE(C145," (Code: ",B145,")")</f>
-        <v>Supply of Single Phase Submersible Pump 1 HP, Discharge 1080-2880 lph, Head 91-50m without Panel Board (Code: GWDMR141)</v>
+        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 3000-7500 lph, Head 65-32m without Panel Board (Code: GWDMR142)</v>
       </c>
       <c r="E145" s="14" t="s">
         <v>18</v>
@@ -7987,10 +7984,10 @@
         <v>97</v>
       </c>
       <c r="H145" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I145" s="16">
-        <v>22498.716</v>
+        <v>24937.404999999995</v>
       </c>
       <c r="J145" s="14">
         <v>0</v>
@@ -8001,7 +7998,7 @@
       </c>
       <c r="L145" s="16">
         <f>SUM(I145:K145)</f>
-        <v>22498.716</v>
+        <v>24937.404999999999</v>
       </c>
     </row>
     <row r="146" spans="1:12" ht="12.75">
@@ -8016,7 +8013,7 @@
       </c>
       <c r="D146" s="15" t="str">
         <f>CONCATENATE(C146," (Code: ",B146,")")</f>
-        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 3000-7500 lph, Head 65-32m without Panel Board (Code: GWDMR142)</v>
+        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 1800-4320 lph, Head 83-52m without Panel Board (Code: GWDMR143)</v>
       </c>
       <c r="E146" s="14" t="s">
         <v>18</v>
@@ -8028,10 +8025,10 @@
         <v>97</v>
       </c>
       <c r="H146" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I146" s="16">
-        <v>24937.404999999995</v>
+        <v>23219.315999999999</v>
       </c>
       <c r="J146" s="14">
         <v>0</v>
@@ -8042,7 +8039,7 @@
       </c>
       <c r="L146" s="16">
         <f>SUM(I146:K146)</f>
-        <v>24937.404999999999</v>
+        <v>23219.315999999999</v>
       </c>
     </row>
     <row r="147" spans="1:12" ht="12.75">
@@ -8057,7 +8054,7 @@
       </c>
       <c r="D147" s="15" t="str">
         <f>CONCATENATE(C147," (Code: ",B147,")")</f>
-        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 1800-4320 lph, Head 83-52m without Panel Board (Code: GWDMR143)</v>
+        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 1800-4320 lph, Head 105-57m without Panel Board (Code: GWDMR144)</v>
       </c>
       <c r="E147" s="14" t="s">
         <v>18</v>
@@ -8069,10 +8066,10 @@
         <v>97</v>
       </c>
       <c r="H147" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I147" s="16">
-        <v>23219.315999999999</v>
+        <v>24493.248</v>
       </c>
       <c r="J147" s="14">
         <v>0</v>
@@ -8083,7 +8080,7 @@
       </c>
       <c r="L147" s="16">
         <f>SUM(I147:K147)</f>
-        <v>23219.315999999999</v>
+        <v>24493.248</v>
       </c>
     </row>
     <row r="148" spans="1:12" ht="12.75">
@@ -8098,7 +8095,7 @@
       </c>
       <c r="D148" s="15" t="str">
         <f>CONCATENATE(C148," (Code: ",B148,")")</f>
-        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 1800-4320 lph, Head 105-57m without Panel Board (Code: GWDMR144)</v>
+        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 500-3000 lph, Head 126-43m without Panel Board (Code: GWDMR145)</v>
       </c>
       <c r="E148" s="14" t="s">
         <v>18</v>
@@ -8110,10 +8107,10 @@
         <v>97</v>
       </c>
       <c r="H148" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I148" s="16">
-        <v>24493.248</v>
+        <v>24159.199999999997</v>
       </c>
       <c r="J148" s="14">
         <v>0</v>
@@ -8124,7 +8121,7 @@
       </c>
       <c r="L148" s="16">
         <f>SUM(I148:K148)</f>
-        <v>24493.248</v>
+        <v>24159.20</v>
       </c>
     </row>
     <row r="149" spans="1:12" ht="12.75">
@@ -8139,7 +8136,7 @@
       </c>
       <c r="D149" s="15" t="str">
         <f>CONCATENATE(C149," (Code: ",B149,")")</f>
-        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 500-3000 lph, Head 126-43m without Panel Board (Code: GWDMR145)</v>
+        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 1080-2880 lph, Head 137-75m without Panel Board (Code: GWDMR146)</v>
       </c>
       <c r="E149" s="14" t="s">
         <v>18</v>
@@ -8151,10 +8148,10 @@
         <v>97</v>
       </c>
       <c r="H149" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I149" s="16">
-        <v>24159.199999999997</v>
+        <v>26133.749999999996</v>
       </c>
       <c r="J149" s="14">
         <v>0</v>
@@ -8165,7 +8162,7 @@
       </c>
       <c r="L149" s="16">
         <f>SUM(I149:K149)</f>
-        <v>24159.20</v>
+        <v>26133.75</v>
       </c>
     </row>
     <row r="150" spans="1:12" ht="12.75">
@@ -8180,7 +8177,7 @@
       </c>
       <c r="D150" s="15" t="str">
         <f>CONCATENATE(C150," (Code: ",B150,")")</f>
-        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 1080-2880 lph, Head 137-75m without Panel Board (Code: GWDMR146)</v>
+        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 500-3000 lph, Head 148-50m without Panel Board (Code: GWDMR147)</v>
       </c>
       <c r="E150" s="14" t="s">
         <v>18</v>
@@ -8192,10 +8189,10 @@
         <v>97</v>
       </c>
       <c r="H150" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I150" s="16">
-        <v>26133.749999999996</v>
+        <v>27980.534999999996</v>
       </c>
       <c r="J150" s="14">
         <v>0</v>
@@ -8206,7 +8203,7 @@
       </c>
       <c r="L150" s="16">
         <f>SUM(I150:K150)</f>
-        <v>26133.75</v>
+        <v>27980.535</v>
       </c>
     </row>
     <row r="151" spans="1:12" ht="12.75">
@@ -8221,7 +8218,7 @@
       </c>
       <c r="D151" s="15" t="str">
         <f>CONCATENATE(C151," (Code: ",B151,")")</f>
-        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 500-3000 lph, Head 148-50m without Panel Board (Code: GWDMR147)</v>
+        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 300-2100 lph, Head 180-51m without Panel Board (Code: GWDMR148)</v>
       </c>
       <c r="E151" s="14" t="s">
         <v>18</v>
@@ -8233,10 +8230,10 @@
         <v>97</v>
       </c>
       <c r="H151" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I151" s="16">
-        <v>27980.534999999996</v>
+        <v>30082.849999999995</v>
       </c>
       <c r="J151" s="14">
         <v>0</v>
@@ -8247,7 +8244,7 @@
       </c>
       <c r="L151" s="16">
         <f>SUM(I151:K151)</f>
-        <v>27980.535</v>
+        <v>30082.85</v>
       </c>
     </row>
     <row r="152" spans="1:12" ht="12.75">
@@ -8262,7 +8259,7 @@
       </c>
       <c r="D152" s="15" t="str">
         <f>CONCATENATE(C152," (Code: ",B152,")")</f>
-        <v>Supply of Single Phase Submersible Pump 1.5 HP, Discharge 300-2100 lph, Head 180-51m without Panel Board (Code: GWDMR148)</v>
+        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 5200-10600 lph, Head 57-18m without Panel Board (Code: GWDMR149)</v>
       </c>
       <c r="E152" s="14" t="s">
         <v>18</v>
@@ -8274,10 +8271,10 @@
         <v>97</v>
       </c>
       <c r="H152" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I152" s="16">
-        <v>30082.849999999995</v>
+        <v>29176.879999999997</v>
       </c>
       <c r="J152" s="14">
         <v>0</v>
@@ -8288,7 +8285,7 @@
       </c>
       <c r="L152" s="16">
         <f>SUM(I152:K152)</f>
-        <v>30082.85</v>
+        <v>29176.88</v>
       </c>
     </row>
     <row r="153" spans="1:12" ht="12.75">
@@ -8303,7 +8300,7 @@
       </c>
       <c r="D153" s="15" t="str">
         <f>CONCATENATE(C153," (Code: ",B153,")")</f>
-        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 5200-10600 lph, Head 57-18m without Panel Board (Code: GWDMR149)</v>
+        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 3000-7500 lph, Head 87-42m without Panel Board (Code: GWDMR150)</v>
       </c>
       <c r="E153" s="14" t="s">
         <v>18</v>
@@ -8315,10 +8312,10 @@
         <v>97</v>
       </c>
       <c r="H153" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I153" s="16">
-        <v>29176.879999999997</v>
+        <v>31360.499999999996</v>
       </c>
       <c r="J153" s="14">
         <v>0</v>
@@ -8329,7 +8326,7 @@
       </c>
       <c r="L153" s="16">
         <f>SUM(I153:K153)</f>
-        <v>29176.88</v>
+        <v>31360.50</v>
       </c>
     </row>
     <row r="154" spans="1:12" ht="12.75">
@@ -8344,7 +8341,7 @@
       </c>
       <c r="D154" s="15" t="str">
         <f>CONCATENATE(C154," (Code: ",B154,")")</f>
-        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 3000-7500 lph, Head 87-42m without Panel Board (Code: GWDMR150)</v>
+        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 2100-5400 lph, Head 116-33m without Panel Board (Code: GWDMR151)</v>
       </c>
       <c r="E154" s="14" t="s">
         <v>18</v>
@@ -8356,10 +8353,10 @@
         <v>97</v>
       </c>
       <c r="H154" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I154" s="16">
-        <v>31360.499999999996</v>
+        <v>29037.499999999996</v>
       </c>
       <c r="J154" s="14">
         <v>0</v>
@@ -8370,7 +8367,7 @@
       </c>
       <c r="L154" s="16">
         <f>SUM(I154:K154)</f>
-        <v>31360.50</v>
+        <v>29037.50</v>
       </c>
     </row>
     <row r="155" spans="1:12" ht="12.75">
@@ -8385,7 +8382,7 @@
       </c>
       <c r="D155" s="15" t="str">
         <f>CONCATENATE(C155," (Code: ",B155,")")</f>
-        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 2100-5400 lph, Head 116-33m without Panel Board (Code: GWDMR151)</v>
+        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 600-3600 lph, Head 161-18m without Panel Board (Code: GWDMR152)</v>
       </c>
       <c r="E155" s="14" t="s">
         <v>18</v>
@@ -8397,10 +8394,10 @@
         <v>97</v>
       </c>
       <c r="H155" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I155" s="16">
-        <v>29037.499999999996</v>
+        <v>29133.904499999997</v>
       </c>
       <c r="J155" s="14">
         <v>0</v>
@@ -8411,7 +8408,7 @@
       </c>
       <c r="L155" s="16">
         <f>SUM(I155:K155)</f>
-        <v>29037.50</v>
+        <v>29133.904500000001</v>
       </c>
     </row>
     <row r="156" spans="1:12" ht="12.75">
@@ -8426,7 +8423,7 @@
       </c>
       <c r="D156" s="15" t="str">
         <f>CONCATENATE(C156," (Code: ",B156,")")</f>
-        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 600-3600 lph, Head 161-18m without Panel Board (Code: GWDMR152)</v>
+        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 500-3000 lph, Head 194-65m without Panel Board (Code: GWDMR153)</v>
       </c>
       <c r="E156" s="14" t="s">
         <v>18</v>
@@ -8438,10 +8435,10 @@
         <v>97</v>
       </c>
       <c r="H156" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I156" s="16">
-        <v>29133.904499999997</v>
+        <v>37864.90</v>
       </c>
       <c r="J156" s="14">
         <v>0</v>
@@ -8452,7 +8449,7 @@
       </c>
       <c r="L156" s="16">
         <f>SUM(I156:K156)</f>
-        <v>29133.904500000001</v>
+        <v>37864.90</v>
       </c>
     </row>
     <row r="157" spans="1:12" ht="12.75">
@@ -8467,7 +8464,7 @@
       </c>
       <c r="D157" s="15" t="str">
         <f>CONCATENATE(C157," (Code: ",B157,")")</f>
-        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 500-3000 lph, Head 194-65m without Panel Board (Code: GWDMR153)</v>
+        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 500-1800 lph, Head 220-92m without Panel Board (Code: GWDMR154)</v>
       </c>
       <c r="E157" s="14" t="s">
         <v>18</v>
@@ -8479,10 +8476,10 @@
         <v>97</v>
       </c>
       <c r="H157" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I157" s="16">
-        <v>37864.90</v>
+        <v>44720.072999999997</v>
       </c>
       <c r="J157" s="14">
         <v>0</v>
@@ -8493,7 +8490,7 @@
       </c>
       <c r="L157" s="16">
         <f>SUM(I157:K157)</f>
-        <v>37864.90</v>
+        <v>44720.072999999997</v>
       </c>
     </row>
     <row r="158" spans="1:12" ht="12.75">
@@ -8508,7 +8505,7 @@
       </c>
       <c r="D158" s="15" t="str">
         <f>CONCATENATE(C158," (Code: ",B158,")")</f>
-        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 500-1800 lph, Head 220-92m without Panel Board (Code: GWDMR154)</v>
+        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 500-1800 lph, Head 247-104m without Panel Board (Code: GWDMR155)</v>
       </c>
       <c r="E158" s="14" t="s">
         <v>18</v>
@@ -8520,10 +8517,10 @@
         <v>97</v>
       </c>
       <c r="H158" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I158" s="16">
-        <v>44720.072999999997</v>
+        <v>47333.447999999997</v>
       </c>
       <c r="J158" s="14">
         <v>0</v>
@@ -8534,7 +8531,7 @@
       </c>
       <c r="L158" s="16">
         <f>SUM(I158:K158)</f>
-        <v>44720.072999999997</v>
+        <v>47333.447999999997</v>
       </c>
     </row>
     <row r="159" spans="1:12" ht="12.75">
@@ -8549,7 +8546,7 @@
       </c>
       <c r="D159" s="15" t="str">
         <f>CONCATENATE(C159," (Code: ",B159,")")</f>
-        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 500-1800 lph, Head 247-104m without Panel Board (Code: GWDMR155)</v>
+        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 500-1800 lph, Head 275-115m without Panel Board (Code: GWDMR156)</v>
       </c>
       <c r="E159" s="14" t="s">
         <v>18</v>
@@ -8561,10 +8558,10 @@
         <v>97</v>
       </c>
       <c r="H159" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I159" s="16">
-        <v>47333.447999999997</v>
+        <v>49068.728999999992</v>
       </c>
       <c r="J159" s="14">
         <v>0</v>
@@ -8575,7 +8572,7 @@
       </c>
       <c r="L159" s="16">
         <f>SUM(I159:K159)</f>
-        <v>47333.447999999997</v>
+        <v>49068.728999999999</v>
       </c>
     </row>
     <row r="160" spans="1:12" ht="12.75">
@@ -8590,7 +8587,7 @@
       </c>
       <c r="D160" s="15" t="str">
         <f>CONCATENATE(C160," (Code: ",B160,")")</f>
-        <v>Supply of Single Phase Submersible Pump 2 HP, Discharge 500-1800 lph, Head 275-115m without Panel Board (Code: GWDMR156)</v>
+        <v>Supply of Single Phase Submersible Pump 3 HP, Discharge 3240-7200 lph, Head 110-42m without Panel Board (Code: GWDMR157)</v>
       </c>
       <c r="E160" s="14" t="s">
         <v>18</v>
@@ -8602,10 +8599,10 @@
         <v>97</v>
       </c>
       <c r="H160" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I160" s="16">
-        <v>49068.728999999992</v>
+        <v>37138.962500000001</v>
       </c>
       <c r="J160" s="14">
         <v>0</v>
@@ -8616,7 +8613,7 @@
       </c>
       <c r="L160" s="16">
         <f>SUM(I160:K160)</f>
-        <v>49068.728999999999</v>
+        <v>37138.962500000001</v>
       </c>
     </row>
     <row r="161" spans="1:12" ht="12.75">
@@ -8631,7 +8628,7 @@
       </c>
       <c r="D161" s="15" t="str">
         <f>CONCATENATE(C161," (Code: ",B161,")")</f>
-        <v>Supply of Single Phase Submersible Pump 3 HP, Discharge 3240-7200 lph, Head 110-42m without Panel Board (Code: GWDMR157)</v>
+        <v>Supply of Single Phase Submersible Pump 3 HP, Discharge 1800-4320 lph, Head 194-114m without Panel Board (Code: GWDMR158)</v>
       </c>
       <c r="E161" s="14" t="s">
         <v>18</v>
@@ -8643,10 +8640,10 @@
         <v>97</v>
       </c>
       <c r="H161" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I161" s="16">
-        <v>37138.962500000001</v>
+        <v>47156.90</v>
       </c>
       <c r="J161" s="14">
         <v>0</v>
@@ -8657,7 +8654,7 @@
       </c>
       <c r="L161" s="16">
         <f>SUM(I161:K161)</f>
-        <v>37138.962500000001</v>
+        <v>47156.90</v>
       </c>
     </row>
     <row r="162" spans="1:12" ht="12.75">
@@ -8672,7 +8669,7 @@
       </c>
       <c r="D162" s="15" t="str">
         <f>CONCATENATE(C162," (Code: ",B162,")")</f>
-        <v>Supply of Single Phase Submersible Pump 3 HP, Discharge 1800-4320 lph, Head 194-114m without Panel Board (Code: GWDMR158)</v>
+        <v>Supply of Single Phase Submersible Pump 5 HP, Discharge 4320-10080 lph, Head 150-82m without Panel Board (Code: GWDMR159)</v>
       </c>
       <c r="E162" s="14" t="s">
         <v>18</v>
@@ -8684,10 +8681,10 @@
         <v>97</v>
       </c>
       <c r="H162" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I162" s="16">
-        <v>47156.90</v>
+        <v>45301.984499999999</v>
       </c>
       <c r="J162" s="14">
         <v>0</v>
@@ -8698,7 +8695,7 @@
       </c>
       <c r="L162" s="16">
         <f>SUM(I162:K162)</f>
-        <v>47156.90</v>
+        <v>45301.984499999999</v>
       </c>
     </row>
     <row r="163" spans="1:12" ht="12.75">
@@ -8713,7 +8710,7 @@
       </c>
       <c r="D163" s="15" t="str">
         <f>CONCATENATE(C163," (Code: ",B163,")")</f>
-        <v>Supply of Single Phase Submersible Pump 5 HP, Discharge 4320-10080 lph, Head 150-82m without Panel Board (Code: GWDMR159)</v>
+        <v>Supply of Single Phase Submersible Pump 6 HP, Discharge 1800-4320 lph, Head 318-210m without Panel Board (Code: GWDMR160)</v>
       </c>
       <c r="E163" s="14" t="s">
         <v>18</v>
@@ -8725,10 +8722,10 @@
         <v>97</v>
       </c>
       <c r="H163" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I163" s="16">
-        <v>45301.984499999999</v>
+        <v>52340.674500000001</v>
       </c>
       <c r="J163" s="14">
         <v>0</v>
@@ -8739,7 +8736,7 @@
       </c>
       <c r="L163" s="16">
         <f>SUM(I163:K163)</f>
-        <v>45301.984499999999</v>
+        <v>52340.674500000001</v>
       </c>
     </row>
     <row r="164" spans="1:12" ht="12.75">
@@ -8754,7 +8751,7 @@
       </c>
       <c r="D164" s="15" t="str">
         <f>CONCATENATE(C164," (Code: ",B164,")")</f>
-        <v>Supply of Single Phase Submersible Pump 6 HP, Discharge 1800-4320 lph, Head 318-210m without Panel Board (Code: GWDMR160)</v>
+        <v>Supply of Three Phase Submersible Pump 10 HP, Discharge 6000-18000 lph, Head 146-90m without Panel Board (Code: GWDMR161)</v>
       </c>
       <c r="E164" s="14" t="s">
         <v>18</v>
@@ -8766,10 +8763,10 @@
         <v>97</v>
       </c>
       <c r="H164" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I164" s="16">
-        <v>52340.674500000001</v>
+        <v>74549.715999999986</v>
       </c>
       <c r="J164" s="14">
         <v>0</v>
@@ -8780,7 +8777,7 @@
       </c>
       <c r="L164" s="16">
         <f>SUM(I164:K164)</f>
-        <v>52340.674500000001</v>
+        <v>74549.716</v>
       </c>
     </row>
     <row r="165" spans="1:12" ht="12.75">
@@ -8795,7 +8792,7 @@
       </c>
       <c r="D165" s="15" t="str">
         <f>CONCATENATE(C165," (Code: ",B165,")")</f>
-        <v>Supply of Three Phase Submersible Pump 10 HP, Discharge 6000-18000 lph, Head 146-90m without Panel Board (Code: GWDMR161)</v>
+        <v>Supply of Three Phase Submersible Pump 10 HP, Discharge 3600-21600 lph, Head 162-27m without Panel Board (Code: GWDMR162)</v>
       </c>
       <c r="E165" s="14" t="s">
         <v>18</v>
@@ -8807,10 +8804,10 @@
         <v>97</v>
       </c>
       <c r="H165" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I165" s="16">
-        <v>74549.715999999986</v>
+        <v>74092.085000000006</v>
       </c>
       <c r="J165" s="14">
         <v>0</v>
@@ -8821,7 +8818,7 @@
       </c>
       <c r="L165" s="16">
         <f>SUM(I165:K165)</f>
-        <v>74549.716</v>
+        <v>74092.085000000006</v>
       </c>
     </row>
     <row r="166" spans="1:12" ht="12.75">
@@ -8836,7 +8833,7 @@
       </c>
       <c r="D166" s="15" t="str">
         <f>CONCATENATE(C166," (Code: ",B166,")")</f>
-        <v>Supply of Three Phase Submersible Pump 10 HP, Discharge 3600-21600 lph, Head 162-27m without Panel Board (Code: GWDMR162)</v>
+        <v>Supply of Three Phase Submersible Pump 10 HP, Discharge 5000-14000 lph, Head 205-110m without Panel Board (Code: GWDMR163)</v>
       </c>
       <c r="E166" s="14" t="s">
         <v>18</v>
@@ -8848,10 +8845,10 @@
         <v>97</v>
       </c>
       <c r="H166" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I166" s="16">
-        <v>74092.085000000006</v>
+        <v>93543.725499999986</v>
       </c>
       <c r="J166" s="14">
         <v>0</v>
@@ -8862,7 +8859,7 @@
       </c>
       <c r="L166" s="16">
         <f>SUM(I166:K166)</f>
-        <v>74092.085000000006</v>
+        <v>93543.7255</v>
       </c>
     </row>
     <row r="167" spans="1:12" ht="12.75">
@@ -8877,7 +8874,7 @@
       </c>
       <c r="D167" s="15" t="str">
         <f>CONCATENATE(C167," (Code: ",B167,")")</f>
-        <v>Supply of Three Phase Submersible Pump 10 HP, Discharge 5000-14000 lph, Head 205-110m without Panel Board (Code: GWDMR163)</v>
+        <v>Supply of Three Phase Submersible Pump 10 HP, Discharge 3000-9000 lph, Head 279-144m without Panel Board (Code: GWDMR164)</v>
       </c>
       <c r="E167" s="14" t="s">
         <v>18</v>
@@ -8889,10 +8886,10 @@
         <v>97</v>
       </c>
       <c r="H167" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I167" s="16">
-        <v>93543.725499999986</v>
+        <v>88520.237999999983</v>
       </c>
       <c r="J167" s="14">
         <v>0</v>
@@ -8903,7 +8900,7 @@
       </c>
       <c r="L167" s="16">
         <f>SUM(I167:K167)</f>
-        <v>93543.7255</v>
+        <v>88520.237999999998</v>
       </c>
     </row>
     <row r="168" spans="1:12" ht="12.75">
@@ -8918,7 +8915,7 @@
       </c>
       <c r="D168" s="15" t="str">
         <f>CONCATENATE(C168," (Code: ",B168,")")</f>
-        <v>Supply of Three Phase Submersible Pump 10 HP, Discharge 3000-9000 lph, Head 279-144m without Panel Board (Code: GWDMR164)</v>
+        <v>Supply of Three Phase Submersible Pump 12.5 HP, Discharge 3600-25200 lph, Head 157-41m without Panel Board (Code: GWDMR165)</v>
       </c>
       <c r="E168" s="14" t="s">
         <v>18</v>
@@ -8930,10 +8927,10 @@
         <v>97</v>
       </c>
       <c r="H168" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I168" s="16">
-        <v>88520.237999999983</v>
+        <v>77646.274999999994</v>
       </c>
       <c r="J168" s="14">
         <v>0</v>
@@ -8944,7 +8941,7 @@
       </c>
       <c r="L168" s="16">
         <f>SUM(I168:K168)</f>
-        <v>88520.237999999998</v>
+        <v>77646.274999999994</v>
       </c>
     </row>
     <row r="169" spans="1:12" ht="12.75">
@@ -8959,7 +8956,7 @@
       </c>
       <c r="D169" s="15" t="str">
         <f>CONCATENATE(C169," (Code: ",B169,")")</f>
-        <v>Supply of Three Phase Submersible Pump 12.5 HP, Discharge 3600-25200 lph, Head 157-41m without Panel Board (Code: GWDMR165)</v>
+        <v>Supply of Three Phase Submersible Pump 12.5 HP, Discharge 6000-18000 lph, Head 179-110m without Panel Board (Code: GWDMR166)</v>
       </c>
       <c r="E169" s="14" t="s">
         <v>18</v>
@@ -8971,10 +8968,10 @@
         <v>97</v>
       </c>
       <c r="H169" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I169" s="16">
-        <v>77646.274999999994</v>
+        <v>82797.527499999997</v>
       </c>
       <c r="J169" s="14">
         <v>0</v>
@@ -8985,7 +8982,7 @@
       </c>
       <c r="L169" s="16">
         <f>SUM(I169:K169)</f>
-        <v>77646.274999999994</v>
+        <v>82797.527499999997</v>
       </c>
     </row>
     <row r="170" spans="1:12" ht="12.75">
@@ -9000,7 +8997,7 @@
       </c>
       <c r="D170" s="15" t="str">
         <f>CONCATENATE(C170," (Code: ",B170,")")</f>
-        <v>Supply of Three Phase Submersible Pump 12.5 HP, Discharge 6000-18000 lph, Head 179-110m without Panel Board (Code: GWDMR166)</v>
+        <v>Supply of Three Phase Submersible Pump 12.5 HP, Discharge 5000-14000 lph, Head 242-129m without Panel Board (Code: GWDMR167)</v>
       </c>
       <c r="E170" s="14" t="s">
         <v>18</v>
@@ -9012,10 +9009,10 @@
         <v>97</v>
       </c>
       <c r="H170" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I170" s="16">
-        <v>82797.527499999997</v>
+        <v>103464.09699999999</v>
       </c>
       <c r="J170" s="14">
         <v>0</v>
@@ -9026,7 +9023,7 @@
       </c>
       <c r="L170" s="16">
         <f>SUM(I170:K170)</f>
-        <v>82797.527499999997</v>
+        <v>103464.09699999999</v>
       </c>
     </row>
     <row r="171" spans="1:12" ht="12.75">
@@ -9041,7 +9038,7 @@
       </c>
       <c r="D171" s="15" t="str">
         <f>CONCATENATE(C171," (Code: ",B171,")")</f>
-        <v>Supply of Three Phase Submersible Pump 12.5 HP, Discharge 5000-14000 lph, Head 242-129m without Panel Board (Code: GWDMR167)</v>
+        <v>Supply of Three Phase Submersible Pump 12.5 HP, Discharge 3000-9000 lph, Head 335-177m without Panel Board (Code: GWDMR168)</v>
       </c>
       <c r="E171" s="14" t="s">
         <v>18</v>
@@ -9053,10 +9050,10 @@
         <v>97</v>
       </c>
       <c r="H171" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I171" s="16">
-        <v>103464.09699999999</v>
+        <v>98931.923999999999</v>
       </c>
       <c r="J171" s="14">
         <v>0</v>
@@ -9067,7 +9064,7 @@
       </c>
       <c r="L171" s="16">
         <f>SUM(I171:K171)</f>
-        <v>103464.09699999999</v>
+        <v>98931.923999999999</v>
       </c>
     </row>
     <row r="172" spans="1:12" ht="12.75">
@@ -9082,7 +9079,7 @@
       </c>
       <c r="D172" s="15" t="str">
         <f>CONCATENATE(C172," (Code: ",B172,")")</f>
-        <v>Supply of Three Phase Submersible Pump 12.5 HP, Discharge 3000-9000 lph, Head 335-177m without Panel Board (Code: GWDMR168)</v>
+        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 5200-10600 lph, Head 86-27m without Panel Board (Code: GWDMR169)</v>
       </c>
       <c r="E172" s="14" t="s">
         <v>18</v>
@@ -9094,10 +9091,10 @@
         <v>97</v>
       </c>
       <c r="H172" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I172" s="16">
-        <v>98931.923999999999</v>
+        <v>33242.13</v>
       </c>
       <c r="J172" s="14">
         <v>0</v>
@@ -9108,7 +9105,7 @@
       </c>
       <c r="L172" s="16">
         <f>SUM(I172:K172)</f>
-        <v>98931.923999999999</v>
+        <v>33242.13</v>
       </c>
     </row>
     <row r="173" spans="1:12" ht="12.75">
@@ -9123,7 +9120,7 @@
       </c>
       <c r="D173" s="15" t="str">
         <f>CONCATENATE(C173," (Code: ",B173,")")</f>
-        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 5200-10600 lph, Head 86-27m without Panel Board (Code: GWDMR169)</v>
+        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 3000-7500 lph, Head 125-60m without Panel Board (Code: GWDMR170)</v>
       </c>
       <c r="E173" s="14" t="s">
         <v>18</v>
@@ -9135,10 +9132,10 @@
         <v>97</v>
       </c>
       <c r="H173" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I173" s="16">
-        <v>33242.13</v>
+        <v>36924.084999999999</v>
       </c>
       <c r="J173" s="14">
         <v>0</v>
@@ -9149,7 +9146,7 @@
       </c>
       <c r="L173" s="16">
         <f>SUM(I173:K173)</f>
-        <v>33242.13</v>
+        <v>36924.084999999999</v>
       </c>
     </row>
     <row r="174" spans="1:12" ht="12.75">
@@ -9164,7 +9161,7 @@
       </c>
       <c r="D174" s="15" t="str">
         <f>CONCATENATE(C174," (Code: ",B174,")")</f>
-        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 3000-7500 lph, Head 125-60m without Panel Board (Code: GWDMR170)</v>
+        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 2500-6000 lph, Head 147-51m without Panel Board (Code: GWDMR171)</v>
       </c>
       <c r="E174" s="14" t="s">
         <v>18</v>
@@ -9176,10 +9173,10 @@
         <v>97</v>
       </c>
       <c r="H174" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I174" s="16">
-        <v>36924.084999999999</v>
+        <v>40652.50</v>
       </c>
       <c r="J174" s="14">
         <v>0</v>
@@ -9190,7 +9187,7 @@
       </c>
       <c r="L174" s="16">
         <f>SUM(I174:K174)</f>
-        <v>36924.084999999999</v>
+        <v>40652.50</v>
       </c>
     </row>
     <row r="175" spans="1:12" ht="12.75">
@@ -9205,7 +9202,7 @@
       </c>
       <c r="D175" s="15" t="str">
         <f>CONCATENATE(C175," (Code: ",B175,")")</f>
-        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 2500-6000 lph, Head 147-51m without Panel Board (Code: GWDMR171)</v>
+        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 1000-5000 lph, Head 163-66m without Panel Board (Code: GWDMR172)</v>
       </c>
       <c r="E175" s="14" t="s">
         <v>18</v>
@@ -9217,10 +9214,10 @@
         <v>97</v>
       </c>
       <c r="H175" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I175" s="16">
-        <v>40652.50</v>
+        <v>43011.506499999996</v>
       </c>
       <c r="J175" s="14">
         <v>0</v>
@@ -9231,7 +9228,7 @@
       </c>
       <c r="L175" s="16">
         <f>SUM(I175:K175)</f>
-        <v>40652.50</v>
+        <v>43011.506500000003</v>
       </c>
     </row>
     <row r="176" spans="1:12" ht="12.75">
@@ -9246,7 +9243,7 @@
       </c>
       <c r="D176" s="15" t="str">
         <f>CONCATENATE(C176," (Code: ",B176,")")</f>
-        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 1000-5000 lph, Head 163-66m without Panel Board (Code: GWDMR172)</v>
+        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 1200-2800 lph, Head 184-86m without Panel Board (Code: GWDMR173)</v>
       </c>
       <c r="E176" s="14" t="s">
         <v>18</v>
@@ -9258,10 +9255,10 @@
         <v>97</v>
       </c>
       <c r="H176" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I176" s="16">
-        <v>43011.506499999996</v>
+        <v>38391.059499999996</v>
       </c>
       <c r="J176" s="14">
         <v>0</v>
@@ -9272,7 +9269,7 @@
       </c>
       <c r="L176" s="16">
         <f>SUM(I176:K176)</f>
-        <v>43011.506500000003</v>
+        <v>38391.059500000003</v>
       </c>
     </row>
     <row r="177" spans="1:12" ht="12.75">
@@ -9287,7 +9284,7 @@
       </c>
       <c r="D177" s="15" t="str">
         <f>CONCATENATE(C177," (Code: ",B177,")")</f>
-        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 1200-2800 lph, Head 184-86m without Panel Board (Code: GWDMR173)</v>
+        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 1200-2800 lph, Head 207-83m without Panel Board (Code: GWDMR174)</v>
       </c>
       <c r="E177" s="14" t="s">
         <v>18</v>
@@ -9299,10 +9296,10 @@
         <v>97</v>
       </c>
       <c r="H177" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I177" s="16">
-        <v>38391.059499999996</v>
+        <v>50417.230499999998</v>
       </c>
       <c r="J177" s="14">
         <v>0</v>
@@ -9313,7 +9310,7 @@
       </c>
       <c r="L177" s="16">
         <f>SUM(I177:K177)</f>
-        <v>38391.059500000003</v>
+        <v>50417.230499999998</v>
       </c>
     </row>
     <row r="178" spans="1:12" ht="12.75">
@@ -9328,7 +9325,7 @@
       </c>
       <c r="D178" s="15" t="str">
         <f>CONCATENATE(C178," (Code: ",B178,")")</f>
-        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 1200-2800 lph, Head 207-83m without Panel Board (Code: GWDMR174)</v>
+        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 1200-2800 lph, Head 245-98m without Panel Board (Code: GWDMR175)</v>
       </c>
       <c r="E178" s="14" t="s">
         <v>18</v>
@@ -9340,10 +9337,10 @@
         <v>97</v>
       </c>
       <c r="H178" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I178" s="16">
-        <v>50417.230499999998</v>
+        <v>53114.233500000002</v>
       </c>
       <c r="J178" s="14">
         <v>0</v>
@@ -9354,7 +9351,7 @@
       </c>
       <c r="L178" s="16">
         <f>SUM(I178:K178)</f>
-        <v>50417.230499999998</v>
+        <v>53114.233500000002</v>
       </c>
     </row>
     <row r="179" spans="1:12" ht="12.75">
@@ -9369,7 +9366,7 @@
       </c>
       <c r="D179" s="15" t="str">
         <f>CONCATENATE(C179," (Code: ",B179,")")</f>
-        <v>Supply of Three Phase Submersible Pump 3 HP, Discharge 1200-2800 lph, Head 245-98m without Panel Board (Code: GWDMR175)</v>
+        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 9000-24000 lph, Head 70-23m without Panel Board (Code: GWDMR176)</v>
       </c>
       <c r="E179" s="14" t="s">
         <v>18</v>
@@ -9381,10 +9378,10 @@
         <v>97</v>
       </c>
       <c r="H179" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I179" s="16">
-        <v>53114.233500000002</v>
+        <v>54682.258499999996</v>
       </c>
       <c r="J179" s="14">
         <v>0</v>
@@ -9395,7 +9392,7 @@
       </c>
       <c r="L179" s="16">
         <f>SUM(I179:K179)</f>
-        <v>53114.233500000002</v>
+        <v>54682.258500000004</v>
       </c>
     </row>
     <row r="180" spans="1:12" ht="12.75">
@@ -9410,7 +9407,7 @@
       </c>
       <c r="D180" s="15" t="str">
         <f>CONCATENATE(C180," (Code: ",B180,")")</f>
-        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 9000-24000 lph, Head 70-23m without Panel Board (Code: GWDMR176)</v>
+        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 7200-15000 lph, Head 78-41m without Panel Board (Code: GWDMR177)</v>
       </c>
       <c r="E180" s="14" t="s">
         <v>18</v>
@@ -9422,10 +9419,10 @@
         <v>97</v>
       </c>
       <c r="H180" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I180" s="16">
-        <v>54682.258499999996</v>
+        <v>55751.999999999993</v>
       </c>
       <c r="J180" s="14">
         <v>0</v>
@@ -9436,7 +9433,7 @@
       </c>
       <c r="L180" s="16">
         <f>SUM(I180:K180)</f>
-        <v>54682.258500000004</v>
+        <v>55752</v>
       </c>
     </row>
     <row r="181" spans="1:12" ht="12.75">
@@ -9451,7 +9448,7 @@
       </c>
       <c r="D181" s="15" t="str">
         <f>CONCATENATE(C181," (Code: ",B181,")")</f>
-        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 7200-15000 lph, Head 78-41m without Panel Board (Code: GWDMR177)</v>
+        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 5000-14000 lph, Head 93-50m without Panel Board (Code: GWDMR178)</v>
       </c>
       <c r="E181" s="14" t="s">
         <v>18</v>
@@ -9463,10 +9460,10 @@
         <v>97</v>
       </c>
       <c r="H181" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I181" s="16">
-        <v>55751.999999999993</v>
+        <v>62396.941499999994</v>
       </c>
       <c r="J181" s="14">
         <v>0</v>
@@ -9477,7 +9474,7 @@
       </c>
       <c r="L181" s="16">
         <f>SUM(I181:K181)</f>
-        <v>55752</v>
+        <v>62396.941500000001</v>
       </c>
     </row>
     <row r="182" spans="1:12" ht="12.75">
@@ -9492,7 +9489,7 @@
       </c>
       <c r="D182" s="15" t="str">
         <f>CONCATENATE(C182," (Code: ",B182,")")</f>
-        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 5000-14000 lph, Head 93-50m without Panel Board (Code: GWDMR178)</v>
+        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 5000-14000 lph, Head 102-55m without Panel Board (Code: GWDMR179)</v>
       </c>
       <c r="E182" s="14" t="s">
         <v>18</v>
@@ -9504,10 +9501,10 @@
         <v>97</v>
       </c>
       <c r="H182" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I182" s="16">
-        <v>62396.941499999994</v>
+        <v>63505.01249999999</v>
       </c>
       <c r="J182" s="14">
         <v>0</v>
@@ -9518,7 +9515,7 @@
       </c>
       <c r="L182" s="16">
         <f>SUM(I182:K182)</f>
-        <v>62396.941500000001</v>
+        <v>63505.012499999997</v>
       </c>
     </row>
     <row r="183" spans="1:12" ht="12.75">
@@ -9533,7 +9530,7 @@
       </c>
       <c r="D183" s="15" t="str">
         <f>CONCATENATE(C183," (Code: ",B183,")")</f>
-        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 5000-14000 lph, Head 102-55m without Panel Board (Code: GWDMR179)</v>
+        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 3900-10800 lph, Head 111-49m without Panel Board (Code: GWDMR180)</v>
       </c>
       <c r="E183" s="14" t="s">
         <v>18</v>
@@ -9545,10 +9542,10 @@
         <v>97</v>
       </c>
       <c r="H183" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I183" s="16">
-        <v>63505.01249999999</v>
+        <v>65043.999999999993</v>
       </c>
       <c r="J183" s="14">
         <v>0</v>
@@ -9559,7 +9556,7 @@
       </c>
       <c r="L183" s="16">
         <f>SUM(I183:K183)</f>
-        <v>63505.012499999997</v>
+        <v>65044</v>
       </c>
     </row>
     <row r="184" spans="1:12" ht="12.75">
@@ -9574,7 +9571,7 @@
       </c>
       <c r="D184" s="15" t="str">
         <f>CONCATENATE(C184," (Code: ",B184,")")</f>
-        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 3900-10800 lph, Head 111-49m without Panel Board (Code: GWDMR180)</v>
+        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 3000-9000 lph, Head 140-72m without Panel Board (Code: GWDMR181)</v>
       </c>
       <c r="E184" s="14" t="s">
         <v>18</v>
@@ -9586,10 +9583,10 @@
         <v>97</v>
       </c>
       <c r="H184" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I184" s="16">
-        <v>65043.999999999993</v>
+        <v>65052.130499999999</v>
       </c>
       <c r="J184" s="14">
         <v>0</v>
@@ -9600,7 +9597,7 @@
       </c>
       <c r="L184" s="16">
         <f>SUM(I184:K184)</f>
-        <v>65044</v>
+        <v>65052.130499999999</v>
       </c>
     </row>
     <row r="185" spans="1:12" ht="12.75">
@@ -9615,7 +9612,7 @@
       </c>
       <c r="D185" s="15" t="str">
         <f>CONCATENATE(C185," (Code: ",B185,")")</f>
-        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 3000-9000 lph, Head 140-72m without Panel Board (Code: GWDMR181)</v>
+        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 4000-10000 lph, Head 163-62m without Panel Board (Code: GWDMR182)</v>
       </c>
       <c r="E185" s="14" t="s">
         <v>18</v>
@@ -9627,10 +9624,10 @@
         <v>97</v>
       </c>
       <c r="H185" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I185" s="16">
-        <v>65052.130499999999</v>
+        <v>51301.131999999998</v>
       </c>
       <c r="J185" s="14">
         <v>0</v>
@@ -9641,7 +9638,7 @@
       </c>
       <c r="L185" s="16">
         <f>SUM(I185:K185)</f>
-        <v>65052.130499999999</v>
+        <v>51301.131999999998</v>
       </c>
     </row>
     <row r="186" spans="1:12" ht="12.75">
@@ -9656,7 +9653,7 @@
       </c>
       <c r="D186" s="15" t="str">
         <f>CONCATENATE(C186," (Code: ",B186,")")</f>
-        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 4000-10000 lph, Head 163-62m without Panel Board (Code: GWDMR182)</v>
+        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 2000-6000 lph, Head 195-120m without Panel Board (Code: GWDMR183)</v>
       </c>
       <c r="E186" s="14" t="s">
         <v>18</v>
@@ -9668,10 +9665,10 @@
         <v>97</v>
       </c>
       <c r="H186" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I186" s="16">
-        <v>51301.131999999998</v>
+        <v>56820.579999999994</v>
       </c>
       <c r="J186" s="14">
         <v>0</v>
@@ -9682,7 +9679,7 @@
       </c>
       <c r="L186" s="16">
         <f>SUM(I186:K186)</f>
-        <v>51301.131999999998</v>
+        <v>56820.58</v>
       </c>
     </row>
     <row r="187" spans="1:12" ht="12.75">
@@ -9697,7 +9694,7 @@
       </c>
       <c r="D187" s="15" t="str">
         <f>CONCATENATE(C187," (Code: ",B187,")")</f>
-        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 2000-6000 lph, Head 195-120m without Panel Board (Code: GWDMR183)</v>
+        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 2500-6000 lph, Head 245-85m without Panel Board (Code: GWDMR184)</v>
       </c>
       <c r="E187" s="14" t="s">
         <v>18</v>
@@ -9709,10 +9706,10 @@
         <v>97</v>
       </c>
       <c r="H187" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I187" s="16">
-        <v>56820.579999999994</v>
+        <v>54590.499999999993</v>
       </c>
       <c r="J187" s="14">
         <v>0</v>
@@ -9723,7 +9720,7 @@
       </c>
       <c r="L187" s="16">
         <f>SUM(I187:K187)</f>
-        <v>56820.58</v>
+        <v>54590.50</v>
       </c>
     </row>
     <row r="188" spans="1:12" ht="12.75">
@@ -9738,7 +9735,7 @@
       </c>
       <c r="D188" s="15" t="str">
         <f>CONCATENATE(C188," (Code: ",B188,")")</f>
-        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 2500-6000 lph, Head 245-85m without Panel Board (Code: GWDMR184)</v>
+        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 2500-6000 lph, Head 285-70m without Panel Board (Code: GWDMR185)</v>
       </c>
       <c r="E188" s="14" t="s">
         <v>18</v>
@@ -9750,10 +9747,10 @@
         <v>97</v>
       </c>
       <c r="H188" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I188" s="16">
-        <v>54590.499999999993</v>
+        <v>61559.499999999993</v>
       </c>
       <c r="J188" s="14">
         <v>0</v>
@@ -9764,7 +9761,7 @@
       </c>
       <c r="L188" s="16">
         <f>SUM(I188:K188)</f>
-        <v>54590.50</v>
+        <v>61559.50</v>
       </c>
     </row>
     <row r="189" spans="1:12" ht="12.75">
@@ -9779,7 +9776,7 @@
       </c>
       <c r="D189" s="15" t="str">
         <f>CONCATENATE(C189," (Code: ",B189,")")</f>
-        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 2500-6000 lph, Head 285-70m without Panel Board (Code: GWDMR185)</v>
+        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 1000-3000 lph, Head 333-183m without Panel Board (Code: GWDMR186)</v>
       </c>
       <c r="E189" s="14" t="s">
         <v>18</v>
@@ -9791,10 +9788,10 @@
         <v>97</v>
       </c>
       <c r="H189" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I189" s="16">
-        <v>61559.499999999993</v>
+        <v>80209.705499999982</v>
       </c>
       <c r="J189" s="14">
         <v>0</v>
@@ -9805,7 +9802,7 @@
       </c>
       <c r="L189" s="16">
         <f>SUM(I189:K189)</f>
-        <v>61559.50</v>
+        <v>80209.705499999996</v>
       </c>
     </row>
     <row r="190" spans="1:12" ht="12.75">
@@ -9820,7 +9817,7 @@
       </c>
       <c r="D190" s="15" t="str">
         <f>CONCATENATE(C190," (Code: ",B190,")")</f>
-        <v>Supply of Three Phase Submersible Pump 5 HP, Discharge 1000-3000 lph, Head 333-183m without Panel Board (Code: GWDMR186)</v>
+        <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 12000-30000 lph, Head 74-29m without Panel Board (Code: GWDMR187)</v>
       </c>
       <c r="E190" s="14" t="s">
         <v>18</v>
@@ -9832,10 +9829,10 @@
         <v>97</v>
       </c>
       <c r="H190" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I190" s="16">
-        <v>80209.705499999982</v>
+        <v>61559.499999999993</v>
       </c>
       <c r="J190" s="14">
         <v>0</v>
@@ -9846,7 +9843,7 @@
       </c>
       <c r="L190" s="16">
         <f>SUM(I190:K190)</f>
-        <v>80209.705499999996</v>
+        <v>61559.50</v>
       </c>
     </row>
     <row r="191" spans="1:12" ht="12.75">
@@ -9861,7 +9858,7 @@
       </c>
       <c r="D191" s="15" t="str">
         <f>CONCATENATE(C191," (Code: ",B191,")")</f>
-        <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 12000-30000 lph, Head 74-29m without Panel Board (Code: GWDMR187)</v>
+        <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 7200-18000 lph, Head 94-65m without Panel Board (Code: GWDMR188)</v>
       </c>
       <c r="E191" s="14" t="s">
         <v>18</v>
@@ -9873,10 +9870,10 @@
         <v>97</v>
       </c>
       <c r="H191" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I191" s="16">
-        <v>61559.499999999993</v>
+        <v>56332.749999999993</v>
       </c>
       <c r="J191" s="14">
         <v>0</v>
@@ -9887,7 +9884,7 @@
       </c>
       <c r="L191" s="16">
         <f>SUM(I191:K191)</f>
-        <v>61559.50</v>
+        <v>56332.75</v>
       </c>
     </row>
     <row r="192" spans="1:12" ht="12.75">
@@ -9902,7 +9899,7 @@
       </c>
       <c r="D192" s="15" t="str">
         <f>CONCATENATE(C192," (Code: ",B192,")")</f>
-        <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 7200-18000 lph, Head 94-65m without Panel Board (Code: GWDMR188)</v>
+        <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 6000-18000 lph, Head 112-69m without Panel Board (Code: GWDMR189)</v>
       </c>
       <c r="E192" s="14" t="s">
         <v>18</v>
@@ -9914,10 +9911,10 @@
         <v>97</v>
       </c>
       <c r="H192" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I192" s="16">
-        <v>56332.749999999993</v>
+        <v>67216.005000000005</v>
       </c>
       <c r="J192" s="14">
         <v>0</v>
@@ -9928,7 +9925,7 @@
       </c>
       <c r="L192" s="16">
         <f>SUM(I192:K192)</f>
-        <v>56332.75</v>
+        <v>67216.005000000005</v>
       </c>
     </row>
     <row r="193" spans="1:12" ht="12.75">
@@ -9943,7 +9940,7 @@
       </c>
       <c r="D193" s="15" t="str">
         <f>CONCATENATE(C193," (Code: ",B193,")")</f>
-        <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 6000-18000 lph, Head 112-69m without Panel Board (Code: GWDMR189)</v>
+        <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 5000-14000 lph, Head 140-75m without Panel Board (Code: GWDMR190)</v>
       </c>
       <c r="E193" s="14" t="s">
         <v>18</v>
@@ -9955,10 +9952,10 @@
         <v>97</v>
       </c>
       <c r="H193" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I193" s="16">
-        <v>67216.005000000005</v>
+        <v>72003.707999999984</v>
       </c>
       <c r="J193" s="14">
         <v>0</v>
@@ -9969,7 +9966,7 @@
       </c>
       <c r="L193" s="16">
         <f>SUM(I193:K193)</f>
-        <v>67216.005000000005</v>
+        <v>72003.707999999999</v>
       </c>
     </row>
     <row r="194" spans="1:12" ht="12.75">
@@ -9984,7 +9981,7 @@
       </c>
       <c r="D194" s="15" t="str">
         <f>CONCATENATE(C194," (Code: ",B194,")")</f>
-        <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 5000-14000 lph, Head 140-75m without Panel Board (Code: GWDMR190)</v>
+        <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 5000-14000 lph, Head 158-85m without Panel Board (Code: GWDMR191)</v>
       </c>
       <c r="E194" s="14" t="s">
         <v>18</v>
@@ -9996,10 +9993,10 @@
         <v>97</v>
       </c>
       <c r="H194" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I194" s="16">
-        <v>72003.707999999984</v>
+        <v>74094.407999999996</v>
       </c>
       <c r="J194" s="14">
         <v>0</v>
@@ -10010,7 +10007,7 @@
       </c>
       <c r="L194" s="16">
         <f>SUM(I194:K194)</f>
-        <v>72003.707999999999</v>
+        <v>74094.407999999996</v>
       </c>
     </row>
     <row r="195" spans="1:12" ht="12.75">
@@ -10025,7 +10022,7 @@
       </c>
       <c r="D195" s="15" t="str">
         <f>CONCATENATE(C195," (Code: ",B195,")")</f>
-        <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 5000-14000 lph, Head 158-85m without Panel Board (Code: GWDMR191)</v>
+        <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 3000-9000 lph, Head 214-110m without Panel Board (Code: GWDMR192)</v>
       </c>
       <c r="E195" s="14" t="s">
         <v>18</v>
@@ -10037,10 +10034,10 @@
         <v>97</v>
       </c>
       <c r="H195" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I195" s="16">
-        <v>74094.407999999996</v>
+        <v>76598.601999999999</v>
       </c>
       <c r="J195" s="14">
         <v>0</v>
@@ -10051,7 +10048,7 @@
       </c>
       <c r="L195" s="16">
         <f>SUM(I195:K195)</f>
-        <v>74094.407999999996</v>
+        <v>76598.601999999999</v>
       </c>
     </row>
     <row r="196" spans="1:12" ht="12.75">
@@ -10066,7 +10063,7 @@
       </c>
       <c r="D196" s="15" t="str">
         <f>CONCATENATE(C196," (Code: ",B196,")")</f>
-        <v>Supply of Three Phase Submersible Pump 7.5 HP, Discharge 3000-9000 lph, Head 214-110m without Panel Board (Code: GWDMR192)</v>
+        <v>32 A DP switch with indicator modular (MR1017) (Code: GWDMR193)</v>
       </c>
       <c r="E196" s="14" t="s">
         <v>18</v>
@@ -10078,10 +10075,10 @@
         <v>97</v>
       </c>
       <c r="H196" s="16" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="I196" s="16">
-        <v>76598.601999999999</v>
+        <v>432</v>
       </c>
       <c r="J196" s="14">
         <v>0</v>
@@ -10092,7 +10089,7 @@
       </c>
       <c r="L196" s="16">
         <f>SUM(I196:K196)</f>
-        <v>76598.601999999999</v>
+        <v>432</v>
       </c>
     </row>
     <row r="197" spans="1:12" ht="12.75">
@@ -10107,7 +10104,7 @@
       </c>
       <c r="D197" s="15" t="str">
         <f>CONCATENATE(C197," (Code: ",B197,")")</f>
-        <v>32 A DP switch with indicator modular (MR1017) (Code: GWDMR193)</v>
+        <v>S&amp;F Digital Timer Switch (Code: GWDMR194)</v>
       </c>
       <c r="E197" s="14" t="s">
         <v>18</v>
@@ -10119,10 +10116,10 @@
         <v>97</v>
       </c>
       <c r="H197" s="16" t="s">
-        <v>275</v>
+        <v>388</v>
       </c>
       <c r="I197" s="16">
-        <v>432</v>
+        <v>6500</v>
       </c>
       <c r="J197" s="14">
         <v>0</v>
@@ -10133,47 +10130,6 @@
       </c>
       <c r="L197" s="16">
         <f>SUM(I197:K197)</f>
-        <v>432</v>
-      </c>
-    </row>
-    <row r="198" spans="1:12" ht="12.75">
-      <c r="A198" s="14">
-        <v>194</v>
-      </c>
-      <c r="B198" s="15" t="s">
-        <v>388</v>
-      </c>
-      <c r="C198" s="15" t="s">
-        <v>389</v>
-      </c>
-      <c r="D198" s="15" t="str">
-        <f>CONCATENATE(C198," (Code: ",B198,")")</f>
-        <v>S&amp;F Digital Timer Switch (Code: GWDMR194)</v>
-      </c>
-      <c r="E198" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F198" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="G198" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="H198" s="16" t="s">
-        <v>390</v>
-      </c>
-      <c r="I198" s="16">
-        <v>6500</v>
-      </c>
-      <c r="J198" s="14">
-        <v>0</v>
-      </c>
-      <c r="K198" s="16">
-        <f>J198*($L$2-1)</f>
-        <v>0</v>
-      </c>
-      <c r="L198" s="16">
-        <f>SUM(I198:K198)</f>
         <v>6500</v>
       </c>
     </row>

--- a/Side Bar Files/GWD Data/GWD MR Abstract.xlsx
+++ b/Side Bar Files/GWD Data/GWD MR Abstract.xlsx
@@ -1969,7 +1969,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70888093-A0FC-4BA7-ABC4-4853744BBAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52202B0D-C0C2-4FBF-95CF-543DE7DCBAA6}">
   <dimension ref="A1:L197"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
